--- a/ContinuationProject/Status.xlsx
+++ b/ContinuationProject/Status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\ContinuationProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C896A366-1AF6-435F-899C-9D1AE0CCB2A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E66656EF-1B3C-4BB4-B7EB-DC4556C93554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="AdditionalActivities" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Status!$B$3:$I$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Status!$B$3:$I$46</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="53">
   <si>
     <t>DISC DEXPI Continuation Project - Status</t>
   </si>
@@ -63,12 +63,6 @@
     <t>Normal</t>
   </si>
   <si>
-    <t>Not Started</t>
-  </si>
-  <si>
-    <t>In Progress</t>
-  </si>
-  <si>
     <t>High</t>
   </si>
   <si>
@@ -102,16 +96,10 @@
     <t>Electrical Line type</t>
   </si>
   <si>
-    <t>Clamp-on sensing element</t>
-  </si>
-  <si>
     <t>Update requirements document</t>
   </si>
   <si>
     <t xml:space="preserve">DISC Workshops and meetings </t>
-  </si>
-  <si>
-    <t>Complete</t>
   </si>
   <si>
     <t>Creation of machine-readable DISC DEXPI Profile</t>
@@ -206,6 +194,15 @@
 Thermowell as Sensorwell
 Proteus example for CustomInlineMeasuringElement
 DEXPI 2.0 examples</t>
+  </si>
+  <si>
+    <t>Motor - Equipment Linking</t>
+  </si>
+  <si>
+    <t>Duplicate/incorrect names Fan/Blower</t>
+  </si>
+  <si>
+    <t>Fixed in DEXPI 2.0</t>
   </si>
 </sst>
 </file>
@@ -215,7 +212,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;Done&quot;;&quot;&quot;;&quot;&quot;"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -274,6 +271,12 @@
       <color theme="3"/>
       <name val="Bookman Old Style"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -335,7 +338,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
@@ -361,32 +364,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="5" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Date" xfId="6" xr:uid="{2ABB41C5-3CC8-4E1C-85D9-965CF83E22BD}"/>
@@ -742,7 +739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825F216F-6A2C-43F0-976D-4459909E096A}">
-  <dimension ref="A1:I47"/>
+  <dimension ref="B1:I46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="45.42578125" customWidth="1"/>
@@ -755,8 +752,8 @@
     <col min="9" max="9" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="35.25" x14ac:dyDescent="0.5">
-      <c r="B1" s="20" t="s">
+    <row r="1" spans="2:9" ht="35.25" x14ac:dyDescent="0.5">
+      <c r="B1" s="17" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="6"/>
@@ -767,7 +764,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="6"/>
     </row>
-    <row r="2" spans="1:9" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:9" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="6"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -776,16 +773,15 @@
       <c r="H2" s="1"/>
       <c r="I2" s="6"/>
     </row>
-    <row r="3" spans="1:9" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="16"/>
+    <row r="3" spans="2:9" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>1</v>
@@ -803,929 +799,955 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>21</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="10" t="s">
-        <v>8</v>
+      <c r="F4" s="10" t="str">
+        <f>IF(G4=1,"Complete",IF(G4&lt;&gt;0,"In Progess","Not Started"))</f>
+        <v>In Progess</v>
       </c>
       <c r="G4" s="11">
         <v>0.3</v>
       </c>
-      <c r="H4" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H4" s="12">
+        <f>--(G4&gt;=1)</f>
+        <v>0</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>26</v>
+        <v>20</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="10"/>
-      <c r="F5" s="10" t="s">
-        <v>8</v>
+      <c r="F5" s="10" t="str">
+        <f t="shared" ref="F5:F46" si="0">IF(G5=1,"Complete",IF(G5&lt;&gt;0,"In Progess","Not Started"))</f>
+        <v>In Progess</v>
       </c>
       <c r="G5" s="11">
         <v>0.75</v>
       </c>
-      <c r="H5" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H5" s="12">
+        <f t="shared" ref="H5:H46" si="1">--(G5&gt;=1)</f>
+        <v>0</v>
       </c>
       <c r="I5" s="10"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>34</v>
+        <v>10</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>30</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="F6" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>In Progess</v>
       </c>
       <c r="G6" s="11">
         <v>0.8</v>
       </c>
-      <c r="H6" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H6" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I6" s="10"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>35</v>
+        <v>10</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>31</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="10"/>
-      <c r="F7" s="10" t="s">
-        <v>7</v>
+      <c r="F7" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
       </c>
       <c r="G7" s="11"/>
-      <c r="H7" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H7" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I7" s="10"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>36</v>
+        <v>10</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>32</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="10" t="s">
         <v>7</v>
       </c>
+      <c r="F8" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
       <c r="G8" s="11"/>
-      <c r="H8" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H8" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I8" s="10"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>37</v>
+        <v>10</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>33</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="10"/>
-      <c r="F9" s="10" t="s">
-        <v>7</v>
+      <c r="F9" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
       </c>
       <c r="G9" s="11"/>
-      <c r="H9" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H9" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I9" s="10"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>37</v>
+        <v>11</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>33</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>7</v>
+        <v>12</v>
+      </c>
+      <c r="F10" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
       </c>
       <c r="G10" s="11"/>
-      <c r="H10" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H10" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I10" s="10"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>35</v>
+        <v>13</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>31</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
-      <c r="F11" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G11" s="11"/>
-      <c r="H11" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="F11" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G11" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="H11" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I11" s="10"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>36</v>
+        <v>13</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>32</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
-      <c r="F12" s="10" t="s">
-        <v>7</v>
+      <c r="F12" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
       </c>
       <c r="G12" s="11"/>
-      <c r="H12" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H12" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I12" s="10"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>37</v>
+        <v>13</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>33</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
-      <c r="F13" s="10" t="s">
-        <v>7</v>
+      <c r="F13" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
       </c>
       <c r="G13" s="11"/>
-      <c r="H13" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H13" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I13" s="10"/>
     </row>
-    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>38</v>
+        <v>14</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>51</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
-      <c r="F14" s="10" t="s">
-        <v>8</v>
+      <c r="F14" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Complete</v>
       </c>
       <c r="G14" s="11">
+        <v>1</v>
+      </c>
+      <c r="H14" s="12">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B15" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G15" s="11">
         <v>0.7</v>
       </c>
-      <c r="H14" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I14" s="10"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="G15" s="11">
-        <v>0.2</v>
-      </c>
-      <c r="H15" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H15" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I15" s="10"/>
     </row>
-    <row r="16" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>34</v>
+        <v>15</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>35</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G16" s="11"/>
-      <c r="H16" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="F16" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G16" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="H16" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I16" s="10"/>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10" t="s">
         <v>7</v>
       </c>
+      <c r="F17" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
       <c r="G17" s="11"/>
-      <c r="H17" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H17" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I17" s="10"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>7</v>
+        <v>15</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="13"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
       </c>
       <c r="G18" s="11"/>
-      <c r="H18" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H18" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I18" s="10"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="13"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10" t="s">
         <v>7</v>
       </c>
+      <c r="F19" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
       <c r="G19" s="11"/>
-      <c r="H19" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H19" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I19" s="10"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>7</v>
+        <v>15</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="13"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
       </c>
       <c r="G20" s="11"/>
-      <c r="H20" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H20" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I20" s="10"/>
     </row>
-    <row r="21" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>34</v>
+        <v>16</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>35</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="10" t="s">
         <v>7</v>
       </c>
+      <c r="F21" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
       <c r="G21" s="11"/>
-      <c r="H21" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H21" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I21" s="10"/>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="13"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10" t="s">
         <v>7</v>
       </c>
+      <c r="F22" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
       <c r="G22" s="11"/>
-      <c r="H22" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H22" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I22" s="10"/>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>7</v>
+        <v>16</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="13"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
       </c>
       <c r="G23" s="11"/>
-      <c r="H23" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H23" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I23" s="10"/>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" s="13"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10" t="s">
         <v>7</v>
       </c>
+      <c r="F24" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
       <c r="G24" s="11"/>
-      <c r="H24" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H24" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I24" s="10"/>
     </row>
-    <row r="25" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" s="13"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G25" s="11"/>
+      <c r="H25" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I25" s="10"/>
+    </row>
+    <row r="26" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="G25" s="11"/>
-      <c r="H25" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I25" s="10"/>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B26" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="D26" s="13"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10" t="s">
+      <c r="C26" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G26" s="11"/>
-      <c r="H26" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="F26" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G26" s="11">
+        <v>0.6</v>
+      </c>
+      <c r="H26" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I26" s="10"/>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B27" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="13"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
       </c>
       <c r="G27" s="11"/>
-      <c r="H27" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H27" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I27" s="10"/>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B28" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D28" s="13"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10" t="s">
         <v>7</v>
       </c>
+      <c r="F28" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
       <c r="G28" s="11"/>
-      <c r="H28" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H28" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I28" s="10"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C29" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" s="13"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
       </c>
       <c r="G29" s="11"/>
-      <c r="H29" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H29" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I29" s="10"/>
     </row>
-    <row r="30" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C30" s="18" t="s">
-        <v>34</v>
+        <v>17</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>35</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" s="10" t="s">
         <v>7</v>
       </c>
+      <c r="F30" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
       <c r="G30" s="11"/>
-      <c r="H30" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H30" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I30" s="10"/>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="D31" s="13"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10" t="s">
         <v>7</v>
       </c>
+      <c r="F31" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
       <c r="G31" s="11"/>
-      <c r="H31" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H31" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I31" s="10"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C32" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>7</v>
+        <v>17</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="13"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
       </c>
       <c r="G32" s="11"/>
-      <c r="H32" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H32" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I32" s="10"/>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C33" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D33" s="13"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10" t="s">
         <v>7</v>
       </c>
+      <c r="F33" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
       <c r="G33" s="11"/>
-      <c r="H33" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H33" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I33" s="10"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C34" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="G34" s="11">
-        <v>0.6</v>
-      </c>
-      <c r="H34" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+        <v>17</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="13"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G34" s="11"/>
+      <c r="H34" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I34" s="10"/>
     </row>
-    <row r="35" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C35" s="18" t="s">
-        <v>34</v>
+        <v>50</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>31</v>
       </c>
       <c r="D35" s="10"/>
       <c r="E35" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="F35" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>In Progess</v>
       </c>
       <c r="G35" s="11">
-        <v>0.6</v>
-      </c>
-      <c r="H35" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+        <v>0.9</v>
+      </c>
+      <c r="H35" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I35" s="10"/>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C36" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="D36" s="13"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10" t="s">
         <v>7</v>
       </c>
+      <c r="F36" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
       <c r="G36" s="11"/>
-      <c r="H36" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H36" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I36" s="10"/>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B37" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D37" s="13"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G37" s="11"/>
+      <c r="H37" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I37" s="10"/>
+    </row>
+    <row r="38" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B38" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10" t="s">
+      <c r="C38" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F37" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G37" s="11"/>
-      <c r="H37" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I37" s="10"/>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B38" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D38" s="13"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G38" s="11"/>
-      <c r="H38" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I38" s="10"/>
-    </row>
-    <row r="39" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="E38" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F38" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G38" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="H38" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C39" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>11</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39" s="10"/>
       <c r="E39" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>8</v>
+      <c r="F39" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>In Progess</v>
       </c>
       <c r="G39" s="11">
         <v>0.8</v>
       </c>
-      <c r="H39" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H39" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" ht="75" x14ac:dyDescent="0.25">
       <c r="B40" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C40" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" s="10" t="s">
-        <v>8</v>
+        <v>18</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D40" s="13"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>In Progess</v>
       </c>
       <c r="G40" s="11">
-        <v>0.8</v>
-      </c>
-      <c r="H40" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+        <v>0.4</v>
+      </c>
+      <c r="H40" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="41" spans="2:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="B41" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C41" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D41" s="13"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10" t="s">
-        <v>8</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B41" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Complete</v>
       </c>
       <c r="G41" s="11">
-        <v>0.4</v>
-      </c>
-      <c r="H41" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I41" s="10" t="s">
-        <v>53</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H41" s="12">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I41" s="10"/>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B42" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C42" s="17" t="s">
-        <v>48</v>
+        <v>19</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
-      <c r="F42" s="10" t="s">
-        <v>23</v>
+      <c r="F42" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Complete</v>
       </c>
       <c r="G42" s="11">
         <v>1</v>
       </c>
-      <c r="H42" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H42" s="12">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="I42" s="10"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C43" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="D43" s="8"/>
+        <v>25</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D43" s="13"/>
       <c r="E43" s="8"/>
-      <c r="F43" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G43" s="11">
-        <v>1</v>
-      </c>
-      <c r="H43" s="12" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="F43" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G43" s="14">
+        <v>0.7</v>
+      </c>
+      <c r="H43" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I43" s="10"/>
     </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B44" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C44" s="17" t="s">
-        <v>44</v>
+        <v>25</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="D44" s="13"/>
       <c r="E44" s="8"/>
-      <c r="F44" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="G44" s="14">
-        <v>0.7</v>
-      </c>
-      <c r="H44" s="15" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I44" s="10"/>
-    </row>
-    <row r="45" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="F44" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G44" s="14"/>
+      <c r="H44" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I44" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B45" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C45" s="17" t="s">
-        <v>45</v>
+        <v>26</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="D45" s="13"/>
       <c r="E45" s="8"/>
-      <c r="F45" s="10" t="s">
-        <v>7</v>
+      <c r="F45" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>In Progess</v>
       </c>
       <c r="G45" s="14">
-        <v>0</v>
-      </c>
-      <c r="H45" s="15" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I45" s="10" t="s">
-        <v>51</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="H45" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I45" s="10"/>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B46" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C46" s="17" t="s">
-        <v>46</v>
+        <v>27</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="D46" s="13"/>
       <c r="E46" s="8"/>
-      <c r="F46" s="10" t="s">
-        <v>8</v>
+      <c r="F46" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>In Progess</v>
       </c>
       <c r="G46" s="14">
         <v>0.5</v>
       </c>
-      <c r="H46" s="15" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
+      <c r="H46" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="I46" s="10"/>
     </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B47" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D47" s="13"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="G47" s="14">
-        <v>0.5</v>
-      </c>
-      <c r="H47" s="15" t="e">
-        <f>--(#REF!&gt;=1)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I47" s="10"/>
-    </row>
   </sheetData>
-  <autoFilter ref="B3:I47" xr:uid="{825F216F-6A2C-43F0-976D-4459909E096A}"/>
-  <conditionalFormatting sqref="G4:G47">
+  <autoFilter ref="B3:I46" xr:uid="{825F216F-6A2C-43F0-976D-4459909E096A}"/>
+  <conditionalFormatting sqref="G4:G46">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -1747,10 +1769,10 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Start Date in this column under this heading" sqref="I3" xr:uid="{B097AD3D-83FE-4DB6-8AA6-82D58880DEE8}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Icon indicator for task completion in this column under this heading is automatically updated as tasks complete" sqref="H3" xr:uid="{E57FD015-A334-4A3D-9540-92E1D8A918A9}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Task in this column under this heading. Use heading filters to find specific entries" sqref="B3:D3" xr:uid="{6FDCA3F5-F6F1-45FB-8AE7-E90C5E60E365}"/>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Select entry from the list. Select CANCEL, then press ALT+DOWN ARROW to navigate the list. Select ENTER to make selection" sqref="E4:E47" xr:uid="{8008394D-C04C-402E-A902-C9B94024D87C}">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Select entry from the list. Select CANCEL, then press ALT+DOWN ARROW to navigate the list. Select ENTER to make selection" sqref="E4:E46" xr:uid="{8008394D-C04C-402E-A902-C9B94024D87C}">
       <formula1>"Low, Normal, High"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Select entry from the list. Select CANCEL, then press ALT+DOWN ARROW to navigate the list. Select ENTER to make selection" sqref="F4:F47" xr:uid="{90892BC2-20A5-4151-9864-7558336C2FE7}">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Select entry from the list. Select CANCEL, then press ALT+DOWN ARROW to navigate the list. Select ENTER to make selection" sqref="F4:F46" xr:uid="{90892BC2-20A5-4151-9864-7558336C2FE7}">
       <formula1>"Not Started, In Progress, Deferred, Complete"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1771,10 +1793,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>G4:G47</xm:sqref>
+          <xm:sqref>G4:G46</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="11" id="{E713B901-0E7B-40B8-A534-1C73C66CF397}">
+          <x14:cfRule type="iconSet" priority="17" id="{E713B901-0E7B-40B8-A534-1C73C66CF397}">
             <x14:iconSet iconSet="3Symbols" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -1790,7 +1812,7 @@
               <x14:cfIcon iconSet="3Symbols" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>H4:H47</xm:sqref>
+          <xm:sqref>H4:H46</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -1808,6 +1830,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100C3422A7FFD03AF47B40E3148D61510DD" ma:contentTypeVersion="10" ma:contentTypeDescription="Opprett et nytt dokument." ma:contentTypeScope="" ma:versionID="93a5827b91256c075a5bcdb454d162de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0" xmlns:ns3="b6192152-6ac4-477a-b62a-2f500fcdf3b6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="13127a08f307124b01356346b67d6a81" ns2:_="" ns3:_="">
     <xsd:import namespace="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
@@ -2008,22 +2045,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CED3C9C-630D-4C4B-A736-44AEC9EEC0A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2040,29 +2087,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/ContinuationProject/Status.xlsx
+++ b/ContinuationProject/Status.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\ContinuationProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E66656EF-1B3C-4BB4-B7EB-DC4556C93554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17228147-18F1-4E29-A4B7-D7FD701E4DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="4" r:id="rId1"/>
-    <sheet name="AdditionalActivities" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId2"/>
+    <sheet name="AdditionalActivities" sheetId="2" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Status!$B$3:$I$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Status!$B$3:$I$47</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="58">
   <si>
     <t>DISC DEXPI Continuation Project - Status</t>
   </si>
@@ -109,9 +110,6 @@
   </si>
   <si>
     <t>Extraction of remaining information from the Excel, Drawio, and SVG sources and inclusion in DiscProfile RC 1</t>
-  </si>
-  <si>
-    <t>Only those symbols in the correct format will be made available in the profile.</t>
   </si>
   <si>
     <t>Currently working on information model for constraints</t>
@@ -203,6 +201,25 @@
   </si>
   <si>
     <t>Fixed in DEXPI 2.0</t>
+  </si>
+  <si>
+    <t>Only those symbols in the correct format will be made available in the profile.
+Challenge with dash lines/hash</t>
+  </si>
+  <si>
+    <t>Label addition to profile</t>
+  </si>
+  <si>
+    <t>Text rotation, Label position, Link to attributes</t>
+  </si>
+  <si>
+    <t>Discussed with Aibel/Hexagon - need to find which rules would apply to ensure correct usage of this new class.</t>
+  </si>
+  <si>
+    <t>Model given OK from Aibel. Need list of component type from Aibel with RDL.</t>
+  </si>
+  <si>
+    <t>Need to add qualifier type to standard ? Discuss with Aibel.</t>
   </si>
 </sst>
 </file>
@@ -739,7 +756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825F216F-6A2C-43F0-976D-4459909E096A}">
-  <dimension ref="B1:I46"/>
+  <dimension ref="B1:I47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="45.42578125" customWidth="1"/>
@@ -775,13 +792,13 @@
     </row>
     <row r="3" spans="2:9" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>1</v>
@@ -822,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="30" x14ac:dyDescent="0.25">
@@ -835,24 +852,24 @@
       <c r="D5" s="13"/>
       <c r="E5" s="10"/>
       <c r="F5" s="10" t="str">
-        <f t="shared" ref="F5:F46" si="0">IF(G5=1,"Complete",IF(G5&lt;&gt;0,"In Progess","Not Started"))</f>
+        <f t="shared" ref="F5:F47" si="0">IF(G5=1,"Complete",IF(G5&lt;&gt;0,"In Progess","Not Started"))</f>
         <v>In Progess</v>
       </c>
       <c r="G5" s="11">
         <v>0.75</v>
       </c>
       <c r="H5" s="12">
-        <f t="shared" ref="H5:H46" si="1">--(G5&gt;=1)</f>
+        <f t="shared" ref="H5:H47" si="1">--(G5&gt;=1)</f>
         <v>0</v>
       </c>
       <c r="I5" s="10"/>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B6" s="10" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10" t="s">
@@ -863,20 +880,22 @@
         <v>In Progess</v>
       </c>
       <c r="G6" s="11">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H6" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I6" s="10"/>
+      <c r="I6" s="10" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="10" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="10"/>
@@ -896,7 +915,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10" t="s">
@@ -918,7 +937,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="10"/>
@@ -938,7 +957,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="10" t="s">
@@ -960,7 +979,7 @@
         <v>13</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
@@ -969,7 +988,7 @@
         <v>In Progess</v>
       </c>
       <c r="G11" s="11">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" si="1"/>
@@ -982,7 +1001,7 @@
         <v>13</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -1002,7 +1021,7 @@
         <v>13</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
@@ -1022,7 +1041,7 @@
         <v>14</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
@@ -1038,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="30" x14ac:dyDescent="0.25">
@@ -1046,7 +1065,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
@@ -1061,14 +1080,16 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I15" s="10"/>
+      <c r="I15" s="10" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10" t="s">
@@ -1092,7 +1113,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="10" t="s">
@@ -1114,7 +1135,7 @@
         <v>15</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="10"/>
@@ -1134,7 +1155,7 @@
         <v>15</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="10" t="s">
@@ -1156,7 +1177,7 @@
         <v>15</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="10"/>
@@ -1176,7 +1197,7 @@
         <v>16</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="10" t="s">
@@ -1198,7 +1219,7 @@
         <v>16</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D22" s="10"/>
       <c r="E22" s="10" t="s">
@@ -1220,7 +1241,7 @@
         <v>16</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D23" s="13"/>
       <c r="E23" s="10"/>
@@ -1240,7 +1261,7 @@
         <v>16</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="10" t="s">
@@ -1262,7 +1283,7 @@
         <v>16</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D25" s="13"/>
       <c r="E25" s="10"/>
@@ -1277,12 +1298,12 @@
       </c>
       <c r="I25" s="10"/>
     </row>
-    <row r="26" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D26" s="10"/>
       <c r="E26" s="10" t="s">
@@ -1293,20 +1314,22 @@
         <v>In Progess</v>
       </c>
       <c r="G26" s="11">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I26" s="10"/>
+      <c r="I26" s="10" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B27" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D27" s="13"/>
       <c r="E27" s="10"/>
@@ -1326,7 +1349,7 @@
         <v>8</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="10" t="s">
@@ -1348,7 +1371,7 @@
         <v>8</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D29" s="13"/>
       <c r="E29" s="10"/>
@@ -1368,7 +1391,7 @@
         <v>17</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="10" t="s">
@@ -1390,7 +1413,7 @@
         <v>17</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D31" s="10"/>
       <c r="E31" s="10" t="s">
@@ -1412,7 +1435,7 @@
         <v>17</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D32" s="13"/>
       <c r="E32" s="10"/>
@@ -1432,7 +1455,7 @@
         <v>17</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D33" s="10"/>
       <c r="E33" s="10" t="s">
@@ -1454,7 +1477,7 @@
         <v>17</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D34" s="13"/>
       <c r="E34" s="10"/>
@@ -1471,10 +1494,10 @@
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D35" s="10"/>
       <c r="E35" s="10" t="s">
@@ -1495,10 +1518,10 @@
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D36" s="10"/>
       <c r="E36" s="10" t="s">
@@ -1517,10 +1540,10 @@
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B37" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D37" s="13"/>
       <c r="E37" s="10"/>
@@ -1535,12 +1558,12 @@
       </c>
       <c r="I37" s="10"/>
     </row>
-    <row r="38" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:9" ht="45" x14ac:dyDescent="0.25">
       <c r="B38" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C38" s="10" t="s">
         <v>36</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>37</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>9</v>
@@ -1553,22 +1576,22 @@
         <v>In Progess</v>
       </c>
       <c r="G38" s="11">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="H38" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D39" s="10"/>
       <c r="E39" s="10" t="s">
@@ -1586,61 +1609,65 @@
         <v>0</v>
       </c>
       <c r="I39" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B40" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F40" s="10" t="str">
+        <f t="shared" ref="F40" si="2">IF(G40=1,"Complete",IF(G40&lt;&gt;0,"In Progess","Not Started"))</f>
+        <v>In Progess</v>
+      </c>
+      <c r="G40" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="H40" s="12">
+        <f t="shared" ref="H40" si="3">--(G40&gt;=1)</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="B41" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D41" s="13"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G41" s="11">
+        <v>0.6</v>
+      </c>
+      <c r="H41" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I41" s="10" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="40" spans="2:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="B40" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D40" s="13"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>In Progess</v>
-      </c>
-      <c r="G40" s="11">
-        <v>0.4</v>
-      </c>
-      <c r="H40" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I40" s="10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Complete</v>
-      </c>
-      <c r="G41" s="11">
-        <v>1</v>
-      </c>
-      <c r="H41" s="12">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="I41" s="10"/>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B42" s="8" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
@@ -1659,76 +1686,76 @@
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" s="8" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D43" s="13"/>
+        <v>44</v>
+      </c>
+      <c r="D43" s="8"/>
       <c r="E43" s="8"/>
       <c r="F43" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>In Progess</v>
-      </c>
-      <c r="G43" s="14">
-        <v>0.7</v>
+        <v>Complete</v>
+      </c>
+      <c r="G43" s="11">
+        <v>1</v>
       </c>
       <c r="H43" s="12">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" s="10"/>
     </row>
-    <row r="44" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B44" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D44" s="13"/>
       <c r="E44" s="8"/>
       <c r="F44" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G44" s="14"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G44" s="14">
+        <v>0.8</v>
+      </c>
       <c r="H44" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I44" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="I44" s="10"/>
+    </row>
+    <row r="45" spans="2:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B45" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D45" s="13"/>
       <c r="E45" s="8"/>
       <c r="F45" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>In Progess</v>
-      </c>
-      <c r="G45" s="14">
-        <v>0.5</v>
-      </c>
+        <v>Not Started</v>
+      </c>
+      <c r="G45" s="14"/>
       <c r="H45" s="12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I45" s="10"/>
+      <c r="I45" s="10" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B46" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D46" s="13"/>
       <c r="E46" s="8"/>
@@ -1745,9 +1772,31 @@
       </c>
       <c r="I46" s="10"/>
     </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B47" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D47" s="13"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="H47" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I47" s="10"/>
+    </row>
   </sheetData>
-  <autoFilter ref="B3:I46" xr:uid="{825F216F-6A2C-43F0-976D-4459909E096A}"/>
-  <conditionalFormatting sqref="G4:G46">
+  <autoFilter ref="B3:I47" xr:uid="{825F216F-6A2C-43F0-976D-4459909E096A}"/>
+  <conditionalFormatting sqref="G4:G47">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -1769,10 +1818,10 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Start Date in this column under this heading" sqref="I3" xr:uid="{B097AD3D-83FE-4DB6-8AA6-82D58880DEE8}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Icon indicator for task completion in this column under this heading is automatically updated as tasks complete" sqref="H3" xr:uid="{E57FD015-A334-4A3D-9540-92E1D8A918A9}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Task in this column under this heading. Use heading filters to find specific entries" sqref="B3:D3" xr:uid="{6FDCA3F5-F6F1-45FB-8AE7-E90C5E60E365}"/>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Select entry from the list. Select CANCEL, then press ALT+DOWN ARROW to navigate the list. Select ENTER to make selection" sqref="E4:E46" xr:uid="{8008394D-C04C-402E-A902-C9B94024D87C}">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Select entry from the list. Select CANCEL, then press ALT+DOWN ARROW to navigate the list. Select ENTER to make selection" sqref="E4:E47" xr:uid="{8008394D-C04C-402E-A902-C9B94024D87C}">
       <formula1>"Low, Normal, High"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Select entry from the list. Select CANCEL, then press ALT+DOWN ARROW to navigate the list. Select ENTER to make selection" sqref="F4:F46" xr:uid="{90892BC2-20A5-4151-9864-7558336C2FE7}">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Select entry from the list. Select CANCEL, then press ALT+DOWN ARROW to navigate the list. Select ENTER to make selection" sqref="F4:F47" xr:uid="{90892BC2-20A5-4151-9864-7558336C2FE7}">
       <formula1>"Not Started, In Progress, Deferred, Complete"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1793,7 +1842,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>G4:G46</xm:sqref>
+          <xm:sqref>G4:G47</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="17" id="{E713B901-0E7B-40B8-A534-1C73C66CF397}">
@@ -1812,7 +1861,7 @@
               <x14:cfIcon iconSet="3Symbols" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>H4:H46</xm:sqref>
+          <xm:sqref>H4:H47</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -1821,6 +1870,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3259FCDE-9EDE-420B-8B6F-D04AEDF9A554}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23963325-1FFB-4B92-8120-662513F10342}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1830,21 +1888,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100C3422A7FFD03AF47B40E3148D61510DD" ma:contentTypeVersion="10" ma:contentTypeDescription="Opprett et nytt dokument." ma:contentTypeScope="" ma:versionID="93a5827b91256c075a5bcdb454d162de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0" xmlns:ns3="b6192152-6ac4-477a-b62a-2f500fcdf3b6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="13127a08f307124b01356346b67d6a81" ns2:_="" ns3:_="">
     <xsd:import namespace="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
@@ -2045,32 +2088,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CED3C9C-630D-4C4B-A736-44AEC9EEC0A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2087,4 +2120,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/ContinuationProject/Status.xlsx
+++ b/ContinuationProject/Status.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\ContinuationProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17228147-18F1-4E29-A4B7-D7FD701E4DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AAB0CF1-AE9E-4102-BFAB-0CECEC1E12D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="4" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId2"/>
-    <sheet name="AdditionalActivities" sheetId="2" state="hidden" r:id="rId3"/>
+    <sheet name="AdditionalActivities" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Status!$B$3:$I$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Status!$B$1:$I$47</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,32 +41,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="56">
   <si>
     <t>DISC DEXPI Continuation Project - Status</t>
   </si>
   <si>
-    <t xml:space="preserve">PRIORITY </t>
-  </si>
-  <si>
-    <t xml:space="preserve">STATUS </t>
-  </si>
-  <si>
-    <t>% COMPLETE</t>
-  </si>
-  <si>
     <t>DONE?</t>
   </si>
   <si>
-    <t>NOTES</t>
-  </si>
-  <si>
-    <t>Normal</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
     <t>ProcessSafetyFunction</t>
   </si>
   <si>
@@ -77,9 +59,6 @@
   </si>
   <si>
     <t>Annotations</t>
-  </si>
-  <si>
-    <t>Low</t>
   </si>
   <si>
     <t>Mount Type</t>
@@ -220,6 +199,21 @@
   </si>
   <si>
     <t>Need to add qualifier type to standard ? Discuss with Aibel.</t>
+  </si>
+  <si>
+    <t>Target Date</t>
+  </si>
+  <si>
+    <t>26.08.2025</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>%Complete</t>
   </si>
 </sst>
 </file>
@@ -355,7 +349,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
@@ -401,6 +395,15 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Date" xfId="6" xr:uid="{2ABB41C5-3CC8-4E1C-85D9-965CF83E22BD}"/>
@@ -408,7 +411,7 @@
     <cellStyle name="Heading 1" xfId="3" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="4" builtinId="17"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
     <cellStyle name="Title" xfId="2" builtinId="15"/>
   </cellStyles>
   <dxfs count="1">
@@ -756,77 +759,80 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825F216F-6A2C-43F0-976D-4459909E096A}">
-  <dimension ref="B1:I47"/>
+  <dimension ref="B1:J47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="1.85546875" customWidth="1"/>
     <col min="2" max="2" width="45.42578125" customWidth="1"/>
     <col min="3" max="3" width="64.42578125" customWidth="1"/>
-    <col min="4" max="4" width="46.85546875" customWidth="1"/>
-    <col min="5" max="5" width="23.7109375" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" customWidth="1"/>
-    <col min="7" max="7" width="38.7109375" customWidth="1"/>
-    <col min="8" max="8" width="5.5703125" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" style="22" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" customWidth="1"/>
+    <col min="7" max="7" width="25.85546875" customWidth="1"/>
+    <col min="8" max="8" width="7" customWidth="1"/>
     <col min="9" max="9" width="49" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="35.25" x14ac:dyDescent="0.5">
+    <row r="1" spans="2:10" ht="35.25" x14ac:dyDescent="0.5">
       <c r="B1" s="17" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="6"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="E1" s="19"/>
       <c r="F1" s="1"/>
       <c r="G1" s="4"/>
       <c r="H1" s="1"/>
       <c r="I1" s="6"/>
     </row>
-    <row r="2" spans="2:9" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="6"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
+      <c r="E2" s="19"/>
       <c r="F2" s="1"/>
       <c r="G2" s="4"/>
       <c r="H2" s="1"/>
       <c r="I2" s="6"/>
     </row>
-    <row r="3" spans="2:9" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" ht="34.5" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="I3" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D4" s="10"/>
-      <c r="E4" s="10" t="s">
-        <v>6</v>
-      </c>
+      <c r="E4" s="21"/>
       <c r="F4" s="10" t="str">
         <f>IF(G4=1,"Complete",IF(G4&lt;&gt;0,"In Progess","Not Started"))</f>
         <v>In Progess</v>
@@ -839,18 +845,21 @@
         <v>0</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="J4" s="23">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B5" s="10" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="10"/>
+        <v>15</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="21"/>
       <c r="F5" s="10" t="str">
         <f t="shared" ref="F5:F47" si="0">IF(G5=1,"Complete",IF(G5&lt;&gt;0,"In Progess","Not Started"))</f>
         <v>In Progess</v>
@@ -863,18 +872,19 @@
         <v>0</v>
       </c>
       <c r="I5" s="10"/>
-    </row>
-    <row r="6" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="J5" s="23">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B6" s="10" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D6" s="10"/>
-      <c r="E6" s="10" t="s">
-        <v>7</v>
-      </c>
+      <c r="E6" s="21"/>
       <c r="F6" s="10" t="str">
         <f t="shared" si="0"/>
         <v>In Progess</v>
@@ -887,18 +897,21 @@
         <v>0</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="J6" s="23">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="10" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="10"/>
+        <v>23</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="21"/>
       <c r="F7" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Not Started</v>
@@ -909,18 +922,17 @@
         <v>0</v>
       </c>
       <c r="I7" s="10"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J7" s="23"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="10" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D8" s="10"/>
-      <c r="E8" s="10" t="s">
-        <v>7</v>
-      </c>
+      <c r="E8" s="21"/>
       <c r="F8" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Not Started</v>
@@ -931,16 +943,17 @@
         <v>0</v>
       </c>
       <c r="I8" s="10"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J8" s="23"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="10"/>
+        <v>25</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="21"/>
       <c r="F9" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Not Started</v>
@@ -951,18 +964,17 @@
         <v>0</v>
       </c>
       <c r="I9" s="10"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J9" s="23"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="10" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D10" s="10"/>
-      <c r="E10" s="10" t="s">
-        <v>12</v>
-      </c>
+      <c r="E10" s="21"/>
       <c r="F10" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Not Started</v>
@@ -973,16 +985,17 @@
         <v>0</v>
       </c>
       <c r="I10" s="10"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J10" s="23"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="10" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
+      <c r="E11" s="21"/>
       <c r="F11" s="10" t="str">
         <f t="shared" si="0"/>
         <v>In Progess</v>
@@ -995,16 +1008,19 @@
         <v>0</v>
       </c>
       <c r="I11" s="10"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J11" s="23">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
+      <c r="E12" s="21"/>
       <c r="F12" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Not Started</v>
@@ -1015,16 +1031,17 @@
         <v>0</v>
       </c>
       <c r="I12" s="10"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J12" s="23"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
+      <c r="E13" s="21"/>
       <c r="F13" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Not Started</v>
@@ -1035,16 +1052,17 @@
         <v>0</v>
       </c>
       <c r="I13" s="10"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J13" s="23"/>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
+      <c r="E14" s="21"/>
       <c r="F14" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Complete</v>
@@ -1057,18 +1075,21 @@
         <v>1</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="J14" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
+      <c r="E15" s="21"/>
       <c r="F15" s="10" t="str">
         <f t="shared" si="0"/>
         <v>In Progess</v>
@@ -1081,20 +1102,21 @@
         <v>0</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="J15" s="23">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D16" s="10"/>
-      <c r="E16" s="10" t="s">
-        <v>7</v>
-      </c>
+      <c r="E16" s="21"/>
       <c r="F16" s="10" t="str">
         <f t="shared" si="0"/>
         <v>In Progess</v>
@@ -1106,19 +1128,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I16" s="10"/>
-    </row>
-    <row r="17" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J16" s="23">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D17" s="10"/>
-      <c r="E17" s="10" t="s">
-        <v>7</v>
-      </c>
+      <c r="E17" s="21"/>
       <c r="F17" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Not Started</v>
@@ -1128,17 +1150,17 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I17" s="10"/>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J17" s="23"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="13"/>
-      <c r="E18" s="10"/>
+        <v>23</v>
+      </c>
+      <c r="D18" s="10"/>
+      <c r="E18" s="21"/>
       <c r="F18" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Not Started</v>
@@ -1148,19 +1170,17 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I18" s="10"/>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J18" s="23"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D19" s="10"/>
-      <c r="E19" s="10" t="s">
-        <v>7</v>
-      </c>
+      <c r="E19" s="21"/>
       <c r="F19" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Not Started</v>
@@ -1170,17 +1190,17 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I19" s="10"/>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J19" s="23"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" s="13"/>
-      <c r="E20" s="10"/>
+        <v>25</v>
+      </c>
+      <c r="D20" s="10"/>
+      <c r="E20" s="21"/>
       <c r="F20" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Not Started</v>
@@ -1190,19 +1210,17 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I20" s="10"/>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J20" s="23"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D21" s="10"/>
-      <c r="E21" s="10" t="s">
-        <v>7</v>
-      </c>
+      <c r="E21" s="21"/>
       <c r="F21" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Not Started</v>
@@ -1212,19 +1230,17 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I21" s="10"/>
-    </row>
-    <row r="22" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J21" s="23"/>
+    </row>
+    <row r="22" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D22" s="10"/>
-      <c r="E22" s="10" t="s">
-        <v>7</v>
-      </c>
+      <c r="E22" s="21"/>
       <c r="F22" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Not Started</v>
@@ -1234,17 +1250,17 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I22" s="10"/>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J22" s="23"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="10" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="13"/>
-      <c r="E23" s="10"/>
+        <v>23</v>
+      </c>
+      <c r="D23" s="10"/>
+      <c r="E23" s="21"/>
       <c r="F23" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Not Started</v>
@@ -1254,19 +1270,17 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I23" s="10"/>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J23" s="23"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="10" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D24" s="10"/>
-      <c r="E24" s="10" t="s">
-        <v>7</v>
-      </c>
+      <c r="E24" s="21"/>
       <c r="F24" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Not Started</v>
@@ -1276,17 +1290,17 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I24" s="10"/>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J24" s="23"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="10" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" s="13"/>
-      <c r="E25" s="10"/>
+        <v>25</v>
+      </c>
+      <c r="D25" s="10"/>
+      <c r="E25" s="21"/>
       <c r="F25" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Not Started</v>
@@ -1296,19 +1310,17 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I25" s="10"/>
-    </row>
-    <row r="26" spans="2:9" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J25" s="23"/>
+    </row>
+    <row r="26" spans="2:10" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="10" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D26" s="10"/>
-      <c r="E26" s="10" t="s">
-        <v>7</v>
-      </c>
+      <c r="E26" s="21"/>
       <c r="F26" s="10" t="str">
         <f t="shared" si="0"/>
         <v>In Progess</v>
@@ -1321,18 +1333,21 @@
         <v>0</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+      <c r="J26" s="23">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="10" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D27" s="13"/>
-      <c r="E27" s="10"/>
+      <c r="E27" s="21"/>
       <c r="F27" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Not Started</v>
@@ -1343,18 +1358,17 @@
         <v>0</v>
       </c>
       <c r="I27" s="10"/>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J27" s="23"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="10" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D28" s="10"/>
-      <c r="E28" s="10" t="s">
-        <v>7</v>
-      </c>
+      <c r="E28" s="21"/>
       <c r="F28" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Not Started</v>
@@ -1365,16 +1379,17 @@
         <v>0</v>
       </c>
       <c r="I28" s="10"/>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J28" s="23"/>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="10" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D29" s="13"/>
-      <c r="E29" s="10"/>
+      <c r="E29" s="21"/>
       <c r="F29" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Not Started</v>
@@ -1385,18 +1400,17 @@
         <v>0</v>
       </c>
       <c r="I29" s="10"/>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J29" s="23"/>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="10" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D30" s="10"/>
-      <c r="E30" s="10" t="s">
-        <v>7</v>
-      </c>
+      <c r="E30" s="21"/>
       <c r="F30" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Not Started</v>
@@ -1407,18 +1421,17 @@
         <v>0</v>
       </c>
       <c r="I30" s="10"/>
-    </row>
-    <row r="31" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J30" s="23"/>
+    </row>
+    <row r="31" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="10" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D31" s="10"/>
-      <c r="E31" s="10" t="s">
-        <v>7</v>
-      </c>
+      <c r="E31" s="21"/>
       <c r="F31" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Not Started</v>
@@ -1429,16 +1442,17 @@
         <v>0</v>
       </c>
       <c r="I31" s="10"/>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J31" s="23"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="10" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D32" s="13"/>
-      <c r="E32" s="10"/>
+      <c r="E32" s="21"/>
       <c r="F32" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Not Started</v>
@@ -1449,18 +1463,17 @@
         <v>0</v>
       </c>
       <c r="I32" s="10"/>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J32" s="23"/>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="10" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D33" s="10"/>
-      <c r="E33" s="10" t="s">
-        <v>7</v>
-      </c>
+      <c r="E33" s="21"/>
       <c r="F33" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Not Started</v>
@@ -1471,16 +1484,17 @@
         <v>0</v>
       </c>
       <c r="I33" s="10"/>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J33" s="23"/>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="10" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D34" s="13"/>
-      <c r="E34" s="10"/>
+      <c r="E34" s="21"/>
       <c r="F34" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Not Started</v>
@@ -1491,18 +1505,17 @@
         <v>0</v>
       </c>
       <c r="I34" s="10"/>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J34" s="23"/>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="10" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D35" s="10"/>
-      <c r="E35" s="10" t="s">
-        <v>7</v>
-      </c>
+      <c r="E35" s="21"/>
       <c r="F35" s="10" t="str">
         <f t="shared" si="0"/>
         <v>In Progess</v>
@@ -1515,18 +1528,19 @@
         <v>0</v>
       </c>
       <c r="I35" s="10"/>
-    </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J35" s="23">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="10" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D36" s="10"/>
-      <c r="E36" s="10" t="s">
-        <v>7</v>
-      </c>
+      <c r="E36" s="21"/>
       <c r="F36" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Not Started</v>
@@ -1537,16 +1551,17 @@
         <v>0</v>
       </c>
       <c r="I36" s="10"/>
-    </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J36" s="23"/>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="10" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D37" s="13"/>
-      <c r="E37" s="10"/>
+      <c r="E37" s="21"/>
       <c r="F37" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Not Started</v>
@@ -1557,20 +1572,19 @@
         <v>0</v>
       </c>
       <c r="I37" s="10"/>
-    </row>
-    <row r="38" spans="2:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="J37" s="23"/>
+    </row>
+    <row r="38" spans="2:10" ht="45" x14ac:dyDescent="0.25">
       <c r="B38" s="10" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>6</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E38" s="21"/>
       <c r="F38" s="10" t="str">
         <f t="shared" si="0"/>
         <v>In Progess</v>
@@ -1583,20 +1597,21 @@
         <v>0</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="J38" s="23">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="10" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D39" s="10"/>
-      <c r="E39" s="10" t="s">
-        <v>6</v>
-      </c>
+      <c r="E39" s="21"/>
       <c r="F39" s="10" t="str">
         <f t="shared" si="0"/>
         <v>In Progess</v>
@@ -1609,20 +1624,21 @@
         <v>0</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="J39" s="23">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="10" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D40" s="10"/>
-      <c r="E40" s="10" t="s">
-        <v>6</v>
-      </c>
+      <c r="E40" s="21"/>
       <c r="F40" s="10" t="str">
         <f t="shared" ref="F40" si="2">IF(G40=1,"Complete",IF(G40&lt;&gt;0,"In Progess","Not Started"))</f>
         <v>In Progess</v>
@@ -1635,18 +1651,21 @@
         <v>0</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="41" spans="2:9" ht="75" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="J40" s="23">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" ht="75" x14ac:dyDescent="0.25">
       <c r="B41" s="10" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D41" s="13"/>
-      <c r="E41" s="10"/>
+      <c r="E41" s="21"/>
       <c r="F41" s="10" t="str">
         <f t="shared" si="0"/>
         <v>In Progess</v>
@@ -1659,18 +1678,21 @@
         <v>0</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="J41" s="23">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="8" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
+      <c r="E42" s="21"/>
       <c r="F42" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Complete</v>
@@ -1683,16 +1705,19 @@
         <v>1</v>
       </c>
       <c r="I42" s="10"/>
-    </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J42" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="8" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
+      <c r="E43" s="21"/>
       <c r="F43" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Complete</v>
@@ -1705,16 +1730,19 @@
         <v>1</v>
       </c>
       <c r="I43" s="10"/>
-    </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J43" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="8" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D44" s="13"/>
-      <c r="E44" s="8"/>
+      <c r="E44" s="21"/>
       <c r="F44" s="10" t="str">
         <f t="shared" si="0"/>
         <v>In Progess</v>
@@ -1727,16 +1755,19 @@
         <v>0</v>
       </c>
       <c r="I44" s="10"/>
-    </row>
-    <row r="45" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="J44" s="23">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B45" s="8" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D45" s="13"/>
-      <c r="E45" s="8"/>
+      <c r="E45" s="21"/>
       <c r="F45" s="10" t="str">
         <f t="shared" si="0"/>
         <v>Not Started</v>
@@ -1747,18 +1778,19 @@
         <v>0</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="J45" s="23"/>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="8" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D46" s="13"/>
-      <c r="E46" s="8"/>
+      <c r="E46" s="21"/>
       <c r="F46" s="10" t="str">
         <f t="shared" si="0"/>
         <v>In Progess</v>
@@ -1771,16 +1803,19 @@
         <v>0</v>
       </c>
       <c r="I46" s="10"/>
-    </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J46" s="23">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="8" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D47" s="13"/>
-      <c r="E47" s="8"/>
+      <c r="E47" s="21"/>
       <c r="F47" s="10" t="str">
         <f t="shared" si="0"/>
         <v>In Progess</v>
@@ -1793,6 +1828,9 @@
         <v>0</v>
       </c>
       <c r="I47" s="10"/>
+      <c r="J47" s="23">
+        <v>0.5</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="B3:I47" xr:uid="{825F216F-6A2C-43F0-976D-4459909E096A}"/>
@@ -1810,22 +1848,20 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="9">
+  <dataValidations count="8">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select % Complete in this column. Press ALT+DOWN ARROW to open the drop-down list, then ENTER to make selection. A status bar indicates progress toward completion" sqref="G3" xr:uid="{151F9C2E-C41F-40E3-927F-E5E520954D3E}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Worksheet title is in this cell" sqref="D1:D2 B1" xr:uid="{CF4F781A-1C6C-43E6-9F83-4F93D6CA6007}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select Priority in this column under this heading. Press ALT+DOWN ARROW to open the drop-down list, then ENTER to make selection" sqref="E3" xr:uid="{95C292DB-FCE2-44BC-8E59-4B8265833898}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Select Status in this column under this heading.  Press ALT+DOWN ARROW to open the drop-down list, then ENTER to make selection" sqref="F3" xr:uid="{EC11B83B-A91F-4C11-ADB1-45F408735AAF}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Start Date in this column under this heading" sqref="I3" xr:uid="{B097AD3D-83FE-4DB6-8AA6-82D58880DEE8}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Start Date in this column under this heading" sqref="J3" xr:uid="{B097AD3D-83FE-4DB6-8AA6-82D58880DEE8}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Icon indicator for task completion in this column under this heading is automatically updated as tasks complete" sqref="H3" xr:uid="{E57FD015-A334-4A3D-9540-92E1D8A918A9}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Task in this column under this heading. Use heading filters to find specific entries" sqref="B3:D3" xr:uid="{6FDCA3F5-F6F1-45FB-8AE7-E90C5E60E365}"/>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Select entry from the list. Select CANCEL, then press ALT+DOWN ARROW to navigate the list. Select ENTER to make selection" sqref="E4:E47" xr:uid="{8008394D-C04C-402E-A902-C9B94024D87C}">
-      <formula1>"Low, Normal, High"</formula1>
-    </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Select entry from the list. Select CANCEL, then press ALT+DOWN ARROW to navigate the list. Select ENTER to make selection" sqref="F4:F47" xr:uid="{90892BC2-20A5-4151-9864-7558336C2FE7}">
       <formula1>"Not Started, In Progress, Deferred, Complete"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -1870,15 +1906,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3259FCDE-9EDE-420B-8B6F-D04AEDF9A554}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23963325-1FFB-4B92-8120-662513F10342}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1888,6 +1915,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100C3422A7FFD03AF47B40E3148D61510DD" ma:contentTypeVersion="10" ma:contentTypeDescription="Opprett et nytt dokument." ma:contentTypeScope="" ma:versionID="93a5827b91256c075a5bcdb454d162de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0" xmlns:ns3="b6192152-6ac4-477a-b62a-2f500fcdf3b6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="13127a08f307124b01356346b67d6a81" ns2:_="" ns3:_="">
     <xsd:import namespace="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
@@ -2088,15 +2124,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -2104,6 +2131,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CED3C9C-630D-4C4B-A736-44AEC9EEC0A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2118,14 +2153,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/ContinuationProject/Status.xlsx
+++ b/ContinuationProject/Status.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\ContinuationProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AAB0CF1-AE9E-4102-BFAB-0CECEC1E12D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28785714-6456-4304-99E5-823692D43FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="4" r:id="rId1"/>
     <sheet name="AdditionalActivities" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Status!$B$3:$I$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Status!$B$3:$BG$47</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Status!$B$1:$I$47</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="57">
   <si>
     <t>DISC DEXPI Continuation Project - Status</t>
   </si>
@@ -52,9 +52,6 @@
     <t>ProcessSafetyFunction</t>
   </si>
   <si>
-    <t>Fix size attribute-to-geometry consistency</t>
-  </si>
-  <si>
     <t>Vessel/Tank Internal Components</t>
   </si>
   <si>
@@ -128,9 +125,6 @@
   </si>
   <si>
     <t>Prepare Symbols for Profile</t>
-  </si>
-  <si>
-    <t>Ensure each symbol is defined in a machine-readable format with correct</t>
   </si>
   <si>
     <t>Include DEXPI 2.0 updates</t>
@@ -182,38 +176,48 @@
     <t>Fixed in DEXPI 2.0</t>
   </si>
   <si>
+    <t>Label addition to profile</t>
+  </si>
+  <si>
+    <t>Text rotation, Label position, Link to attributes</t>
+  </si>
+  <si>
+    <t>Discussed with Aibel/Hexagon - need to find which rules would apply to ensure correct usage of this new class.</t>
+  </si>
+  <si>
+    <t>Model given OK from Aibel. Need list of component type from Aibel with RDL.</t>
+  </si>
+  <si>
+    <t>Need to add qualifier type to standard ? Discuss with Aibel.</t>
+  </si>
+  <si>
+    <t>Target Date</t>
+  </si>
+  <si>
+    <t>26.08.2025</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>%Complete</t>
+  </si>
+  <si>
     <t>Only those symbols in the correct format will be made available in the profile.
-Challenge with dash lines/hash</t>
-  </si>
-  <si>
-    <t>Label addition to profile</t>
-  </si>
-  <si>
-    <t>Text rotation, Label position, Link to attributes</t>
-  </si>
-  <si>
-    <t>Discussed with Aibel/Hexagon - need to find which rules would apply to ensure correct usage of this new class.</t>
-  </si>
-  <si>
-    <t>Model given OK from Aibel. Need list of component type from Aibel with RDL.</t>
-  </si>
-  <si>
-    <t>Need to add qualifier type to standard ? Discuss with Aibel.</t>
-  </si>
-  <si>
-    <t>Target Date</t>
-  </si>
-  <si>
-    <t>26.08.2025</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>%Complete</t>
+Challenge with dash lines/hash
+Connection points to check and correct.</t>
+  </si>
+  <si>
+    <t>Ensure each symbol is defined in a machine-readable format with correct sizing definitions, connection point definitions.</t>
+  </si>
+  <si>
+    <t>Complete</t>
+  </si>
+  <si>
+    <t>08.09.2025</t>
   </si>
 </sst>
 </file>
@@ -223,7 +227,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;Done&quot;;&quot;&quot;;&quot;&quot;"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,12 +286,6 @@
       <color theme="3"/>
       <name val="Bookman Old Style"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -365,9 +363,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -394,7 +389,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -403,7 +397,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Date" xfId="6" xr:uid="{2ABB41C5-3CC8-4E1C-85D9-965CF83E22BD}"/>
@@ -411,7 +409,7 @@
     <cellStyle name="Heading 1" xfId="3" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="4" builtinId="17"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
     <cellStyle name="Title" xfId="2" builtinId="15"/>
   </cellStyles>
   <dxfs count="1">
@@ -759,1081 +757,1278 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825F216F-6A2C-43F0-976D-4459909E096A}">
-  <dimension ref="B1:J47"/>
+  <dimension ref="B1:BG47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.85546875" customWidth="1"/>
     <col min="2" max="2" width="45.42578125" customWidth="1"/>
     <col min="3" max="3" width="64.42578125" customWidth="1"/>
     <col min="4" max="4" width="22.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" style="22" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" style="20" customWidth="1"/>
     <col min="6" max="6" width="14.42578125" customWidth="1"/>
     <col min="7" max="7" width="25.85546875" customWidth="1"/>
     <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="49" customWidth="1"/>
-    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="9" max="9" width="25.140625" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" style="22" customWidth="1"/>
+    <col min="11" max="11" width="16.85546875" style="22" customWidth="1"/>
+    <col min="12" max="36" width="9.140625" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="35.25" x14ac:dyDescent="0.5">
-      <c r="B1" s="17" t="s">
+    <row r="1" spans="2:59" ht="35.25" x14ac:dyDescent="0.5">
+      <c r="B1" s="16" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="6"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="19"/>
+      <c r="E1" s="17"/>
       <c r="F1" s="1"/>
       <c r="G1" s="4"/>
       <c r="H1" s="1"/>
       <c r="I1" s="6"/>
     </row>
-    <row r="2" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:59" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="6"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="19"/>
+      <c r="E2" s="17"/>
       <c r="F2" s="1"/>
       <c r="G2" s="4"/>
       <c r="H2" s="1"/>
       <c r="I2" s="6"/>
     </row>
-    <row r="3" spans="2:10" ht="34.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:59" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="9" t="s">
         <v>20</v>
       </c>
+      <c r="C3" s="8" t="s">
+        <v>19</v>
+      </c>
       <c r="D3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="G3" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="2:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B4" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20"/>
+      <c r="R3" s="20"/>
+      <c r="S3" s="20"/>
+      <c r="T3" s="20"/>
+      <c r="U3" s="20"/>
+      <c r="V3" s="20"/>
+      <c r="W3" s="20"/>
+      <c r="X3" s="20"/>
+      <c r="Y3" s="20"/>
+      <c r="Z3" s="20"/>
+      <c r="AA3" s="20"/>
+      <c r="AB3" s="20"/>
+      <c r="AC3" s="20"/>
+      <c r="AD3" s="20"/>
+      <c r="AE3" s="20"/>
+      <c r="AF3" s="20"/>
+      <c r="AG3" s="20"/>
+      <c r="AH3" s="20"/>
+      <c r="AI3" s="20"/>
+      <c r="AJ3" s="20"/>
+      <c r="AK3" s="20"/>
+      <c r="AL3" s="20"/>
+      <c r="AM3" s="20"/>
+      <c r="AN3" s="20"/>
+      <c r="AO3" s="20"/>
+      <c r="AP3" s="20"/>
+      <c r="AQ3" s="20"/>
+      <c r="AR3" s="20"/>
+      <c r="AS3" s="20"/>
+      <c r="AT3" s="20"/>
+      <c r="AU3" s="20"/>
+      <c r="AV3" s="20"/>
+      <c r="AW3" s="20"/>
+      <c r="AX3" s="20"/>
+      <c r="AY3" s="20"/>
+      <c r="AZ3" s="20"/>
+      <c r="BA3" s="20"/>
+      <c r="BB3" s="20"/>
+      <c r="BC3" s="20"/>
+      <c r="BD3" s="20"/>
+      <c r="BE3" s="20"/>
+      <c r="BF3" s="20"/>
+      <c r="BG3" s="20"/>
+    </row>
+    <row r="4" spans="2:59" ht="30" x14ac:dyDescent="0.25">
+      <c r="B4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="10" t="str">
+      <c r="D4" s="9"/>
+      <c r="E4" s="19">
+        <v>46010</v>
+      </c>
+      <c r="F4" s="9" t="str">
         <f>IF(G4=1,"Complete",IF(G4&lt;&gt;0,"In Progess","Not Started"))</f>
         <v>In Progess</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="10">
         <v>0.3</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="11">
         <f>--(G4&gt;=1)</f>
         <v>0</v>
       </c>
-      <c r="I4" s="10" t="s">
-        <v>16</v>
+      <c r="I4" s="9" t="s">
+        <v>15</v>
       </c>
       <c r="J4" s="23">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="5" spans="2:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B5" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="10" t="str">
+      <c r="K4" s="22">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="5" spans="2:59" ht="30" x14ac:dyDescent="0.25">
+      <c r="B5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="9"/>
+      <c r="E5" s="19">
+        <v>46010</v>
+      </c>
+      <c r="F5" s="9" t="str">
         <f t="shared" ref="F5:F47" si="0">IF(G5=1,"Complete",IF(G5&lt;&gt;0,"In Progess","Not Started"))</f>
         <v>In Progess</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="10">
         <v>0.75</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="11">
         <f t="shared" ref="H5:H47" si="1">--(G5&gt;=1)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="10"/>
+      <c r="I5" s="9"/>
       <c r="J5" s="23">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="6" spans="2:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B6" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="10" t="str">
+      <c r="K5" s="22">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="6" spans="2:59" ht="30" x14ac:dyDescent="0.25">
+      <c r="B6" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="9"/>
+      <c r="E6" s="19">
+        <v>45917</v>
+      </c>
+      <c r="F6" s="9" t="str">
         <f t="shared" si="0"/>
         <v>In Progess</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="10">
         <v>0.9</v>
       </c>
-      <c r="H6" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>49</v>
+      <c r="H6" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>46</v>
       </c>
       <c r="J6" s="23">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B7" s="10" t="s">
+      <c r="K6" s="22">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="7" spans="2:59" x14ac:dyDescent="0.25">
+      <c r="B7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="19">
+        <v>45925</v>
+      </c>
+      <c r="F7" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G7" s="10"/>
+      <c r="H7" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I7" s="9"/>
+      <c r="J7" s="23"/>
+    </row>
+    <row r="8" spans="2:59" x14ac:dyDescent="0.25">
+      <c r="B8" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="19">
+        <v>45931</v>
+      </c>
+      <c r="F8" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G8" s="10"/>
+      <c r="H8" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="9"/>
+      <c r="J8" s="23"/>
+    </row>
+    <row r="9" spans="2:59" x14ac:dyDescent="0.25">
+      <c r="B9" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="9"/>
+      <c r="E9" s="19">
+        <v>45870</v>
+      </c>
+      <c r="F9" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G9" s="10"/>
+      <c r="H9" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="9"/>
+      <c r="J9" s="23"/>
+    </row>
+    <row r="10" spans="2:59" x14ac:dyDescent="0.25">
+      <c r="B10" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G7" s="11"/>
-      <c r="H7" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I7" s="10"/>
-      <c r="J7" s="23"/>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="16" t="s">
+      <c r="C10" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G8" s="11"/>
-      <c r="H8" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="23"/>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B9" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="23"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B10" s="10" t="s">
+      <c r="D10" s="9"/>
+      <c r="E10" s="19">
+        <v>45909</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" s="10">
+        <v>1</v>
+      </c>
+      <c r="H10" s="11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I10" s="9"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:59" x14ac:dyDescent="0.25">
+      <c r="B11" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G10" s="11"/>
-      <c r="H10" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="23"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="10" t="str">
+      <c r="C11" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="9"/>
+      <c r="E11" s="19">
+        <v>45917</v>
+      </c>
+      <c r="F11" s="9" t="str">
         <f t="shared" si="0"/>
         <v>In Progess</v>
       </c>
-      <c r="G11" s="11">
-        <v>0.6</v>
-      </c>
-      <c r="H11" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I11" s="10"/>
+      <c r="G11" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="H11" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="9"/>
       <c r="J11" s="23">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B12" s="10" t="s">
+      <c r="K11" s="22">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="12" spans="2:59" x14ac:dyDescent="0.25">
+      <c r="B12" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="19">
+        <v>45924</v>
+      </c>
+      <c r="F12" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G12" s="10"/>
+      <c r="H12" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="9"/>
+      <c r="J12" s="23"/>
+    </row>
+    <row r="13" spans="2:59" x14ac:dyDescent="0.25">
+      <c r="B13" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="E13" s="19">
+        <v>45931</v>
+      </c>
+      <c r="F13" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G13" s="10"/>
+      <c r="H13" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="9"/>
+      <c r="J13" s="23"/>
+    </row>
+    <row r="14" spans="2:59" x14ac:dyDescent="0.25">
+      <c r="B14" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G12" s="11"/>
-      <c r="H12" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="10"/>
-      <c r="J12" s="23"/>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B13" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G13" s="11"/>
-      <c r="H13" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I13" s="10"/>
-      <c r="J13" s="23"/>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B14" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="10"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="10" t="str">
+      <c r="C14" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="E14" s="19">
+        <v>45888</v>
+      </c>
+      <c r="F14" s="9" t="str">
         <f t="shared" si="0"/>
         <v>Complete</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="10">
         <v>1</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="11">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="I14" s="10" t="s">
-        <v>44</v>
+      <c r="I14" s="9" t="s">
+        <v>42</v>
       </c>
       <c r="J14" s="23">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="2:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B15" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="10" t="str">
+      <c r="K14" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:59" ht="30" x14ac:dyDescent="0.25">
+      <c r="B15" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="9"/>
+      <c r="E15" s="19">
+        <v>45919</v>
+      </c>
+      <c r="F15" s="9" t="str">
         <f t="shared" si="0"/>
         <v>In Progess</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="10">
         <v>0.7</v>
       </c>
-      <c r="H15" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>50</v>
+      <c r="H15" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>47</v>
       </c>
       <c r="J15" s="23">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B16" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="10" t="str">
+      <c r="K15" s="22">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:59" x14ac:dyDescent="0.25">
+      <c r="B16" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="9"/>
+      <c r="E16" s="19">
+        <v>45966</v>
+      </c>
+      <c r="F16" s="9" t="str">
         <f t="shared" si="0"/>
         <v>In Progess</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="10">
         <v>0.2</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J16" s="23">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="17" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="10" t="s">
+      <c r="K16" s="22">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="9"/>
+      <c r="E17" s="19">
+        <v>45982</v>
+      </c>
+      <c r="F17" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G17" s="10"/>
+      <c r="H17" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="23"/>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="9"/>
+      <c r="E18" s="19">
+        <v>45989</v>
+      </c>
+      <c r="F18" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G18" s="10"/>
+      <c r="H18" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="23"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B19" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="9"/>
+      <c r="E19" s="19">
+        <v>45996</v>
+      </c>
+      <c r="F19" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G19" s="10"/>
+      <c r="H19" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="23"/>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B20" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="9"/>
+      <c r="E20" s="19">
+        <v>46003</v>
+      </c>
+      <c r="F20" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G20" s="10"/>
+      <c r="H20" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="23"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B21" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C21" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="9"/>
+      <c r="E21" s="19">
+        <v>45912</v>
+      </c>
+      <c r="F21" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G21" s="10"/>
+      <c r="H21" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="23"/>
+    </row>
+    <row r="22" spans="2:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="9"/>
+      <c r="E22" s="19">
+        <v>45919</v>
+      </c>
+      <c r="F22" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G22" s="10"/>
+      <c r="H22" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="23"/>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B23" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G17" s="11"/>
-      <c r="H17" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="23"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B18" s="10" t="s">
+      <c r="D23" s="9"/>
+      <c r="E23" s="19">
+        <v>45922</v>
+      </c>
+      <c r="F23" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G23" s="10"/>
+      <c r="H23" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="23"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B24" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C24" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D18" s="10"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G18" s="11"/>
-      <c r="H18" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J18" s="23"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B19" s="10" t="s">
+      <c r="D24" s="9"/>
+      <c r="E24" s="19">
+        <v>45929</v>
+      </c>
+      <c r="F24" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G24" s="10"/>
+      <c r="H24" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="23"/>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B25" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C25" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D19" s="10"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G19" s="11"/>
-      <c r="H19" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="23"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B20" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G20" s="11"/>
-      <c r="H20" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="23"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B21" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G21" s="11"/>
-      <c r="H21" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J21" s="23"/>
-    </row>
-    <row r="22" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="10"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G22" s="11"/>
-      <c r="H22" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J22" s="23"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G23" s="11"/>
-      <c r="H23" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J23" s="23"/>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B24" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24" s="10"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G24" s="11"/>
-      <c r="H24" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J24" s="23"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B25" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" s="10"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G25" s="11"/>
-      <c r="H25" s="12">
+      <c r="D25" s="9"/>
+      <c r="E25" s="19">
+        <v>45936</v>
+      </c>
+      <c r="F25" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G25" s="10"/>
+      <c r="H25" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J25" s="23"/>
     </row>
-    <row r="26" spans="2:10" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="10" t="s">
+    <row r="26" spans="2:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" s="10"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="10" t="str">
+      <c r="C26" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" s="9"/>
+      <c r="E26" s="19">
+        <v>45912</v>
+      </c>
+      <c r="F26" s="9" t="str">
         <f t="shared" si="0"/>
         <v>In Progess</v>
       </c>
-      <c r="G26" s="11">
-        <v>0.7</v>
-      </c>
-      <c r="H26" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I26" s="10" t="s">
-        <v>48</v>
+      <c r="G26" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="H26" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>45</v>
       </c>
       <c r="J26" s="23">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="10" t="s">
+      <c r="K26" s="22">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B27" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" s="12"/>
+      <c r="E27" s="19">
+        <v>45919</v>
+      </c>
+      <c r="F27" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G27" s="10"/>
+      <c r="H27" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I27" s="9"/>
+      <c r="J27" s="23"/>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B28" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D27" s="13"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G27" s="11"/>
-      <c r="H27" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I27" s="10"/>
-      <c r="J27" s="23"/>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B28" s="10" t="s">
+      <c r="D28" s="9"/>
+      <c r="E28" s="19">
+        <v>45922</v>
+      </c>
+      <c r="F28" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G28" s="10"/>
+      <c r="H28" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="9"/>
+      <c r="J28" s="23"/>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B29" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C29" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="10"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G28" s="11"/>
-      <c r="H28" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I28" s="10"/>
-      <c r="J28" s="23"/>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B29" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D29" s="13"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G29" s="11"/>
-      <c r="H29" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I29" s="10"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="19">
+        <v>45929</v>
+      </c>
+      <c r="F29" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G29" s="10"/>
+      <c r="H29" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I29" s="9"/>
       <c r="J29" s="23"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B30" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D30" s="10"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G30" s="11"/>
-      <c r="H30" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I30" s="10"/>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B30" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30" s="9"/>
+      <c r="E30" s="19">
+        <v>45926</v>
+      </c>
+      <c r="F30" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G30" s="10"/>
+      <c r="H30" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I30" s="9"/>
       <c r="J30" s="23"/>
     </row>
-    <row r="31" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="15" t="s">
+    <row r="31" spans="2:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="9"/>
+      <c r="E31" s="19">
+        <v>45931</v>
+      </c>
+      <c r="F31" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G31" s="10"/>
+      <c r="H31" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I31" s="9"/>
+      <c r="J31" s="23"/>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B32" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D31" s="10"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G31" s="11"/>
-      <c r="H31" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I31" s="10"/>
-      <c r="J31" s="23"/>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B32" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="16" t="s">
+      <c r="D32" s="12"/>
+      <c r="E32" s="19">
+        <v>45938</v>
+      </c>
+      <c r="F32" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G32" s="10"/>
+      <c r="H32" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I32" s="9"/>
+      <c r="J32" s="23"/>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B33" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D32" s="13"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G32" s="11"/>
-      <c r="H32" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I32" s="10"/>
-      <c r="J32" s="23"/>
-    </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B33" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="16" t="s">
+      <c r="D33" s="9"/>
+      <c r="E33" s="19">
+        <v>45945</v>
+      </c>
+      <c r="F33" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G33" s="10"/>
+      <c r="H33" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I33" s="9"/>
+      <c r="J33" s="23"/>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B34" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D33" s="10"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G33" s="11"/>
-      <c r="H33" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I33" s="10"/>
-      <c r="J33" s="23"/>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B34" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D34" s="13"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G34" s="11"/>
-      <c r="H34" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I34" s="10"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="19">
+        <v>45952</v>
+      </c>
+      <c r="F34" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G34" s="10"/>
+      <c r="H34" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I34" s="9"/>
       <c r="J34" s="23"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B35" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D35" s="10"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="10" t="str">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B35" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" s="9"/>
+      <c r="E35" s="19">
+        <v>45919</v>
+      </c>
+      <c r="F35" s="9" t="str">
         <f t="shared" si="0"/>
         <v>In Progess</v>
       </c>
-      <c r="G35" s="11">
+      <c r="G35" s="10">
         <v>0.9</v>
       </c>
-      <c r="H35" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I35" s="10"/>
+      <c r="H35" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I35" s="9"/>
       <c r="J35" s="23">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B36" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C36" s="16" t="s">
+      <c r="K35" s="22">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B36" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" s="9"/>
+      <c r="E36" s="19">
+        <v>45938</v>
+      </c>
+      <c r="F36" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G36" s="10"/>
+      <c r="H36" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I36" s="9"/>
+      <c r="J36" s="23"/>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B37" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D36" s="10"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G36" s="11"/>
-      <c r="H36" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I36" s="10"/>
-      <c r="J36" s="23"/>
-    </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B37" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D37" s="13"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G37" s="11"/>
-      <c r="H37" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I37" s="10"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="19">
+        <v>45945</v>
+      </c>
+      <c r="F37" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G37" s="10"/>
+      <c r="H37" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I37" s="9"/>
       <c r="J37" s="23"/>
     </row>
-    <row r="38" spans="2:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="B38" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E38" s="21"/>
-      <c r="F38" s="10" t="str">
+    <row r="38" spans="2:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="B38" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D38" s="9"/>
+      <c r="E38" s="19">
+        <v>45910</v>
+      </c>
+      <c r="F38" s="9" t="str">
         <f t="shared" si="0"/>
         <v>In Progess</v>
       </c>
-      <c r="G38" s="11">
-        <v>0.85</v>
-      </c>
-      <c r="H38" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I38" s="10" t="s">
-        <v>45</v>
+      <c r="G38" s="10">
+        <v>0.95</v>
+      </c>
+      <c r="H38" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>53</v>
       </c>
       <c r="J38" s="23">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B39" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C39" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D39" s="10"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="10" t="str">
+      <c r="K38" s="22">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B39" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" s="9"/>
+      <c r="E39" s="19">
+        <v>45912</v>
+      </c>
+      <c r="F39" s="9" t="str">
         <f t="shared" si="0"/>
         <v>In Progess</v>
       </c>
-      <c r="G39" s="11">
-        <v>0.8</v>
-      </c>
-      <c r="H39" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I39" s="10" t="s">
-        <v>40</v>
+      <c r="G39" s="10">
+        <v>0.9</v>
+      </c>
+      <c r="H39" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="J39" s="23">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B40" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C40" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" s="10"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="10" t="str">
+      <c r="K39" s="22">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B40" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40" s="9"/>
+      <c r="E40" s="19">
+        <v>45973</v>
+      </c>
+      <c r="F40" s="9" t="str">
         <f t="shared" ref="F40" si="2">IF(G40=1,"Complete",IF(G40&lt;&gt;0,"In Progess","Not Started"))</f>
         <v>In Progess</v>
       </c>
-      <c r="G40" s="11">
+      <c r="G40" s="10">
         <v>0.2</v>
       </c>
-      <c r="H40" s="12">
+      <c r="H40" s="11">
         <f t="shared" ref="H40" si="3">--(G40&gt;=1)</f>
         <v>0</v>
       </c>
-      <c r="I40" s="10" t="s">
-        <v>47</v>
+      <c r="I40" s="9" t="s">
+        <v>44</v>
       </c>
       <c r="J40" s="23">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="41" spans="2:10" ht="75" x14ac:dyDescent="0.25">
-      <c r="B41" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D41" s="13"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="10" t="str">
+      <c r="K40" s="22">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="B41" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" s="12"/>
+      <c r="E41" s="19">
+        <v>45912</v>
+      </c>
+      <c r="F41" s="9" t="str">
         <f t="shared" si="0"/>
         <v>In Progess</v>
       </c>
-      <c r="G41" s="11">
+      <c r="G41" s="10">
         <v>0.6</v>
       </c>
-      <c r="H41" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I41" s="10" t="s">
-        <v>41</v>
+      <c r="H41" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="J41" s="23">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B42" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D42" s="8"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="10" t="str">
+      <c r="K41" s="22">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B42" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D42" s="7"/>
+      <c r="E42" s="19">
+        <v>45879</v>
+      </c>
+      <c r="F42" s="9" t="str">
         <f t="shared" si="0"/>
         <v>Complete</v>
       </c>
-      <c r="G42" s="11">
+      <c r="G42" s="10">
         <v>1</v>
       </c>
-      <c r="H42" s="12">
+      <c r="H42" s="11">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="I42" s="10"/>
+      <c r="I42" s="9"/>
       <c r="J42" s="23">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B43" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D43" s="8"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="10" t="str">
+      <c r="K42" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B43" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D43" s="7"/>
+      <c r="E43" s="19">
+        <v>45879</v>
+      </c>
+      <c r="F43" s="9" t="str">
         <f t="shared" si="0"/>
         <v>Complete</v>
       </c>
-      <c r="G43" s="11">
+      <c r="G43" s="10">
         <v>1</v>
       </c>
-      <c r="H43" s="12">
+      <c r="H43" s="11">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="I43" s="10"/>
+      <c r="I43" s="9"/>
       <c r="J43" s="23">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B44" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D44" s="13"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="10" t="str">
+      <c r="K43" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B44" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D44" s="12"/>
+      <c r="E44" s="19">
+        <v>45912</v>
+      </c>
+      <c r="F44" s="9" t="str">
         <f t="shared" si="0"/>
         <v>In Progess</v>
       </c>
-      <c r="G44" s="14">
+      <c r="G44" s="13">
         <v>0.8</v>
       </c>
-      <c r="H44" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I44" s="10"/>
+      <c r="H44" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I44" s="9"/>
       <c r="J44" s="23">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="45" spans="2:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B45" s="8" t="s">
+      <c r="K44" s="22">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="B45" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D45" s="12"/>
+      <c r="E45" s="19">
+        <v>46010</v>
+      </c>
+      <c r="F45" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Not Started</v>
+      </c>
+      <c r="G45" s="13"/>
+      <c r="H45" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="J45" s="23"/>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B46" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C45" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D45" s="13"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G45" s="14"/>
-      <c r="H45" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I45" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="J45" s="23"/>
-    </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B46" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D46" s="13"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="10" t="str">
+      <c r="C46" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D46" s="12"/>
+      <c r="E46" s="19">
+        <v>46010</v>
+      </c>
+      <c r="F46" s="9" t="str">
         <f t="shared" si="0"/>
         <v>In Progess</v>
       </c>
-      <c r="G46" s="14">
+      <c r="G46" s="13">
         <v>0.5</v>
       </c>
-      <c r="H46" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I46" s="10"/>
+      <c r="H46" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I46" s="9"/>
       <c r="J46" s="23">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B47" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D47" s="13"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="10" t="str">
+      <c r="K46" s="22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B47" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D47" s="12"/>
+      <c r="E47" s="19">
+        <v>45971</v>
+      </c>
+      <c r="F47" s="9" t="str">
         <f t="shared" si="0"/>
         <v>In Progess</v>
       </c>
-      <c r="G47" s="14">
+      <c r="G47" s="13">
         <v>0.5</v>
       </c>
-      <c r="H47" s="12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I47" s="10"/>
+      <c r="H47" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I47" s="9"/>
       <c r="J47" s="23">
         <v>0.5</v>
       </c>
+      <c r="K47" s="22">
+        <v>0.5</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:I47" xr:uid="{825F216F-6A2C-43F0-976D-4459909E096A}"/>
+  <autoFilter ref="B3:BG47" xr:uid="{825F216F-6A2C-43F0-976D-4459909E096A}"/>
   <conditionalFormatting sqref="G4:G47">
     <cfRule type="dataBar" priority="1">
       <dataBar>
@@ -1881,7 +2076,7 @@
           <xm:sqref>G4:G47</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="17" id="{E713B901-0E7B-40B8-A534-1C73C66CF397}">
+          <x14:cfRule type="iconSet" priority="20" id="{E713B901-0E7B-40B8-A534-1C73C66CF397}">
             <x14:iconSet iconSet="3Symbols" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -1915,12 +2110,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2125,15 +2317,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2158,18 +2362,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/ContinuationProject/Status.xlsx
+++ b/ContinuationProject/Status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\ContinuationProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28785714-6456-4304-99E5-823692D43FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE0B3E4A-6A26-4231-8F9B-0E597DA0D67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
   </bookViews>
@@ -401,7 +401,7 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Date" xfId="6" xr:uid="{2ABB41C5-3CC8-4E1C-85D9-965CF83E22BD}"/>
@@ -768,10 +768,11 @@
     <col min="6" max="6" width="14.42578125" customWidth="1"/>
     <col min="7" max="7" width="25.85546875" customWidth="1"/>
     <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="25.140625" customWidth="1"/>
+    <col min="9" max="9" width="34" customWidth="1"/>
     <col min="10" max="10" width="18.140625" style="22" customWidth="1"/>
     <col min="11" max="11" width="16.85546875" style="22" customWidth="1"/>
-    <col min="12" max="36" width="9.140625" style="22"/>
+    <col min="12" max="12" width="15" style="22" customWidth="1"/>
+    <col min="13" max="36" width="9.140625" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:59" ht="35.25" x14ac:dyDescent="0.5">
@@ -2116,6 +2117,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100C3422A7FFD03AF47B40E3148D61510DD" ma:contentTypeVersion="10" ma:contentTypeDescription="Opprett et nytt dokument." ma:contentTypeScope="" ma:versionID="93a5827b91256c075a5bcdb454d162de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0" xmlns:ns3="b6192152-6ac4-477a-b62a-2f500fcdf3b6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="13127a08f307124b01356346b67d6a81" ns2:_="" ns3:_="">
     <xsd:import namespace="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
@@ -2316,15 +2326,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
   <ds:schemaRefs>
@@ -2343,6 +2344,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CED3C9C-630D-4C4B-A736-44AEC9EEC0A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2359,12 +2368,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/ContinuationProject/Status.xlsx
+++ b/ContinuationProject/Status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\ContinuationProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE0B3E4A-6A26-4231-8F9B-0E597DA0D67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F34359FF-671B-48E8-80D7-3AF252E69B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="63">
   <si>
     <t>DISC DEXPI Continuation Project - Status</t>
   </si>
@@ -182,9 +182,6 @@
     <t>Text rotation, Label position, Link to attributes</t>
   </si>
   <si>
-    <t>Discussed with Aibel/Hexagon - need to find which rules would apply to ensure correct usage of this new class.</t>
-  </si>
-  <si>
     <t>Model given OK from Aibel. Need list of component type from Aibel with RDL.</t>
   </si>
   <si>
@@ -218,6 +215,29 @@
   </si>
   <si>
     <t>08.09.2025</t>
+  </si>
+  <si>
+    <t>15.09.2025</t>
+  </si>
+  <si>
+    <t>Agreed with Aibel that rules for which sub-type to use will be project specific linked to specific function types.</t>
+  </si>
+  <si>
+    <t>Model prepared and will be presented during workshop.</t>
+  </si>
+  <si>
+    <t>Challenge with battery-limits, these are often drafted using vendor limiting 'boxes' connected via nozzles and overlapping signal lines. 
+Suggest to separate out tie-ins from battery-limits.</t>
+  </si>
+  <si>
+    <t>LineStyles support in DEXPI</t>
+  </si>
+  <si>
+    <t>NEW: DEXPI graphical primitives does not support linestyles used in DISC.
+Add issue to DEXPI content team.</t>
+  </si>
+  <si>
+    <t>Not Started</t>
   </si>
 </sst>
 </file>
@@ -288,12 +308,18 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -347,7 +373,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
@@ -402,6 +428,17 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Date" xfId="6" xr:uid="{2ABB41C5-3CC8-4E1C-85D9-965CF83E22BD}"/>
@@ -757,10 +794,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825F216F-6A2C-43F0-976D-4459909E096A}">
-  <dimension ref="B1:BG47"/>
+  <dimension ref="B1:BG48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.85546875" customWidth="1"/>
+    <col min="1" max="1" width="5.85546875" customWidth="1"/>
     <col min="2" max="2" width="45.42578125" customWidth="1"/>
     <col min="3" max="3" width="64.42578125" customWidth="1"/>
     <col min="4" max="4" width="22.7109375" customWidth="1"/>
@@ -807,30 +844,32 @@
         <v>36</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K3" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="L3" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
-      <c r="O3" s="20"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
       <c r="P3" s="20"/>
       <c r="Q3" s="20"/>
       <c r="R3" s="20"/>
@@ -892,7 +931,7 @@
         <v>In Progess</v>
       </c>
       <c r="G4" s="10">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="H4" s="11">
         <f>--(G4&gt;=1)</f>
@@ -906,6 +945,9 @@
       </c>
       <c r="K4" s="22">
         <v>0.3</v>
+      </c>
+      <c r="L4" s="22">
+        <v>0.35</v>
       </c>
     </row>
     <row r="5" spans="2:59" ht="30" x14ac:dyDescent="0.25">
@@ -924,10 +966,10 @@
         <v>In Progess</v>
       </c>
       <c r="G5" s="10">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="H5" s="11">
-        <f t="shared" ref="H5:H47" si="1">--(G5&gt;=1)</f>
+        <f t="shared" ref="H5:H48" si="1">--(G5&gt;=1)</f>
         <v>0</v>
       </c>
       <c r="I5" s="9"/>
@@ -937,6 +979,9 @@
       <c r="K5" s="22">
         <v>0.75</v>
       </c>
+      <c r="L5" s="22">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="6" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
@@ -954,20 +999,23 @@
         <v>In Progess</v>
       </c>
       <c r="G6" s="10">
-        <v>0.9</v>
+        <v>0.98</v>
       </c>
       <c r="H6" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J6" s="23">
         <v>0.9</v>
       </c>
       <c r="K6" s="22">
         <v>0.9</v>
+      </c>
+      <c r="L6" s="22">
+        <v>0.98</v>
       </c>
     </row>
     <row r="7" spans="2:59" x14ac:dyDescent="0.25">
@@ -1051,7 +1099,7 @@
         <v>45909</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G10" s="10">
         <v>1</v>
@@ -1065,6 +1113,9 @@
       <c r="K10" s="22">
         <v>1</v>
       </c>
+      <c r="L10" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
@@ -1095,6 +1146,9 @@
       <c r="K11" s="22">
         <v>0.75</v>
       </c>
+      <c r="L11" s="22">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="12" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
@@ -1173,6 +1227,9 @@
       <c r="K14" s="22">
         <v>1</v>
       </c>
+      <c r="L14" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
@@ -1197,12 +1254,15 @@
         <v>0</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J15" s="23">
         <v>0.7</v>
       </c>
       <c r="K15" s="22">
+        <v>0.7</v>
+      </c>
+      <c r="L15" s="22">
         <v>0.7</v>
       </c>
     </row>
@@ -1234,8 +1294,11 @@
       <c r="K16" s="22">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="17" spans="2:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L16" s="22">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>7</v>
       </c>
@@ -1257,7 +1320,7 @@
       </c>
       <c r="J17" s="23"/>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
         <v>7</v>
       </c>
@@ -1279,7 +1342,7 @@
       </c>
       <c r="J18" s="23"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
         <v>7</v>
       </c>
@@ -1301,7 +1364,7 @@
       </c>
       <c r="J19" s="23"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>7</v>
       </c>
@@ -1323,7 +1386,7 @@
       </c>
       <c r="J20" s="23"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" ht="105" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
         <v>8</v>
       </c>
@@ -1336,16 +1399,24 @@
       </c>
       <c r="F21" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G21" s="10"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G21" s="10">
+        <v>0.4</v>
+      </c>
       <c r="H21" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="I21" s="6" t="s">
+        <v>59</v>
+      </c>
       <c r="J21" s="23"/>
-    </row>
-    <row r="22" spans="2:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L21" s="22">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
         <v>8</v>
       </c>
@@ -1358,16 +1429,21 @@
       </c>
       <c r="F22" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G22" s="10"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G22" s="10">
+        <v>0.3</v>
+      </c>
       <c r="H22" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J22" s="23"/>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L22" s="22">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
         <v>8</v>
       </c>
@@ -1389,7 +1465,7 @@
       </c>
       <c r="J23" s="23"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
         <v>8</v>
       </c>
@@ -1411,7 +1487,7 @@
       </c>
       <c r="J24" s="23"/>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" s="9" t="s">
         <v>8</v>
       </c>
@@ -1433,7 +1509,7 @@
       </c>
       <c r="J25" s="23"/>
     </row>
-    <row r="26" spans="2:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="9" t="s">
         <v>2</v>
       </c>
@@ -1449,14 +1525,14 @@
         <v>In Progess</v>
       </c>
       <c r="G26" s="10">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="H26" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="J26" s="23">
         <v>0.7</v>
@@ -1464,8 +1540,11 @@
       <c r="K26" s="22">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L26" s="22">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B27" s="9" t="s">
         <v>2</v>
       </c>
@@ -1488,7 +1567,7 @@
       <c r="I27" s="9"/>
       <c r="J27" s="23"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
         <v>2</v>
       </c>
@@ -1511,7 +1590,7 @@
       <c r="I28" s="9"/>
       <c r="J28" s="23"/>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
         <v>2</v>
       </c>
@@ -1534,7 +1613,7 @@
       <c r="I29" s="9"/>
       <c r="J29" s="23"/>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="30" x14ac:dyDescent="0.25">
       <c r="B30" s="9" t="s">
         <v>9</v>
       </c>
@@ -1547,17 +1626,24 @@
       </c>
       <c r="F30" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G30" s="10"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G30" s="10">
+        <v>0.5</v>
+      </c>
       <c r="H30" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I30" s="9"/>
+      <c r="I30" s="9" t="s">
+        <v>58</v>
+      </c>
       <c r="J30" s="23"/>
-    </row>
-    <row r="31" spans="2:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L30" s="22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="9" t="s">
         <v>9</v>
       </c>
@@ -1570,17 +1656,22 @@
       </c>
       <c r="F31" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G31" s="10"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G31" s="10">
+        <v>0.5</v>
+      </c>
       <c r="H31" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="23"/>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L31" s="22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B32" s="9" t="s">
         <v>9</v>
       </c>
@@ -1603,7 +1694,7 @@
       <c r="I32" s="9"/>
       <c r="J32" s="23"/>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B33" s="9" t="s">
         <v>9</v>
       </c>
@@ -1626,7 +1717,7 @@
       <c r="I33" s="9"/>
       <c r="J33" s="23"/>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="9" t="s">
         <v>9</v>
       </c>
@@ -1649,7 +1740,7 @@
       <c r="I34" s="9"/>
       <c r="J34" s="23"/>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B35" s="9" t="s">
         <v>40</v>
       </c>
@@ -1678,8 +1769,11 @@
       <c r="K35" s="22">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L35" s="22">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B36" s="9" t="s">
         <v>40</v>
       </c>
@@ -1702,7 +1796,7 @@
       <c r="I36" s="9"/>
       <c r="J36" s="23"/>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B37" s="9" t="s">
         <v>40</v>
       </c>
@@ -1725,12 +1819,12 @@
       <c r="I37" s="9"/>
       <c r="J37" s="23"/>
     </row>
-    <row r="38" spans="2:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:12" ht="90" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="19">
@@ -1741,14 +1835,14 @@
         <v>In Progess</v>
       </c>
       <c r="G38" s="10">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="H38" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J38" s="23">
         <v>0.85</v>
@@ -1756,8 +1850,11 @@
       <c r="K38" s="22">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L38" s="22">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" ht="30" x14ac:dyDescent="0.25">
       <c r="B39" s="9" t="s">
         <v>27</v>
       </c>
@@ -1773,7 +1870,7 @@
         <v>In Progess</v>
       </c>
       <c r="G39" s="10">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H39" s="11">
         <f t="shared" si="1"/>
@@ -1788,8 +1885,11 @@
       <c r="K39" s="22">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L39" s="22">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" ht="30" x14ac:dyDescent="0.25">
       <c r="B40" s="9" t="s">
         <v>27</v>
       </c>
@@ -1820,8 +1920,11 @@
       <c r="K40" s="22">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="41" spans="2:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="L40" s="22">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" ht="90" x14ac:dyDescent="0.25">
       <c r="B41" s="9" t="s">
         <v>10</v>
       </c>
@@ -1852,8 +1955,11 @@
       <c r="K41" s="22">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L41" s="22">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B42" s="7" t="s">
         <v>29</v>
       </c>
@@ -1882,8 +1988,11 @@
       <c r="K42" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L42" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
         <v>11</v>
       </c>
@@ -1912,8 +2021,11 @@
       <c r="K43" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L43" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
         <v>16</v>
       </c>
@@ -1929,7 +2041,7 @@
         <v>In Progess</v>
       </c>
       <c r="G44" s="13">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="H44" s="11">
         <f t="shared" si="1"/>
@@ -1942,8 +2054,11 @@
       <c r="K44" s="22">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="45" spans="2:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="L44" s="22">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" ht="30" x14ac:dyDescent="0.25">
       <c r="B45" s="7" t="s">
         <v>16</v>
       </c>
@@ -1968,7 +2083,7 @@
       </c>
       <c r="J45" s="23"/>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B46" s="7" t="s">
         <v>17</v>
       </c>
@@ -1997,8 +2112,11 @@
       <c r="K46" s="22">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="L46" s="22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
         <v>18</v>
       </c>
@@ -2027,10 +2145,37 @@
       <c r="K47" s="22">
         <v>0.5</v>
       </c>
+      <c r="L47" s="22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="B48" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="C48" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="E48" s="20">
+        <v>46010</v>
+      </c>
+      <c r="F48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G48" s="26">
+        <v>0</v>
+      </c>
+      <c r="H48" s="27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L48" s="28">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="B3:BG47" xr:uid="{825F216F-6A2C-43F0-976D-4459909E096A}"/>
-  <conditionalFormatting sqref="G4:G47">
+  <conditionalFormatting sqref="G4:G48">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -2074,10 +2219,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>G4:G47</xm:sqref>
+          <xm:sqref>G4:G48</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="20" id="{E713B901-0E7B-40B8-A534-1C73C66CF397}">
+          <x14:cfRule type="iconSet" priority="21" id="{E713B901-0E7B-40B8-A534-1C73C66CF397}">
             <x14:iconSet iconSet="3Symbols" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -2093,7 +2238,7 @@
               <x14:cfIcon iconSet="3Symbols" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>H4:H47</xm:sqref>
+          <xm:sqref>H4:H48</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -2111,21 +2256,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100C3422A7FFD03AF47B40E3148D61510DD" ma:contentTypeVersion="10" ma:contentTypeDescription="Opprett et nytt dokument." ma:contentTypeScope="" ma:versionID="93a5827b91256c075a5bcdb454d162de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0" xmlns:ns3="b6192152-6ac4-477a-b62a-2f500fcdf3b6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="13127a08f307124b01356346b67d6a81" ns2:_="" ns3:_="">
     <xsd:import namespace="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
@@ -2326,32 +2456,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CED3C9C-630D-4C4B-A736-44AEC9EEC0A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2368,4 +2488,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/ContinuationProject/Status.xlsx
+++ b/ContinuationProject/Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\ContinuationProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F34359FF-671B-48E8-80D7-3AF252E69B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA56A651-8B80-4E16-B4CF-50955F7C3FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="4" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="66">
   <si>
     <t>DISC DEXPI Continuation Project - Status</t>
   </si>
@@ -238,6 +238,15 @@
   </si>
   <si>
     <t>Not Started</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete Workshop 1 </t>
+  </si>
+  <si>
+    <t>DISC DEXPI workshop at Equinor 2 - days</t>
+  </si>
+  <si>
+    <t>22.09.2025</t>
   </si>
 </sst>
 </file>
@@ -308,18 +317,12 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -373,7 +376,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
@@ -428,17 +431,16 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="5" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Date" xfId="6" xr:uid="{2ABB41C5-3CC8-4E1C-85D9-965CF83E22BD}"/>
@@ -794,7 +796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825F216F-6A2C-43F0-976D-4459909E096A}">
-  <dimension ref="B1:BG48"/>
+  <dimension ref="B1:BG49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.85546875" customWidth="1"/>
@@ -809,7 +811,8 @@
     <col min="10" max="10" width="18.140625" style="22" customWidth="1"/>
     <col min="11" max="11" width="16.85546875" style="22" customWidth="1"/>
     <col min="12" max="12" width="15" style="22" customWidth="1"/>
-    <col min="13" max="36" width="9.140625" style="22"/>
+    <col min="13" max="13" width="19.85546875" style="22" customWidth="1"/>
+    <col min="14" max="36" width="9.140625" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:59" ht="35.25" x14ac:dyDescent="0.5">
@@ -833,7 +836,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="6"/>
     </row>
-    <row r="3" spans="2:59" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:59" ht="34.5" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>20</v>
       </c>
@@ -867,7 +870,9 @@
       <c r="L3" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="M3" s="21"/>
+      <c r="M3" s="21" t="s">
+        <v>65</v>
+      </c>
       <c r="N3" s="21"/>
       <c r="O3" s="21"/>
       <c r="P3" s="20"/>
@@ -949,6 +954,9 @@
       <c r="L4" s="22">
         <v>0.35</v>
       </c>
+      <c r="M4" s="22">
+        <v>0.35</v>
+      </c>
     </row>
     <row r="5" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
@@ -969,7 +977,7 @@
         <v>0.8</v>
       </c>
       <c r="H5" s="11">
-        <f t="shared" ref="H5:H48" si="1">--(G5&gt;=1)</f>
+        <f t="shared" ref="H5:H49" si="1">--(G5&gt;=1)</f>
         <v>0</v>
       </c>
       <c r="I5" s="9"/>
@@ -982,8 +990,11 @@
       <c r="L5" s="22">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="6" spans="2:59" ht="30" x14ac:dyDescent="0.25">
+      <c r="M5" s="22">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="6" spans="2:59" ht="45" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>3</v>
       </c>
@@ -1015,6 +1026,9 @@
         <v>0.9</v>
       </c>
       <c r="L6" s="22">
+        <v>0.98</v>
+      </c>
+      <c r="M6" s="22">
         <v>0.98</v>
       </c>
     </row>
@@ -1116,6 +1130,9 @@
       <c r="L10" s="22">
         <v>1</v>
       </c>
+      <c r="M10" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
@@ -1133,7 +1150,7 @@
         <v>In Progess</v>
       </c>
       <c r="G11" s="10">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="H11" s="11">
         <f t="shared" si="1"/>
@@ -1149,6 +1166,9 @@
       <c r="L11" s="22">
         <v>0.75</v>
       </c>
+      <c r="M11" s="22">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="12" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
@@ -1230,6 +1250,9 @@
       <c r="L14" s="22">
         <v>1</v>
       </c>
+      <c r="M14" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
@@ -1265,6 +1288,9 @@
       <c r="L15" s="22">
         <v>0.7</v>
       </c>
+      <c r="M15" s="22">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="16" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
@@ -1282,7 +1308,7 @@
         <v>In Progess</v>
       </c>
       <c r="G16" s="10">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H16" s="11">
         <f t="shared" si="1"/>
@@ -1297,8 +1323,11 @@
       <c r="L16" s="22">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="17" spans="2:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M16" s="22">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>7</v>
       </c>
@@ -1320,7 +1349,7 @@
       </c>
       <c r="J17" s="23"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
         <v>7</v>
       </c>
@@ -1342,7 +1371,7 @@
       </c>
       <c r="J18" s="23"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
         <v>7</v>
       </c>
@@ -1364,7 +1393,7 @@
       </c>
       <c r="J19" s="23"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>7</v>
       </c>
@@ -1386,7 +1415,7 @@
       </c>
       <c r="J20" s="23"/>
     </row>
-    <row r="21" spans="2:12" ht="105" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:13" ht="105" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
         <v>8</v>
       </c>
@@ -1402,7 +1431,7 @@
         <v>In Progess</v>
       </c>
       <c r="G21" s="10">
-        <v>0.4</v>
+        <v>0.65</v>
       </c>
       <c r="H21" s="11">
         <f t="shared" si="1"/>
@@ -1415,8 +1444,11 @@
       <c r="L21" s="22">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="22" spans="2:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M21" s="22">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
         <v>8</v>
       </c>
@@ -1442,8 +1474,11 @@
       <c r="L22" s="22">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M22" s="22">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
         <v>8</v>
       </c>
@@ -1465,7 +1500,7 @@
       </c>
       <c r="J23" s="23"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
         <v>8</v>
       </c>
@@ -1487,7 +1522,7 @@
       </c>
       <c r="J24" s="23"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B25" s="9" t="s">
         <v>8</v>
       </c>
@@ -1509,7 +1544,7 @@
       </c>
       <c r="J25" s="23"/>
     </row>
-    <row r="26" spans="2:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:13" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="9" t="s">
         <v>2</v>
       </c>
@@ -1543,8 +1578,11 @@
       <c r="L26" s="22">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M26" s="22">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B27" s="9" t="s">
         <v>2</v>
       </c>
@@ -1567,7 +1605,7 @@
       <c r="I27" s="9"/>
       <c r="J27" s="23"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
         <v>2</v>
       </c>
@@ -1590,7 +1628,7 @@
       <c r="I28" s="9"/>
       <c r="J28" s="23"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
         <v>2</v>
       </c>
@@ -1613,7 +1651,7 @@
       <c r="I29" s="9"/>
       <c r="J29" s="23"/>
     </row>
-    <row r="30" spans="2:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B30" s="9" t="s">
         <v>9</v>
       </c>
@@ -1629,7 +1667,7 @@
         <v>In Progess</v>
       </c>
       <c r="G30" s="10">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="H30" s="11">
         <f t="shared" si="1"/>
@@ -1642,8 +1680,11 @@
       <c r="L30" s="22">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="31" spans="2:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M30" s="22">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="9" t="s">
         <v>9</v>
       </c>
@@ -1670,8 +1711,11 @@
       <c r="L31" s="22">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M31" s="22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B32" s="9" t="s">
         <v>9</v>
       </c>
@@ -1694,7 +1738,7 @@
       <c r="I32" s="9"/>
       <c r="J32" s="23"/>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B33" s="9" t="s">
         <v>9</v>
       </c>
@@ -1717,7 +1761,7 @@
       <c r="I33" s="9"/>
       <c r="J33" s="23"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B34" s="9" t="s">
         <v>9</v>
       </c>
@@ -1740,7 +1784,7 @@
       <c r="I34" s="9"/>
       <c r="J34" s="23"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B35" s="9" t="s">
         <v>40</v>
       </c>
@@ -1772,8 +1816,11 @@
       <c r="L35" s="22">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M35" s="22">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B36" s="9" t="s">
         <v>40</v>
       </c>
@@ -1796,7 +1843,7 @@
       <c r="I36" s="9"/>
       <c r="J36" s="23"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B37" s="9" t="s">
         <v>40</v>
       </c>
@@ -1819,7 +1866,7 @@
       <c r="I37" s="9"/>
       <c r="J37" s="23"/>
     </row>
-    <row r="38" spans="2:12" ht="90" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:13" ht="90" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="s">
         <v>27</v>
       </c>
@@ -1853,8 +1900,11 @@
       <c r="L38" s="22">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="39" spans="2:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="M38" s="22">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B39" s="9" t="s">
         <v>27</v>
       </c>
@@ -1888,8 +1938,11 @@
       <c r="L39" s="22">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="40" spans="2:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="M39" s="22">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B40" s="9" t="s">
         <v>27</v>
       </c>
@@ -1923,8 +1976,11 @@
       <c r="L40" s="22">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="41" spans="2:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="M40" s="22">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13" ht="90" x14ac:dyDescent="0.25">
       <c r="B41" s="9" t="s">
         <v>10</v>
       </c>
@@ -1958,8 +2014,11 @@
       <c r="L41" s="22">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M41" s="22">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B42" s="7" t="s">
         <v>29</v>
       </c>
@@ -1991,8 +2050,11 @@
       <c r="L42" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M42" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
         <v>11</v>
       </c>
@@ -2024,8 +2086,11 @@
       <c r="L43" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M43" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
         <v>16</v>
       </c>
@@ -2041,7 +2106,7 @@
         <v>In Progess</v>
       </c>
       <c r="G44" s="13">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="H44" s="11">
         <f t="shared" si="1"/>
@@ -2057,8 +2122,11 @@
       <c r="L44" s="22">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="M44" s="22">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B45" s="7" t="s">
         <v>16</v>
       </c>
@@ -2083,7 +2151,7 @@
       </c>
       <c r="J45" s="23"/>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B46" s="7" t="s">
         <v>17</v>
       </c>
@@ -2115,8 +2183,11 @@
       <c r="L46" s="22">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M46" s="22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
         <v>18</v>
       </c>
@@ -2148,12 +2219,15 @@
       <c r="L47" s="22">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="B48" s="24" t="s">
+      <c r="M47" s="22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
         <v>60</v>
       </c>
-      <c r="C48" s="25" t="s">
+      <c r="C48" s="6" t="s">
         <v>61</v>
       </c>
       <c r="E48" s="20">
@@ -2162,20 +2236,47 @@
       <c r="F48" t="s">
         <v>62</v>
       </c>
-      <c r="G48" s="26">
-        <v>0</v>
-      </c>
-      <c r="H48" s="27">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L48" s="28">
-        <v>0</v>
+      <c r="G48" s="24">
+        <v>0</v>
+      </c>
+      <c r="H48" s="25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L48" s="27">
+        <v>0</v>
+      </c>
+      <c r="M48" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>63</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E49" s="20">
+        <v>45918</v>
+      </c>
+      <c r="F49" t="s">
+        <v>54</v>
+      </c>
+      <c r="G49" s="24">
+        <v>1</v>
+      </c>
+      <c r="H49" s="26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M49" s="22">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B3:BG47" xr:uid="{825F216F-6A2C-43F0-976D-4459909E096A}"/>
-  <conditionalFormatting sqref="G4:G48">
+  <conditionalFormatting sqref="G4:G49">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -2219,7 +2320,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>G4:G48</xm:sqref>
+          <xm:sqref>G4:G49</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="21" id="{E713B901-0E7B-40B8-A534-1C73C66CF397}">
@@ -2238,7 +2339,7 @@
               <x14:cfIcon iconSet="3Symbols" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>H4:H48</xm:sqref>
+          <xm:sqref>H4:H49</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -2256,6 +2357,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100C3422A7FFD03AF47B40E3148D61510DD" ma:contentTypeVersion="10" ma:contentTypeDescription="Opprett et nytt dokument." ma:contentTypeScope="" ma:versionID="93a5827b91256c075a5bcdb454d162de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0" xmlns:ns3="b6192152-6ac4-477a-b62a-2f500fcdf3b6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="13127a08f307124b01356346b67d6a81" ns2:_="" ns3:_="">
     <xsd:import namespace="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
@@ -2456,22 +2572,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CED3C9C-630D-4C4B-A736-44AEC9EEC0A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2488,29 +2614,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/ContinuationProject/Status.xlsx
+++ b/ContinuationProject/Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\ContinuationProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA56A651-8B80-4E16-B4CF-50955F7C3FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97C4D69F-E82A-4F22-8996-5B9A3690E14F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="4" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="69">
   <si>
     <t>DISC DEXPI Continuation Project - Status</t>
   </si>
@@ -247,6 +247,15 @@
   </si>
   <si>
     <t>22.09.2025</t>
+  </si>
+  <si>
+    <t>Determined that this gap must be solved in a different way.</t>
+  </si>
+  <si>
+    <t>MeasuringSystem only allows 1 MeasuringElement: need a new solution.</t>
+  </si>
+  <si>
+    <t>29.09.2025</t>
   </si>
 </sst>
 </file>
@@ -376,7 +385,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
@@ -437,10 +446,6 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="5" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Date" xfId="6" xr:uid="{2ABB41C5-3CC8-4E1C-85D9-965CF83E22BD}"/>
@@ -448,7 +453,7 @@
     <cellStyle name="Heading 1" xfId="3" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="4" builtinId="17"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
     <cellStyle name="Title" xfId="2" builtinId="15"/>
   </cellStyles>
   <dxfs count="1">
@@ -808,11 +813,12 @@
     <col min="7" max="7" width="25.85546875" customWidth="1"/>
     <col min="8" max="8" width="7" customWidth="1"/>
     <col min="9" max="9" width="34" customWidth="1"/>
-    <col min="10" max="10" width="18.140625" style="22" customWidth="1"/>
-    <col min="11" max="11" width="16.85546875" style="22" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" style="22" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="16.85546875" style="22" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="15" style="22" customWidth="1"/>
     <col min="13" max="13" width="19.85546875" style="22" customWidth="1"/>
-    <col min="14" max="36" width="9.140625" style="22"/>
+    <col min="14" max="14" width="17.7109375" style="22" customWidth="1"/>
+    <col min="15" max="36" width="9.140625" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:59" ht="35.25" x14ac:dyDescent="0.5">
@@ -873,7 +879,9 @@
       <c r="M3" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="N3" s="21"/>
+      <c r="N3" s="21" t="s">
+        <v>68</v>
+      </c>
       <c r="O3" s="21"/>
       <c r="P3" s="20"/>
       <c r="Q3" s="20"/>
@@ -936,7 +944,7 @@
         <v>In Progess</v>
       </c>
       <c r="G4" s="10">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="H4" s="11">
         <f>--(G4&gt;=1)</f>
@@ -956,6 +964,9 @@
       </c>
       <c r="M4" s="22">
         <v>0.35</v>
+      </c>
+      <c r="N4" s="22">
+        <v>0.4</v>
       </c>
     </row>
     <row r="5" spans="2:59" ht="30" x14ac:dyDescent="0.25">
@@ -993,6 +1004,9 @@
       <c r="M5" s="22">
         <v>0.8</v>
       </c>
+      <c r="N5" s="22">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="6" spans="2:59" ht="45" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
@@ -1007,14 +1021,14 @@
       </c>
       <c r="F6" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>In Progess</v>
+        <v>Complete</v>
       </c>
       <c r="G6" s="10">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="H6" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="9" t="s">
         <v>45</v>
@@ -1030,6 +1044,9 @@
       </c>
       <c r="M6" s="22">
         <v>0.98</v>
+      </c>
+      <c r="N6" s="22">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:59" x14ac:dyDescent="0.25">
@@ -1045,15 +1062,20 @@
       </c>
       <c r="F7" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G7" s="10"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G7" s="10">
+        <v>0.1</v>
+      </c>
       <c r="H7" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="23"/>
+      <c r="N7" s="22">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="8" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
@@ -1068,15 +1090,20 @@
       </c>
       <c r="F8" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G8" s="10"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G8" s="10">
+        <v>0.1</v>
+      </c>
       <c r="H8" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="23"/>
+      <c r="N8" s="22">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="9" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
@@ -1133,15 +1160,20 @@
       <c r="M10" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="2:59" x14ac:dyDescent="0.25">
+      <c r="N10" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:59" ht="60" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="9"/>
+      <c r="D11" s="9" t="s">
+        <v>67</v>
+      </c>
       <c r="E11" s="19">
         <v>45917</v>
       </c>
@@ -1150,13 +1182,15 @@
         <v>In Progess</v>
       </c>
       <c r="G11" s="10">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="H11" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I11" s="9"/>
+      <c r="I11" s="9" t="s">
+        <v>66</v>
+      </c>
       <c r="J11" s="23">
         <v>0.6</v>
       </c>
@@ -1168,6 +1202,9 @@
       </c>
       <c r="M11" s="22">
         <v>0.85</v>
+      </c>
+      <c r="N11" s="22">
+        <v>0.8</v>
       </c>
     </row>
     <row r="12" spans="2:59" x14ac:dyDescent="0.25">
@@ -1253,6 +1290,9 @@
       <c r="M14" s="22">
         <v>1</v>
       </c>
+      <c r="N14" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
@@ -1291,6 +1331,9 @@
       <c r="M15" s="22">
         <v>0.7</v>
       </c>
+      <c r="N15" s="22">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="16" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
@@ -1326,8 +1369,11 @@
       <c r="M16" s="22">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="17" spans="2:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N16" s="22">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>7</v>
       </c>
@@ -1349,7 +1395,7 @@
       </c>
       <c r="J17" s="23"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
         <v>7</v>
       </c>
@@ -1371,7 +1417,7 @@
       </c>
       <c r="J18" s="23"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
         <v>7</v>
       </c>
@@ -1393,7 +1439,7 @@
       </c>
       <c r="J19" s="23"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>7</v>
       </c>
@@ -1415,7 +1461,7 @@
       </c>
       <c r="J20" s="23"/>
     </row>
-    <row r="21" spans="2:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:14" ht="105" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
         <v>8</v>
       </c>
@@ -1431,7 +1477,7 @@
         <v>In Progess</v>
       </c>
       <c r="G21" s="10">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="H21" s="11">
         <f t="shared" si="1"/>
@@ -1447,8 +1493,11 @@
       <c r="M21" s="22">
         <v>0.65</v>
       </c>
-    </row>
-    <row r="22" spans="2:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N21" s="22">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
         <v>8</v>
       </c>
@@ -1464,7 +1513,7 @@
         <v>In Progess</v>
       </c>
       <c r="G22" s="10">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H22" s="11">
         <f t="shared" si="1"/>
@@ -1477,8 +1526,11 @@
       <c r="M22" s="22">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N22" s="22">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
         <v>8</v>
       </c>
@@ -1500,7 +1552,7 @@
       </c>
       <c r="J23" s="23"/>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
         <v>8</v>
       </c>
@@ -1522,7 +1574,7 @@
       </c>
       <c r="J24" s="23"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" s="9" t="s">
         <v>8</v>
       </c>
@@ -1544,7 +1596,7 @@
       </c>
       <c r="J25" s="23"/>
     </row>
-    <row r="26" spans="2:13" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:14" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="9" t="s">
         <v>2</v>
       </c>
@@ -1557,14 +1609,14 @@
       </c>
       <c r="F26" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>In Progess</v>
+        <v>Complete</v>
       </c>
       <c r="G26" s="10">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H26" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="9" t="s">
         <v>57</v>
@@ -1581,8 +1633,11 @@
       <c r="M26" s="22">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N26" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="9" t="s">
         <v>2</v>
       </c>
@@ -1595,17 +1650,22 @@
       </c>
       <c r="F27" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G27" s="10"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G27" s="10">
+        <v>0.6</v>
+      </c>
       <c r="H27" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I27" s="9"/>
       <c r="J27" s="23"/>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N27" s="22">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
         <v>2</v>
       </c>
@@ -1628,7 +1688,7 @@
       <c r="I28" s="9"/>
       <c r="J28" s="23"/>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
         <v>2</v>
       </c>
@@ -1651,7 +1711,7 @@
       <c r="I29" s="9"/>
       <c r="J29" s="23"/>
     </row>
-    <row r="30" spans="2:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B30" s="9" t="s">
         <v>9</v>
       </c>
@@ -1683,8 +1743,11 @@
       <c r="M30" s="22">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="31" spans="2:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N30" s="22">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="9" t="s">
         <v>9</v>
       </c>
@@ -1714,8 +1777,11 @@
       <c r="M31" s="22">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N31" s="22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B32" s="9" t="s">
         <v>9</v>
       </c>
@@ -1738,7 +1804,7 @@
       <c r="I32" s="9"/>
       <c r="J32" s="23"/>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B33" s="9" t="s">
         <v>9</v>
       </c>
@@ -1761,7 +1827,7 @@
       <c r="I33" s="9"/>
       <c r="J33" s="23"/>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B34" s="9" t="s">
         <v>9</v>
       </c>
@@ -1784,7 +1850,7 @@
       <c r="I34" s="9"/>
       <c r="J34" s="23"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B35" s="9" t="s">
         <v>40</v>
       </c>
@@ -1819,8 +1885,11 @@
       <c r="M35" s="22">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N35" s="22">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="36" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B36" s="9" t="s">
         <v>40</v>
       </c>
@@ -1833,17 +1902,22 @@
       </c>
       <c r="F36" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G36" s="10"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G36" s="10">
+        <v>0.2</v>
+      </c>
       <c r="H36" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I36" s="9"/>
       <c r="J36" s="23"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N36" s="22">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B37" s="9" t="s">
         <v>40</v>
       </c>
@@ -1866,7 +1940,7 @@
       <c r="I37" s="9"/>
       <c r="J37" s="23"/>
     </row>
-    <row r="38" spans="2:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:14" ht="90" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="s">
         <v>27</v>
       </c>
@@ -1903,8 +1977,11 @@
       <c r="M38" s="22">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="39" spans="2:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="N38" s="22">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B39" s="9" t="s">
         <v>27</v>
       </c>
@@ -1941,8 +2018,11 @@
       <c r="M39" s="22">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="40" spans="2:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="N39" s="22">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="40" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B40" s="9" t="s">
         <v>27</v>
       </c>
@@ -1979,8 +2059,11 @@
       <c r="M40" s="22">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="41" spans="2:13" ht="90" x14ac:dyDescent="0.25">
+      <c r="N40" s="22">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="41" spans="2:14" ht="90" x14ac:dyDescent="0.25">
       <c r="B41" s="9" t="s">
         <v>10</v>
       </c>
@@ -1996,7 +2079,7 @@
         <v>In Progess</v>
       </c>
       <c r="G41" s="10">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="H41" s="11">
         <f t="shared" si="1"/>
@@ -2017,8 +2100,11 @@
       <c r="M41" s="22">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N41" s="22">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B42" s="7" t="s">
         <v>29</v>
       </c>
@@ -2053,8 +2139,11 @@
       <c r="M42" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N42" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
         <v>11</v>
       </c>
@@ -2089,8 +2178,11 @@
       <c r="M43" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N43" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
         <v>16</v>
       </c>
@@ -2125,8 +2217,11 @@
       <c r="M44" s="22">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="N44" s="22">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" ht="30" x14ac:dyDescent="0.25">
       <c r="B45" s="7" t="s">
         <v>16</v>
       </c>
@@ -2151,7 +2246,7 @@
       </c>
       <c r="J45" s="23"/>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B46" s="7" t="s">
         <v>17</v>
       </c>
@@ -2186,8 +2281,11 @@
       <c r="M46" s="22">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N46" s="22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
         <v>18</v>
       </c>
@@ -2222,8 +2320,11 @@
       <c r="M47" s="22">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="N47" s="22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" ht="45" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>60</v>
       </c>
@@ -2243,14 +2344,17 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L48" s="27">
+      <c r="L48" s="22">
         <v>0</v>
       </c>
       <c r="M48" s="22">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N48" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>63</v>
       </c>
@@ -2266,11 +2370,14 @@
       <c r="G49" s="24">
         <v>1</v>
       </c>
-      <c r="H49" s="26">
+      <c r="H49" s="25">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="M49" s="22">
+        <v>1</v>
+      </c>
+      <c r="N49" s="22">
         <v>1</v>
       </c>
     </row>
@@ -2357,21 +2464,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100C3422A7FFD03AF47B40E3148D61510DD" ma:contentTypeVersion="10" ma:contentTypeDescription="Opprett et nytt dokument." ma:contentTypeScope="" ma:versionID="93a5827b91256c075a5bcdb454d162de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0" xmlns:ns3="b6192152-6ac4-477a-b62a-2f500fcdf3b6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="13127a08f307124b01356346b67d6a81" ns2:_="" ns3:_="">
     <xsd:import namespace="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
@@ -2572,32 +2664,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CED3C9C-630D-4C4B-A736-44AEC9EEC0A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2614,4 +2696,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/ContinuationProject/Status.xlsx
+++ b/ContinuationProject/Status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\ContinuationProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97C4D69F-E82A-4F22-8996-5B9A3690E14F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD2FEDAF-668A-41D1-9651-B01E684802F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="4" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="71">
   <si>
     <t>DISC DEXPI Continuation Project - Status</t>
   </si>
@@ -256,6 +256,12 @@
   </si>
   <si>
     <t>29.09.2025</t>
+  </si>
+  <si>
+    <t>To check Text rotation</t>
+  </si>
+  <si>
+    <t>06.10.2025</t>
   </si>
 </sst>
 </file>
@@ -453,7 +459,7 @@
     <cellStyle name="Heading 1" xfId="3" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="4" builtinId="17"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
     <cellStyle name="Title" xfId="2" builtinId="15"/>
   </cellStyles>
   <dxfs count="1">
@@ -815,10 +821,11 @@
     <col min="9" max="9" width="34" customWidth="1"/>
     <col min="10" max="10" width="18.140625" style="22" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="16.85546875" style="22" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="15" style="22" customWidth="1"/>
+    <col min="12" max="12" width="15" style="22" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="19.85546875" style="22" customWidth="1"/>
     <col min="14" max="14" width="17.7109375" style="22" customWidth="1"/>
-    <col min="15" max="36" width="9.140625" style="22"/>
+    <col min="15" max="15" width="16" style="22" customWidth="1"/>
+    <col min="16" max="36" width="9.140625" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:59" ht="35.25" x14ac:dyDescent="0.5">
@@ -842,7 +849,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="6"/>
     </row>
-    <row r="3" spans="2:59" ht="34.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:59" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>20</v>
       </c>
@@ -882,7 +889,9 @@
       <c r="N3" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="O3" s="21"/>
+      <c r="O3" s="21" t="s">
+        <v>70</v>
+      </c>
       <c r="P3" s="20"/>
       <c r="Q3" s="20"/>
       <c r="R3" s="20"/>
@@ -968,6 +977,9 @@
       <c r="N4" s="22">
         <v>0.4</v>
       </c>
+      <c r="O4" s="22">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="5" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
@@ -985,7 +997,7 @@
         <v>In Progess</v>
       </c>
       <c r="G5" s="10">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H5" s="11">
         <f t="shared" ref="H5:H49" si="1">--(G5&gt;=1)</f>
@@ -1007,6 +1019,9 @@
       <c r="N5" s="22">
         <v>0.8</v>
       </c>
+      <c r="O5" s="22">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="6" spans="2:59" ht="45" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
@@ -1048,6 +1063,9 @@
       <c r="N6" s="22">
         <v>1</v>
       </c>
+      <c r="O6" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
@@ -1062,20 +1080,23 @@
       </c>
       <c r="F7" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>In Progess</v>
+        <v>Complete</v>
       </c>
       <c r="G7" s="10">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="H7" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="23"/>
       <c r="N7" s="22">
         <v>0.1</v>
       </c>
+      <c r="O7" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
@@ -1104,6 +1125,9 @@
       <c r="N8" s="22">
         <v>0.1</v>
       </c>
+      <c r="O8" s="22">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="9" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
@@ -1163,6 +1187,9 @@
       <c r="N10" s="22">
         <v>1</v>
       </c>
+      <c r="O10" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="2:59" ht="60" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
@@ -1206,6 +1233,9 @@
       <c r="N11" s="22">
         <v>0.8</v>
       </c>
+      <c r="O11" s="22">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="12" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
@@ -1243,15 +1273,20 @@
       </c>
       <c r="F13" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G13" s="10"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G13" s="10">
+        <v>0.4</v>
+      </c>
       <c r="H13" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="23"/>
+      <c r="O13" s="22">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="14" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B14" s="9" t="s">
@@ -1293,6 +1328,9 @@
       <c r="N14" s="22">
         <v>1</v>
       </c>
+      <c r="O14" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
@@ -1334,6 +1372,9 @@
       <c r="N15" s="22">
         <v>0.7</v>
       </c>
+      <c r="O15" s="22">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="16" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
@@ -1372,8 +1413,11 @@
       <c r="N16" s="22">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="17" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O16" s="22">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>7</v>
       </c>
@@ -1395,7 +1439,7 @@
       </c>
       <c r="J17" s="23"/>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
         <v>7</v>
       </c>
@@ -1417,7 +1461,7 @@
       </c>
       <c r="J18" s="23"/>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
         <v>7</v>
       </c>
@@ -1439,7 +1483,7 @@
       </c>
       <c r="J19" s="23"/>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>7</v>
       </c>
@@ -1461,7 +1505,7 @@
       </c>
       <c r="J20" s="23"/>
     </row>
-    <row r="21" spans="2:14" ht="105" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:15" ht="105" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
         <v>8</v>
       </c>
@@ -1496,8 +1540,11 @@
       <c r="N21" s="22">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="22" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O21" s="22">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
         <v>8</v>
       </c>
@@ -1529,8 +1576,11 @@
       <c r="N22" s="22">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O22" s="22">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
         <v>8</v>
       </c>
@@ -1552,7 +1602,7 @@
       </c>
       <c r="J23" s="23"/>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
         <v>8</v>
       </c>
@@ -1574,7 +1624,7 @@
       </c>
       <c r="J24" s="23"/>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B25" s="9" t="s">
         <v>8</v>
       </c>
@@ -1596,7 +1646,7 @@
       </c>
       <c r="J25" s="23"/>
     </row>
-    <row r="26" spans="2:14" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:15" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="9" t="s">
         <v>2</v>
       </c>
@@ -1636,8 +1686,11 @@
       <c r="N26" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O26" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B27" s="9" t="s">
         <v>2</v>
       </c>
@@ -1650,22 +1703,25 @@
       </c>
       <c r="F27" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>In Progess</v>
+        <v>Complete</v>
       </c>
       <c r="G27" s="10">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="H27" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="9"/>
       <c r="J27" s="23"/>
       <c r="N27" s="22">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O27" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
         <v>2</v>
       </c>
@@ -1688,7 +1744,7 @@
       <c r="I28" s="9"/>
       <c r="J28" s="23"/>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
         <v>2</v>
       </c>
@@ -1711,7 +1767,7 @@
       <c r="I29" s="9"/>
       <c r="J29" s="23"/>
     </row>
-    <row r="30" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:15" ht="30" x14ac:dyDescent="0.25">
       <c r="B30" s="9" t="s">
         <v>9</v>
       </c>
@@ -1746,8 +1802,11 @@
       <c r="N30" s="22">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="31" spans="2:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O30" s="22">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="9" t="s">
         <v>9</v>
       </c>
@@ -1780,8 +1839,11 @@
       <c r="N31" s="22">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O31" s="22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B32" s="9" t="s">
         <v>9</v>
       </c>
@@ -1804,7 +1866,7 @@
       <c r="I32" s="9"/>
       <c r="J32" s="23"/>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B33" s="9" t="s">
         <v>9</v>
       </c>
@@ -1827,7 +1889,7 @@
       <c r="I33" s="9"/>
       <c r="J33" s="23"/>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B34" s="9" t="s">
         <v>9</v>
       </c>
@@ -1850,7 +1912,7 @@
       <c r="I34" s="9"/>
       <c r="J34" s="23"/>
     </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B35" s="9" t="s">
         <v>40</v>
       </c>
@@ -1863,14 +1925,14 @@
       </c>
       <c r="F35" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>In Progess</v>
+        <v>Complete</v>
       </c>
       <c r="G35" s="10">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H35" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="9"/>
       <c r="J35" s="23">
@@ -1888,8 +1950,11 @@
       <c r="N35" s="22">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="36" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O35" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B36" s="9" t="s">
         <v>40</v>
       </c>
@@ -1916,8 +1981,11 @@
       <c r="N36" s="22">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O36" s="22">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B37" s="9" t="s">
         <v>40</v>
       </c>
@@ -1930,17 +1998,22 @@
       </c>
       <c r="F37" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G37" s="10"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G37" s="10">
+        <v>0.4</v>
+      </c>
       <c r="H37" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I37" s="9"/>
       <c r="J37" s="23"/>
-    </row>
-    <row r="38" spans="2:14" ht="90" x14ac:dyDescent="0.25">
+      <c r="O37" s="22">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15" ht="90" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="s">
         <v>27</v>
       </c>
@@ -1953,14 +2026,14 @@
       </c>
       <c r="F38" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>In Progess</v>
+        <v>Complete</v>
       </c>
       <c r="G38" s="10">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="H38" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" s="9" t="s">
         <v>52</v>
@@ -1980,8 +2053,11 @@
       <c r="N38" s="22">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="39" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="O38" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" ht="30" x14ac:dyDescent="0.25">
       <c r="B39" s="9" t="s">
         <v>27</v>
       </c>
@@ -1994,14 +2070,14 @@
       </c>
       <c r="F39" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>In Progess</v>
+        <v>Complete</v>
       </c>
       <c r="G39" s="10">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H39" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" s="9" t="s">
         <v>38</v>
@@ -2021,15 +2097,20 @@
       <c r="N39" s="22">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="40" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="O39" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15" ht="30" x14ac:dyDescent="0.25">
       <c r="B40" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D40" s="9"/>
+      <c r="D40" s="9" t="s">
+        <v>69</v>
+      </c>
       <c r="E40" s="19">
         <v>45973</v>
       </c>
@@ -2038,7 +2119,7 @@
         <v>In Progess</v>
       </c>
       <c r="G40" s="10">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="H40" s="11">
         <f t="shared" ref="H40" si="3">--(G40&gt;=1)</f>
@@ -2062,8 +2143,11 @@
       <c r="N40" s="22">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="41" spans="2:14" ht="90" x14ac:dyDescent="0.25">
+      <c r="O40" s="22">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15" ht="90" x14ac:dyDescent="0.25">
       <c r="B41" s="9" t="s">
         <v>10</v>
       </c>
@@ -2076,14 +2160,14 @@
       </c>
       <c r="F41" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>In Progess</v>
+        <v>Complete</v>
       </c>
       <c r="G41" s="10">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H41" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" s="9" t="s">
         <v>39</v>
@@ -2103,8 +2187,11 @@
       <c r="N41" s="22">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O41" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B42" s="7" t="s">
         <v>29</v>
       </c>
@@ -2142,8 +2229,11 @@
       <c r="N42" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O42" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
         <v>11</v>
       </c>
@@ -2181,8 +2271,11 @@
       <c r="N43" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O43" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
         <v>16</v>
       </c>
@@ -2220,8 +2313,11 @@
       <c r="N44" s="22">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="O44" s="22">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" ht="30" x14ac:dyDescent="0.25">
       <c r="B45" s="7" t="s">
         <v>16</v>
       </c>
@@ -2246,7 +2342,7 @@
       </c>
       <c r="J45" s="23"/>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B46" s="7" t="s">
         <v>17</v>
       </c>
@@ -2262,7 +2358,7 @@
         <v>In Progess</v>
       </c>
       <c r="G46" s="13">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="H46" s="11">
         <f t="shared" si="1"/>
@@ -2284,8 +2380,11 @@
       <c r="N46" s="22">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O46" s="22">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
         <v>18</v>
       </c>
@@ -2323,8 +2422,11 @@
       <c r="N47" s="22">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="O47" s="22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" ht="45" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>60</v>
       </c>
@@ -2353,8 +2455,11 @@
       <c r="N48" s="22">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O48" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>63</v>
       </c>
@@ -2378,6 +2483,9 @@
         <v>1</v>
       </c>
       <c r="N49" s="22">
+        <v>1</v>
+      </c>
+      <c r="O49" s="22">
         <v>1</v>
       </c>
     </row>
@@ -2464,6 +2572,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100C3422A7FFD03AF47B40E3148D61510DD" ma:contentTypeVersion="10" ma:contentTypeDescription="Opprett et nytt dokument." ma:contentTypeScope="" ma:versionID="93a5827b91256c075a5bcdb454d162de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0" xmlns:ns3="b6192152-6ac4-477a-b62a-2f500fcdf3b6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="13127a08f307124b01356346b67d6a81" ns2:_="" ns3:_="">
     <xsd:import namespace="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
@@ -2664,22 +2787,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CED3C9C-630D-4C4B-A736-44AEC9EEC0A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2696,29 +2829,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/ContinuationProject/Status.xlsx
+++ b/ContinuationProject/Status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\ContinuationProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD2FEDAF-668A-41D1-9651-B01E684802F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8701DBF-7392-45E1-9C7B-2716CE434784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="73">
   <si>
     <t>DISC DEXPI Continuation Project - Status</t>
   </si>
@@ -152,9 +152,6 @@
   </si>
   <si>
     <t>Additional details</t>
-  </si>
-  <si>
-    <t>New requirements not confirmed yet.</t>
   </si>
   <si>
     <t>Automate conversion and add to profile</t>
@@ -237,9 +234,6 @@
 Add issue to DEXPI content team.</t>
   </si>
   <si>
-    <t>Not Started</t>
-  </si>
-  <si>
     <t xml:space="preserve">Complete Workshop 1 </t>
   </si>
   <si>
@@ -262,6 +256,20 @@
   </si>
   <si>
     <t>06.10.2025</t>
+  </si>
+  <si>
+    <t>Label position incl. note
+Label text
+Node directions/type/position</t>
+  </si>
+  <si>
+    <t>Exact text positions - fine adjustments</t>
+  </si>
+  <si>
+    <t>13.10.2025</t>
+  </si>
+  <si>
+    <t>Some issues with original files.</t>
   </si>
 </sst>
 </file>
@@ -391,7 +399,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
@@ -451,6 +459,16 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="5" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -813,7 +831,7 @@
     <col min="1" max="1" width="5.85546875" customWidth="1"/>
     <col min="2" max="2" width="45.42578125" customWidth="1"/>
     <col min="3" max="3" width="64.42578125" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" customWidth="1"/>
+    <col min="4" max="4" width="33.42578125" customWidth="1"/>
     <col min="5" max="5" width="16.5703125" style="20" customWidth="1"/>
     <col min="6" max="6" width="14.42578125" customWidth="1"/>
     <col min="7" max="7" width="25.85546875" customWidth="1"/>
@@ -822,10 +840,11 @@
     <col min="10" max="10" width="18.140625" style="22" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="16.85546875" style="22" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="15" style="22" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="19.85546875" style="22" customWidth="1"/>
+    <col min="13" max="13" width="19.85546875" style="22" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="17.7109375" style="22" customWidth="1"/>
     <col min="15" max="15" width="16" style="22" customWidth="1"/>
-    <col min="16" max="36" width="9.140625" style="22"/>
+    <col min="16" max="16" width="16.42578125" customWidth="1"/>
+    <col min="17" max="36" width="9.140625" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:59" ht="35.25" x14ac:dyDescent="0.5">
@@ -839,6 +858,7 @@
       <c r="G1" s="4"/>
       <c r="H1" s="1"/>
       <c r="I1" s="6"/>
+      <c r="P1" s="26"/>
     </row>
     <row r="2" spans="2:59" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="6"/>
@@ -848,6 +868,7 @@
       <c r="G2" s="4"/>
       <c r="H2" s="1"/>
       <c r="I2" s="6"/>
+      <c r="P2" s="26"/>
     </row>
     <row r="3" spans="2:59" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
@@ -860,39 +881,41 @@
         <v>36</v>
       </c>
       <c r="E3" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J3" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>48</v>
-      </c>
       <c r="K3" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="L3" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="L3" s="21" t="s">
-        <v>56</v>
-      </c>
       <c r="M3" s="21" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="N3" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="O3" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="O3" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="P3" s="20"/>
+      <c r="P3" s="27" t="s">
+        <v>71</v>
+      </c>
       <c r="Q3" s="20"/>
       <c r="R3" s="20"/>
       <c r="S3" s="20"/>
@@ -937,14 +960,16 @@
       <c r="BF3" s="20"/>
       <c r="BG3" s="20"/>
     </row>
-    <row r="4" spans="2:59" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:59" ht="45" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="9"/>
+      <c r="D4" s="9" t="s">
+        <v>69</v>
+      </c>
       <c r="E4" s="19">
         <v>46010</v>
       </c>
@@ -953,7 +978,7 @@
         <v>In Progess</v>
       </c>
       <c r="G4" s="10">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="H4" s="11">
         <f>--(G4&gt;=1)</f>
@@ -979,6 +1004,9 @@
       </c>
       <c r="O4" s="22">
         <v>0.4</v>
+      </c>
+      <c r="P4" s="28">
+        <v>0.8</v>
       </c>
     </row>
     <row r="5" spans="2:59" ht="30" x14ac:dyDescent="0.25">
@@ -993,17 +1021,19 @@
         <v>46010</v>
       </c>
       <c r="F5" s="9" t="str">
-        <f t="shared" ref="F5:F47" si="0">IF(G5=1,"Complete",IF(G5&lt;&gt;0,"In Progess","Not Started"))</f>
+        <f t="shared" ref="F5:F49" si="0">IF(G5=1,"Complete",IF(G5&lt;&gt;0,"In Progess","Not Started"))</f>
         <v>In Progess</v>
       </c>
       <c r="G5" s="10">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H5" s="11">
         <f t="shared" ref="H5:H49" si="1">--(G5&gt;=1)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="9"/>
+      <c r="I5" s="9" t="s">
+        <v>70</v>
+      </c>
       <c r="J5" s="23">
         <v>0.75</v>
       </c>
@@ -1021,6 +1051,9 @@
       </c>
       <c r="O5" s="22">
         <v>0.9</v>
+      </c>
+      <c r="P5" s="28">
+        <v>0.95</v>
       </c>
     </row>
     <row r="6" spans="2:59" ht="45" x14ac:dyDescent="0.25">
@@ -1046,7 +1079,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J6" s="23">
         <v>0.9</v>
@@ -1064,6 +1097,9 @@
         <v>1</v>
       </c>
       <c r="O6" s="22">
+        <v>1</v>
+      </c>
+      <c r="P6" s="28">
         <v>1</v>
       </c>
     </row>
@@ -1097,6 +1133,9 @@
       <c r="O7" s="22">
         <v>1</v>
       </c>
+      <c r="P7" s="28">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
@@ -1114,7 +1153,7 @@
         <v>In Progess</v>
       </c>
       <c r="G8" s="10">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H8" s="11">
         <f t="shared" si="1"/>
@@ -1128,6 +1167,9 @@
       <c r="O8" s="22">
         <v>0.1</v>
       </c>
+      <c r="P8" s="28">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="9" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
@@ -1151,6 +1193,7 @@
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="23"/>
+      <c r="P9" s="28"/>
     </row>
     <row r="10" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
@@ -1164,7 +1207,7 @@
         <v>45909</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G10" s="10">
         <v>1</v>
@@ -1190,8 +1233,11 @@
       <c r="O10" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="2:59" ht="60" x14ac:dyDescent="0.25">
+      <c r="P10" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:59" ht="45" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
         <v>5</v>
       </c>
@@ -1199,24 +1245,24 @@
         <v>22</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E11" s="19">
         <v>45917</v>
       </c>
       <c r="F11" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>In Progess</v>
+        <v>Complete</v>
       </c>
       <c r="G11" s="10">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H11" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J11" s="23">
         <v>0.6</v>
@@ -1235,6 +1281,9 @@
       </c>
       <c r="O11" s="22">
         <v>0.8</v>
+      </c>
+      <c r="P11" s="28">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="2:59" x14ac:dyDescent="0.25">
@@ -1250,15 +1299,20 @@
       </c>
       <c r="F12" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G12" s="10"/>
+        <v>Complete</v>
+      </c>
+      <c r="G12" s="10">
+        <v>1</v>
+      </c>
       <c r="H12" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="23"/>
+      <c r="P12" s="28">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
@@ -1276,7 +1330,7 @@
         <v>In Progess</v>
       </c>
       <c r="G13" s="10">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="H13" s="11">
         <f t="shared" si="1"/>
@@ -1287,13 +1341,16 @@
       <c r="O13" s="22">
         <v>0.4</v>
       </c>
+      <c r="P13" s="28">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="14" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B14" s="9" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D14" s="9"/>
       <c r="E14" s="19">
@@ -1311,7 +1368,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J14" s="23">
         <v>1</v>
@@ -1329,6 +1386,9 @@
         <v>1</v>
       </c>
       <c r="O14" s="22">
+        <v>1</v>
+      </c>
+      <c r="P14" s="28">
         <v>1</v>
       </c>
     </row>
@@ -1355,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J15" s="23">
         <v>0.7</v>
@@ -1373,6 +1433,9 @@
         <v>0.7</v>
       </c>
       <c r="O15" s="22">
+        <v>0.7</v>
+      </c>
+      <c r="P15" s="28">
         <v>0.7</v>
       </c>
     </row>
@@ -1416,8 +1479,11 @@
       <c r="O16" s="22">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="17" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P16" s="28">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>7</v>
       </c>
@@ -1438,8 +1504,9 @@
         <v>0</v>
       </c>
       <c r="J17" s="23"/>
-    </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P17" s="28"/>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
         <v>7</v>
       </c>
@@ -1460,8 +1527,9 @@
         <v>0</v>
       </c>
       <c r="J18" s="23"/>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P18" s="28"/>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
         <v>7</v>
       </c>
@@ -1482,8 +1550,9 @@
         <v>0</v>
       </c>
       <c r="J19" s="23"/>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P19" s="28"/>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>7</v>
       </c>
@@ -1504,8 +1573,9 @@
         <v>0</v>
       </c>
       <c r="J20" s="23"/>
-    </row>
-    <row r="21" spans="2:15" ht="105" x14ac:dyDescent="0.25">
+      <c r="P20" s="28"/>
+    </row>
+    <row r="21" spans="2:16" ht="105" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
         <v>8</v>
       </c>
@@ -1528,7 +1598,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J21" s="23"/>
       <c r="L21" s="22">
@@ -1543,8 +1613,11 @@
       <c r="O21" s="22">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="22" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P21" s="28">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
         <v>8</v>
       </c>
@@ -1579,8 +1652,11 @@
       <c r="O22" s="22">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P22" s="28">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
         <v>8</v>
       </c>
@@ -1601,8 +1677,9 @@
         <v>0</v>
       </c>
       <c r="J23" s="23"/>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P23" s="28"/>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
         <v>8</v>
       </c>
@@ -1623,8 +1700,9 @@
         <v>0</v>
       </c>
       <c r="J24" s="23"/>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P24" s="28"/>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B25" s="9" t="s">
         <v>8</v>
       </c>
@@ -1645,8 +1723,9 @@
         <v>0</v>
       </c>
       <c r="J25" s="23"/>
-    </row>
-    <row r="26" spans="2:15" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P25" s="28"/>
+    </row>
+    <row r="26" spans="2:16" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="9" t="s">
         <v>2</v>
       </c>
@@ -1669,7 +1748,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J26" s="23">
         <v>0.7</v>
@@ -1689,8 +1768,11 @@
       <c r="O26" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P26" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B27" s="9" t="s">
         <v>2</v>
       </c>
@@ -1720,8 +1802,11 @@
       <c r="O27" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P27" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
         <v>2</v>
       </c>
@@ -1734,17 +1819,22 @@
       </c>
       <c r="F28" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G28" s="10"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G28" s="10">
+        <v>0.75</v>
+      </c>
       <c r="H28" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I28" s="9"/>
       <c r="J28" s="23"/>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P28" s="28">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
         <v>2</v>
       </c>
@@ -1766,8 +1856,9 @@
       </c>
       <c r="I29" s="9"/>
       <c r="J29" s="23"/>
-    </row>
-    <row r="30" spans="2:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="P29" s="28"/>
+    </row>
+    <row r="30" spans="2:16" ht="30" x14ac:dyDescent="0.25">
       <c r="B30" s="9" t="s">
         <v>9</v>
       </c>
@@ -1790,7 +1881,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J30" s="23"/>
       <c r="L30" s="22">
@@ -1805,8 +1896,11 @@
       <c r="O30" s="22">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="31" spans="2:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P30" s="28">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="31" spans="2:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="9" t="s">
         <v>9</v>
       </c>
@@ -1842,8 +1936,11 @@
       <c r="O31" s="22">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P31" s="28">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B32" s="9" t="s">
         <v>9</v>
       </c>
@@ -1865,8 +1962,9 @@
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="23"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P32" s="28"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B33" s="9" t="s">
         <v>9</v>
       </c>
@@ -1888,8 +1986,9 @@
       </c>
       <c r="I33" s="9"/>
       <c r="J33" s="23"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P33" s="28"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B34" s="9" t="s">
         <v>9</v>
       </c>
@@ -1911,10 +2010,11 @@
       </c>
       <c r="I34" s="9"/>
       <c r="J34" s="23"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P34" s="28"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B35" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>22</v>
@@ -1953,10 +2053,13 @@
       <c r="O35" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P35" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B36" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>23</v>
@@ -1967,14 +2070,14 @@
       </c>
       <c r="F36" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>In Progess</v>
+        <v>Complete</v>
       </c>
       <c r="G36" s="10">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H36" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" s="9"/>
       <c r="J36" s="23"/>
@@ -1984,10 +2087,13 @@
       <c r="O36" s="22">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P36" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B37" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>24</v>
@@ -2012,13 +2118,16 @@
       <c r="O37" s="22">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="38" spans="2:15" ht="90" x14ac:dyDescent="0.25">
+      <c r="P37" s="28">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="38" spans="2:16" ht="90" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="19">
@@ -2036,7 +2145,7 @@
         <v>1</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J38" s="23">
         <v>0.85</v>
@@ -2056,8 +2165,11 @@
       <c r="O38" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="P38" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" ht="30" x14ac:dyDescent="0.25">
       <c r="B39" s="9" t="s">
         <v>27</v>
       </c>
@@ -2080,7 +2192,7 @@
         <v>1</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J39" s="23">
         <v>0.8</v>
@@ -2100,16 +2212,19 @@
       <c r="O39" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="2:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="P39" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="2:16" ht="30" x14ac:dyDescent="0.25">
       <c r="B40" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E40" s="19">
         <v>45973</v>
@@ -2119,14 +2234,14 @@
         <v>In Progess</v>
       </c>
       <c r="G40" s="10">
-        <v>0.6</v>
+        <v>0.95</v>
       </c>
       <c r="H40" s="11">
         <f t="shared" ref="H40" si="3">--(G40&gt;=1)</f>
         <v>0</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J40" s="23">
         <v>0.2</v>
@@ -2146,8 +2261,11 @@
       <c r="O40" s="22">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="41" spans="2:15" ht="90" x14ac:dyDescent="0.25">
+      <c r="P40" s="28">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="41" spans="2:16" ht="90" x14ac:dyDescent="0.25">
       <c r="B41" s="9" t="s">
         <v>10</v>
       </c>
@@ -2170,7 +2288,7 @@
         <v>1</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J41" s="23">
         <v>0.6</v>
@@ -2190,8 +2308,11 @@
       <c r="O41" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P41" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B42" s="7" t="s">
         <v>29</v>
       </c>
@@ -2232,8 +2353,11 @@
       <c r="O42" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P42" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
         <v>11</v>
       </c>
@@ -2274,8 +2398,11 @@
       <c r="O43" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P43" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
         <v>16</v>
       </c>
@@ -2316,8 +2443,11 @@
       <c r="O44" s="22">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="P44" s="29">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" ht="30" x14ac:dyDescent="0.25">
       <c r="B45" s="7" t="s">
         <v>16</v>
       </c>
@@ -2330,19 +2460,24 @@
       </c>
       <c r="F45" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G45" s="13"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G45" s="13">
+        <v>0.1</v>
+      </c>
       <c r="H45" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="J45" s="23"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P45" s="29">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B46" s="7" t="s">
         <v>17</v>
       </c>
@@ -2383,8 +2518,11 @@
       <c r="O46" s="22">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P46" s="29">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
         <v>18</v>
       </c>
@@ -2425,52 +2563,60 @@
       <c r="O47" s="22">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" ht="45" x14ac:dyDescent="0.25">
+      <c r="P47" s="29">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" ht="45" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
+        <v>59</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>60</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>61</v>
       </c>
       <c r="E48" s="20">
         <v>46010</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G48" s="24">
+        <v>0.15</v>
+      </c>
+      <c r="H48" s="25">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L48" s="22">
+        <v>0</v>
+      </c>
+      <c r="M48" s="22">
+        <v>0</v>
+      </c>
+      <c r="N48" s="22">
+        <v>0</v>
+      </c>
+      <c r="O48" s="22">
+        <v>0</v>
+      </c>
+      <c r="P48" s="24">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>61</v>
+      </c>
+      <c r="C49" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="G48" s="24">
-        <v>0</v>
-      </c>
-      <c r="H48" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L48" s="22">
-        <v>0</v>
-      </c>
-      <c r="M48" s="22">
-        <v>0</v>
-      </c>
-      <c r="N48" s="22">
-        <v>0</v>
-      </c>
-      <c r="O48" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B49" t="s">
-        <v>63</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="E49" s="20">
         <v>45918</v>
       </c>
-      <c r="F49" t="s">
-        <v>54</v>
+      <c r="F49" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Complete</v>
       </c>
       <c r="G49" s="24">
         <v>1</v>
@@ -2486,13 +2632,16 @@
         <v>1</v>
       </c>
       <c r="O49" s="22">
+        <v>1</v>
+      </c>
+      <c r="P49" s="24">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B3:BG47" xr:uid="{825F216F-6A2C-43F0-976D-4459909E096A}"/>
   <conditionalFormatting sqref="G4:G49">
-    <cfRule type="dataBar" priority="1">
+    <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
@@ -2513,7 +2662,7 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Start Date in this column under this heading" sqref="J3" xr:uid="{B097AD3D-83FE-4DB6-8AA6-82D58880DEE8}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Icon indicator for task completion in this column under this heading is automatically updated as tasks complete" sqref="H3" xr:uid="{E57FD015-A334-4A3D-9540-92E1D8A918A9}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Task in this column under this heading. Use heading filters to find specific entries" sqref="B3:D3" xr:uid="{6FDCA3F5-F6F1-45FB-8AE7-E90C5E60E365}"/>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Select entry from the list. Select CANCEL, then press ALT+DOWN ARROW to navigate the list. Select ENTER to make selection" sqref="F4:F47" xr:uid="{90892BC2-20A5-4151-9864-7558336C2FE7}">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Select entry from the list. Select CANCEL, then press ALT+DOWN ARROW to navigate the list. Select ENTER to make selection" sqref="F4:F49" xr:uid="{90892BC2-20A5-4151-9864-7558336C2FE7}">
       <formula1>"Not Started, In Progress, Deferred, Complete"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2538,7 +2687,7 @@
           <xm:sqref>G4:G49</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="21" id="{E713B901-0E7B-40B8-A534-1C73C66CF397}">
+          <x14:cfRule type="iconSet" priority="22" id="{E713B901-0E7B-40B8-A534-1C73C66CF397}">
             <x14:iconSet iconSet="3Symbols" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -2572,12 +2721,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -2586,7 +2729,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100C3422A7FFD03AF47B40E3148D61510DD" ma:contentTypeVersion="10" ma:contentTypeDescription="Opprett et nytt dokument." ma:contentTypeScope="" ma:versionID="93a5827b91256c075a5bcdb454d162de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0" xmlns:ns3="b6192152-6ac4-477a-b62a-2f500fcdf3b6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="13127a08f307124b01356346b67d6a81" ns2:_="" ns3:_="">
     <xsd:import namespace="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
@@ -2787,24 +2930,13 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -2812,7 +2944,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CED3C9C-630D-4C4B-A736-44AEC9EEC0A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2829,4 +2961,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/ContinuationProject/Status.xlsx
+++ b/ContinuationProject/Status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\ContinuationProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8701DBF-7392-45E1-9C7B-2716CE434784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76733C8E-5AD4-45C2-ADB2-CE4D6E306E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="74">
   <si>
     <t>DISC DEXPI Continuation Project - Status</t>
   </si>
@@ -270,6 +270,9 @@
   </si>
   <si>
     <t>Some issues with original files.</t>
+  </si>
+  <si>
+    <t>16.10.2025</t>
   </si>
 </sst>
 </file>
@@ -844,7 +847,8 @@
     <col min="14" max="14" width="17.7109375" style="22" customWidth="1"/>
     <col min="15" max="15" width="16" style="22" customWidth="1"/>
     <col min="16" max="16" width="16.42578125" customWidth="1"/>
-    <col min="17" max="36" width="9.140625" style="22"/>
+    <col min="17" max="17" width="16.140625" style="22" customWidth="1"/>
+    <col min="18" max="36" width="9.140625" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:59" ht="35.25" x14ac:dyDescent="0.5">
@@ -916,7 +920,9 @@
       <c r="P3" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="Q3" s="20"/>
+      <c r="Q3" s="27" t="s">
+        <v>73</v>
+      </c>
       <c r="R3" s="20"/>
       <c r="S3" s="20"/>
       <c r="T3" s="20"/>
@@ -1008,6 +1014,9 @@
       <c r="P4" s="28">
         <v>0.8</v>
       </c>
+      <c r="Q4" s="22">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="5" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
@@ -1055,6 +1064,9 @@
       <c r="P5" s="28">
         <v>0.95</v>
       </c>
+      <c r="Q5" s="22">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="6" spans="2:59" ht="45" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
@@ -1100,6 +1112,9 @@
         <v>1</v>
       </c>
       <c r="P6" s="28">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="22">
         <v>1</v>
       </c>
     </row>
@@ -1136,6 +1151,9 @@
       <c r="P7" s="28">
         <v>1</v>
       </c>
+      <c r="Q7" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
@@ -1150,14 +1168,14 @@
       </c>
       <c r="F8" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>In Progess</v>
+        <v>Complete</v>
       </c>
       <c r="G8" s="10">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H8" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="23"/>
@@ -1170,6 +1188,9 @@
       <c r="P8" s="28">
         <v>0.2</v>
       </c>
+      <c r="Q8" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
@@ -1236,6 +1257,9 @@
       <c r="P10" s="28">
         <v>1</v>
       </c>
+      <c r="Q10" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="2:59" ht="45" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
@@ -1285,6 +1309,9 @@
       <c r="P11" s="28">
         <v>1</v>
       </c>
+      <c r="Q11" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
@@ -1311,6 +1338,9 @@
       <c r="I12" s="9"/>
       <c r="J12" s="23"/>
       <c r="P12" s="28">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="22">
         <v>1</v>
       </c>
     </row>
@@ -1344,6 +1374,9 @@
       <c r="P13" s="28">
         <v>0.15</v>
       </c>
+      <c r="Q13" s="22">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="14" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B14" s="9" t="s">
@@ -1391,6 +1424,9 @@
       <c r="P14" s="28">
         <v>1</v>
       </c>
+      <c r="Q14" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
@@ -1438,6 +1474,9 @@
       <c r="P15" s="28">
         <v>0.7</v>
       </c>
+      <c r="Q15" s="22">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="16" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
@@ -1482,8 +1521,11 @@
       <c r="P16" s="28">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="17" spans="2:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q16" s="22">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>7</v>
       </c>
@@ -1506,7 +1548,7 @@
       <c r="J17" s="23"/>
       <c r="P17" s="28"/>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
         <v>7</v>
       </c>
@@ -1529,7 +1571,7 @@
       <c r="J18" s="23"/>
       <c r="P18" s="28"/>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
         <v>7</v>
       </c>
@@ -1552,7 +1594,7 @@
       <c r="J19" s="23"/>
       <c r="P19" s="28"/>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>7</v>
       </c>
@@ -1575,7 +1617,7 @@
       <c r="J20" s="23"/>
       <c r="P20" s="28"/>
     </row>
-    <row r="21" spans="2:16" ht="105" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:17" ht="105" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
         <v>8</v>
       </c>
@@ -1616,8 +1658,11 @@
       <c r="P21" s="28">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="22" spans="2:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q21" s="22">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
         <v>8</v>
       </c>
@@ -1655,8 +1700,11 @@
       <c r="P22" s="28">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q22" s="22">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
         <v>8</v>
       </c>
@@ -1679,7 +1727,7 @@
       <c r="J23" s="23"/>
       <c r="P23" s="28"/>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
         <v>8</v>
       </c>
@@ -1702,7 +1750,7 @@
       <c r="J24" s="23"/>
       <c r="P24" s="28"/>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B25" s="9" t="s">
         <v>8</v>
       </c>
@@ -1725,7 +1773,7 @@
       <c r="J25" s="23"/>
       <c r="P25" s="28"/>
     </row>
-    <row r="26" spans="2:16" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:17" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="9" t="s">
         <v>2</v>
       </c>
@@ -1771,8 +1819,11 @@
       <c r="P26" s="28">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q26" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B27" s="9" t="s">
         <v>2</v>
       </c>
@@ -1805,8 +1856,11 @@
       <c r="P27" s="28">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q27" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
         <v>2</v>
       </c>
@@ -1819,22 +1873,25 @@
       </c>
       <c r="F28" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>In Progess</v>
+        <v>Complete</v>
       </c>
       <c r="G28" s="10">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H28" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="9"/>
       <c r="J28" s="23"/>
       <c r="P28" s="28">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q28" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
         <v>2</v>
       </c>
@@ -1858,7 +1915,7 @@
       <c r="J29" s="23"/>
       <c r="P29" s="28"/>
     </row>
-    <row r="30" spans="2:16" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B30" s="9" t="s">
         <v>9</v>
       </c>
@@ -1899,8 +1956,11 @@
       <c r="P30" s="28">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="31" spans="2:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q30" s="22">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="9" t="s">
         <v>9</v>
       </c>
@@ -1939,8 +1999,11 @@
       <c r="P31" s="28">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q31" s="22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B32" s="9" t="s">
         <v>9</v>
       </c>
@@ -1964,7 +2027,7 @@
       <c r="J32" s="23"/>
       <c r="P32" s="28"/>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B33" s="9" t="s">
         <v>9</v>
       </c>
@@ -1988,7 +2051,7 @@
       <c r="J33" s="23"/>
       <c r="P33" s="28"/>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B34" s="9" t="s">
         <v>9</v>
       </c>
@@ -2012,7 +2075,7 @@
       <c r="J34" s="23"/>
       <c r="P34" s="28"/>
     </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B35" s="9" t="s">
         <v>39</v>
       </c>
@@ -2056,8 +2119,11 @@
       <c r="P35" s="28">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q35" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B36" s="9" t="s">
         <v>39</v>
       </c>
@@ -2090,8 +2156,11 @@
       <c r="P36" s="28">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q36" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B37" s="9" t="s">
         <v>39</v>
       </c>
@@ -2121,8 +2190,11 @@
       <c r="P37" s="28">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="38" spans="2:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q37" s="22">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="38" spans="2:17" ht="90" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="s">
         <v>27</v>
       </c>
@@ -2168,8 +2240,11 @@
       <c r="P38" s="28">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q38" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B39" s="9" t="s">
         <v>27</v>
       </c>
@@ -2215,8 +2290,11 @@
       <c r="P39" s="28">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="2:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q39" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B40" s="9" t="s">
         <v>27</v>
       </c>
@@ -2264,8 +2342,11 @@
       <c r="P40" s="28">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="41" spans="2:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q40" s="22">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="41" spans="2:17" ht="90" x14ac:dyDescent="0.25">
       <c r="B41" s="9" t="s">
         <v>10</v>
       </c>
@@ -2311,8 +2392,11 @@
       <c r="P41" s="28">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q41" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B42" s="7" t="s">
         <v>29</v>
       </c>
@@ -2356,8 +2440,11 @@
       <c r="P42" s="28">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q42" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
         <v>11</v>
       </c>
@@ -2401,8 +2488,11 @@
       <c r="P43" s="28">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q43" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
         <v>16</v>
       </c>
@@ -2415,14 +2505,14 @@
       </c>
       <c r="F44" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>In Progess</v>
+        <v>Complete</v>
       </c>
       <c r="G44" s="13">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="H44" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" s="9"/>
       <c r="J44" s="23">
@@ -2446,8 +2536,11 @@
       <c r="P44" s="29">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q44" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B45" s="7" t="s">
         <v>16</v>
       </c>
@@ -2476,8 +2569,11 @@
       <c r="P45" s="29">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q45" s="22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B46" s="7" t="s">
         <v>17</v>
       </c>
@@ -2493,7 +2589,7 @@
         <v>In Progess</v>
       </c>
       <c r="G46" s="13">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H46" s="11">
         <f t="shared" si="1"/>
@@ -2521,8 +2617,11 @@
       <c r="P46" s="29">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q46" s="22">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
         <v>18</v>
       </c>
@@ -2566,8 +2665,11 @@
       <c r="P47" s="29">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="Q47" s="22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" ht="45" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>59</v>
       </c>
@@ -2603,8 +2705,11 @@
       <c r="P48" s="24">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q48" s="22">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="49" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>61</v>
       </c>
@@ -2635,6 +2740,9 @@
         <v>1</v>
       </c>
       <c r="P49" s="24">
+        <v>1</v>
+      </c>
+      <c r="Q49" s="22">
         <v>1</v>
       </c>
     </row>
@@ -2721,12 +2829,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2931,15 +3036,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2964,18 +3081,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/ContinuationProject/Status.xlsx
+++ b/ContinuationProject/Status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\ContinuationProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76733C8E-5AD4-45C2-ADB2-CE4D6E306E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE06DB4-4530-47C5-B7AE-ACF8F1D79227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
   </bookViews>
@@ -832,9 +832,9 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.85546875" customWidth="1"/>
-    <col min="2" max="2" width="45.42578125" customWidth="1"/>
+    <col min="2" max="2" width="41.42578125" customWidth="1"/>
     <col min="3" max="3" width="64.42578125" customWidth="1"/>
-    <col min="4" max="4" width="33.42578125" customWidth="1"/>
+    <col min="4" max="4" width="25.85546875" customWidth="1"/>
     <col min="5" max="5" width="16.5703125" style="20" customWidth="1"/>
     <col min="6" max="6" width="14.42578125" customWidth="1"/>
     <col min="7" max="7" width="25.85546875" customWidth="1"/>
@@ -844,8 +844,8 @@
     <col min="11" max="11" width="16.85546875" style="22" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="15" style="22" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="19.85546875" style="22" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="17.7109375" style="22" customWidth="1"/>
-    <col min="15" max="15" width="16" style="22" customWidth="1"/>
+    <col min="14" max="14" width="17.7109375" style="22" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="16" style="22" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="16.42578125" customWidth="1"/>
     <col min="17" max="17" width="16.140625" style="22" customWidth="1"/>
     <col min="18" max="36" width="9.140625" style="22"/>
@@ -1205,9 +1205,11 @@
       </c>
       <c r="F9" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G9" s="10"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G9" s="10">
+        <v>0.25</v>
+      </c>
       <c r="H9" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1215,6 +1217,9 @@
       <c r="I9" s="9"/>
       <c r="J9" s="23"/>
       <c r="P9" s="28"/>
+      <c r="Q9" s="22">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="10" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
@@ -2829,9 +2834,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3036,27 +3044,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3081,9 +3077,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/ContinuationProject/Status.xlsx
+++ b/ContinuationProject/Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\ContinuationProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8701DBF-7392-45E1-9C7B-2716CE434784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C7CBE0B-9658-4ED3-8B6C-ADF7568EB7AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="4" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="75">
   <si>
     <t>DISC DEXPI Continuation Project - Status</t>
   </si>
@@ -270,6 +270,12 @@
   </si>
   <si>
     <t>Some issues with original files.</t>
+  </si>
+  <si>
+    <t>tonia to check drafting standard for ht</t>
+  </si>
+  <si>
+    <t>20.10.2025</t>
   </si>
 </sst>
 </file>
@@ -477,7 +483,7 @@
     <cellStyle name="Heading 1" xfId="3" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="4" builtinId="17"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
     <cellStyle name="Title" xfId="2" builtinId="15"/>
   </cellStyles>
   <dxfs count="1">
@@ -826,28 +832,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825F216F-6A2C-43F0-976D-4459909E096A}">
   <dimension ref="B1:BG49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="5.85546875" customWidth="1"/>
-    <col min="2" max="2" width="45.42578125" customWidth="1"/>
-    <col min="3" max="3" width="64.42578125" customWidth="1"/>
-    <col min="4" max="4" width="33.42578125" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" customWidth="1"/>
-    <col min="7" max="7" width="25.85546875" customWidth="1"/>
+    <col min="1" max="1" width="5.86328125" customWidth="1"/>
+    <col min="2" max="2" width="45.3984375" customWidth="1"/>
+    <col min="3" max="3" width="64.3984375" customWidth="1"/>
+    <col min="4" max="4" width="33.3984375" customWidth="1"/>
+    <col min="5" max="5" width="16.59765625" style="20" customWidth="1"/>
+    <col min="6" max="6" width="14.3984375" customWidth="1"/>
+    <col min="7" max="7" width="25.86328125" customWidth="1"/>
     <col min="8" max="8" width="7" customWidth="1"/>
     <col min="9" max="9" width="34" customWidth="1"/>
-    <col min="10" max="10" width="18.140625" style="22" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="16.85546875" style="22" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="18.1328125" style="22" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="16.86328125" style="22" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="15" style="22" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="19.85546875" style="22" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="17.7109375" style="22" customWidth="1"/>
+    <col min="13" max="13" width="19.86328125" style="22" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="17.73046875" style="22" customWidth="1"/>
     <col min="15" max="15" width="16" style="22" customWidth="1"/>
-    <col min="16" max="16" width="16.42578125" customWidth="1"/>
-    <col min="17" max="36" width="9.140625" style="22"/>
+    <col min="16" max="16" width="16.3984375" customWidth="1"/>
+    <col min="17" max="17" width="15.73046875" style="22" customWidth="1"/>
+    <col min="18" max="36" width="9.1328125" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:59" ht="35.25" x14ac:dyDescent="0.5">
+    <row r="1" spans="2:59" ht="34.9" x14ac:dyDescent="0.9">
       <c r="B1" s="16" t="s">
         <v>0</v>
       </c>
@@ -860,7 +867,7 @@
       <c r="I1" s="6"/>
       <c r="P1" s="26"/>
     </row>
-    <row r="2" spans="2:59" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:59" ht="9" customHeight="1" x14ac:dyDescent="0.7">
       <c r="C2" s="6"/>
       <c r="D2" s="1"/>
       <c r="E2" s="17"/>
@@ -870,7 +877,7 @@
       <c r="I2" s="6"/>
       <c r="P2" s="26"/>
     </row>
-    <row r="3" spans="2:59" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:59" ht="19.5" x14ac:dyDescent="0.6">
       <c r="B3" s="2" t="s">
         <v>20</v>
       </c>
@@ -916,7 +923,9 @@
       <c r="P3" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="Q3" s="20"/>
+      <c r="Q3" s="27" t="s">
+        <v>74</v>
+      </c>
       <c r="R3" s="20"/>
       <c r="S3" s="20"/>
       <c r="T3" s="20"/>
@@ -960,7 +969,7 @@
       <c r="BF3" s="20"/>
       <c r="BG3" s="20"/>
     </row>
-    <row r="4" spans="2:59" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:59" ht="42.75" x14ac:dyDescent="0.45">
       <c r="B4" s="9" t="s">
         <v>12</v>
       </c>
@@ -978,7 +987,7 @@
         <v>In Progess</v>
       </c>
       <c r="G4" s="10">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="H4" s="11">
         <f>--(G4&gt;=1)</f>
@@ -1008,8 +1017,11 @@
       <c r="P4" s="28">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="5" spans="2:59" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q4" s="22">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="5" spans="2:59" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B5" s="9" t="s">
         <v>12</v>
       </c>
@@ -1055,8 +1067,11 @@
       <c r="P5" s="28">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="6" spans="2:59" ht="45" x14ac:dyDescent="0.25">
+      <c r="Q5" s="22">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="6" spans="2:59" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B6" s="9" t="s">
         <v>3</v>
       </c>
@@ -1102,8 +1117,11 @@
       <c r="P6" s="28">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="2:59" x14ac:dyDescent="0.25">
+      <c r="Q6" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:59" x14ac:dyDescent="0.45">
       <c r="B7" s="9" t="s">
         <v>3</v>
       </c>
@@ -1136,8 +1154,11 @@
       <c r="P7" s="28">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="2:59" x14ac:dyDescent="0.25">
+      <c r="Q7" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:59" x14ac:dyDescent="0.45">
       <c r="B8" s="9" t="s">
         <v>3</v>
       </c>
@@ -1150,14 +1171,14 @@
       </c>
       <c r="F8" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>In Progess</v>
+        <v>Complete</v>
       </c>
       <c r="G8" s="10">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H8" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="23"/>
@@ -1170,8 +1191,11 @@
       <c r="P8" s="28">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="9" spans="2:59" x14ac:dyDescent="0.25">
+      <c r="Q8" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:59" x14ac:dyDescent="0.45">
       <c r="B9" s="9" t="s">
         <v>3</v>
       </c>
@@ -1184,9 +1208,11 @@
       </c>
       <c r="F9" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G9" s="10"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G9" s="10">
+        <v>0.1</v>
+      </c>
       <c r="H9" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1194,8 +1220,11 @@
       <c r="I9" s="9"/>
       <c r="J9" s="23"/>
       <c r="P9" s="28"/>
-    </row>
-    <row r="10" spans="2:59" x14ac:dyDescent="0.25">
+      <c r="Q9" s="22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:59" x14ac:dyDescent="0.45">
       <c r="B10" s="9" t="s">
         <v>4</v>
       </c>
@@ -1236,8 +1265,11 @@
       <c r="P10" s="28">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="2:59" ht="45" x14ac:dyDescent="0.25">
+      <c r="Q10" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:59" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B11" s="9" t="s">
         <v>5</v>
       </c>
@@ -1285,8 +1317,11 @@
       <c r="P11" s="28">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="2:59" x14ac:dyDescent="0.25">
+      <c r="Q11" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:59" x14ac:dyDescent="0.45">
       <c r="B12" s="9" t="s">
         <v>5</v>
       </c>
@@ -1313,8 +1348,11 @@
       <c r="P12" s="28">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="2:59" x14ac:dyDescent="0.25">
+      <c r="Q12" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:59" x14ac:dyDescent="0.45">
       <c r="B13" s="9" t="s">
         <v>5</v>
       </c>
@@ -1344,8 +1382,11 @@
       <c r="P13" s="28">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="14" spans="2:59" x14ac:dyDescent="0.25">
+      <c r="Q13" s="22">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="14" spans="2:59" x14ac:dyDescent="0.45">
       <c r="B14" s="9" t="s">
         <v>6</v>
       </c>
@@ -1391,8 +1432,11 @@
       <c r="P14" s="28">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="2:59" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q14" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:59" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B15" s="9" t="s">
         <v>6</v>
       </c>
@@ -1438,8 +1482,11 @@
       <c r="P15" s="28">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="16" spans="2:59" x14ac:dyDescent="0.25">
+      <c r="Q15" s="22">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:59" x14ac:dyDescent="0.45">
       <c r="B16" s="9" t="s">
         <v>7</v>
       </c>
@@ -1482,8 +1529,11 @@
       <c r="P16" s="28">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="17" spans="2:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q16" s="22">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B17" s="9" t="s">
         <v>7</v>
       </c>
@@ -1506,7 +1556,7 @@
       <c r="J17" s="23"/>
       <c r="P17" s="28"/>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B18" s="9" t="s">
         <v>7</v>
       </c>
@@ -1529,7 +1579,7 @@
       <c r="J18" s="23"/>
       <c r="P18" s="28"/>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B19" s="9" t="s">
         <v>7</v>
       </c>
@@ -1552,7 +1602,7 @@
       <c r="J19" s="23"/>
       <c r="P19" s="28"/>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B20" s="9" t="s">
         <v>7</v>
       </c>
@@ -1575,7 +1625,7 @@
       <c r="J20" s="23"/>
       <c r="P20" s="28"/>
     </row>
-    <row r="21" spans="2:16" ht="105" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:17" ht="85.5" x14ac:dyDescent="0.45">
       <c r="B21" s="9" t="s">
         <v>8</v>
       </c>
@@ -1616,8 +1666,11 @@
       <c r="P21" s="28">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="22" spans="2:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q21" s="22">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B22" s="9" t="s">
         <v>8</v>
       </c>
@@ -1655,8 +1708,11 @@
       <c r="P22" s="28">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q22" s="22">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B23" s="9" t="s">
         <v>8</v>
       </c>
@@ -1679,7 +1735,7 @@
       <c r="J23" s="23"/>
       <c r="P23" s="28"/>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B24" s="9" t="s">
         <v>8</v>
       </c>
@@ -1702,7 +1758,7 @@
       <c r="J24" s="23"/>
       <c r="P24" s="28"/>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B25" s="9" t="s">
         <v>8</v>
       </c>
@@ -1725,7 +1781,7 @@
       <c r="J25" s="23"/>
       <c r="P25" s="28"/>
     </row>
-    <row r="26" spans="2:16" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:17" ht="49.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B26" s="9" t="s">
         <v>2</v>
       </c>
@@ -1771,8 +1827,11 @@
       <c r="P26" s="28">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q26" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B27" s="9" t="s">
         <v>2</v>
       </c>
@@ -1805,8 +1864,11 @@
       <c r="P27" s="28">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q27" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B28" s="9" t="s">
         <v>2</v>
       </c>
@@ -1819,22 +1881,25 @@
       </c>
       <c r="F28" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>In Progess</v>
+        <v>Complete</v>
       </c>
       <c r="G28" s="10">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H28" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="9"/>
       <c r="J28" s="23"/>
       <c r="P28" s="28">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q28" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B29" s="9" t="s">
         <v>2</v>
       </c>
@@ -1847,9 +1912,11 @@
       </c>
       <c r="F29" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G29" s="10"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G29" s="10">
+        <v>0.1</v>
+      </c>
       <c r="H29" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1857,8 +1924,11 @@
       <c r="I29" s="9"/>
       <c r="J29" s="23"/>
       <c r="P29" s="28"/>
-    </row>
-    <row r="30" spans="2:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q29" s="22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B30" s="9" t="s">
         <v>9</v>
       </c>
@@ -1899,8 +1969,11 @@
       <c r="P30" s="28">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="31" spans="2:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q30" s="22">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B31" s="9" t="s">
         <v>9</v>
       </c>
@@ -1939,8 +2012,11 @@
       <c r="P31" s="28">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q31" s="22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B32" s="9" t="s">
         <v>9</v>
       </c>
@@ -1964,7 +2040,7 @@
       <c r="J32" s="23"/>
       <c r="P32" s="28"/>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B33" s="9" t="s">
         <v>9</v>
       </c>
@@ -1988,7 +2064,7 @@
       <c r="J33" s="23"/>
       <c r="P33" s="28"/>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B34" s="9" t="s">
         <v>9</v>
       </c>
@@ -2012,7 +2088,7 @@
       <c r="J34" s="23"/>
       <c r="P34" s="28"/>
     </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B35" s="9" t="s">
         <v>39</v>
       </c>
@@ -2056,8 +2132,11 @@
       <c r="P35" s="28">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q35" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B36" s="9" t="s">
         <v>39</v>
       </c>
@@ -2090,8 +2169,11 @@
       <c r="P36" s="28">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q36" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B37" s="9" t="s">
         <v>39</v>
       </c>
@@ -2121,8 +2203,11 @@
       <c r="P37" s="28">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="38" spans="2:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q37" s="22">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="38" spans="2:17" ht="57" x14ac:dyDescent="0.45">
       <c r="B38" s="9" t="s">
         <v>27</v>
       </c>
@@ -2168,8 +2253,11 @@
       <c r="P38" s="28">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q38" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B39" s="9" t="s">
         <v>27</v>
       </c>
@@ -2215,8 +2303,11 @@
       <c r="P39" s="28">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="2:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q39" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="2:17" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B40" s="9" t="s">
         <v>27</v>
       </c>
@@ -2264,8 +2355,11 @@
       <c r="P40" s="28">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="41" spans="2:16" ht="90" x14ac:dyDescent="0.25">
+      <c r="Q40" s="22">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="41" spans="2:17" ht="85.5" x14ac:dyDescent="0.45">
       <c r="B41" s="9" t="s">
         <v>10</v>
       </c>
@@ -2311,8 +2405,11 @@
       <c r="P41" s="28">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q41" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B42" s="7" t="s">
         <v>29</v>
       </c>
@@ -2356,8 +2453,11 @@
       <c r="P42" s="28">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q42" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B43" s="7" t="s">
         <v>11</v>
       </c>
@@ -2401,8 +2501,11 @@
       <c r="P43" s="28">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q43" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B44" s="7" t="s">
         <v>16</v>
       </c>
@@ -2446,8 +2549,11 @@
       <c r="P44" s="29">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="Q44" s="22">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B45" s="7" t="s">
         <v>16</v>
       </c>
@@ -2476,8 +2582,11 @@
       <c r="P45" s="29">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q45" s="22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B46" s="7" t="s">
         <v>17</v>
       </c>
@@ -2521,8 +2630,11 @@
       <c r="P46" s="29">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q46" s="22">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B47" s="7" t="s">
         <v>18</v>
       </c>
@@ -2566,8 +2678,11 @@
       <c r="P47" s="29">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="Q47" s="22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
         <v>59</v>
       </c>
@@ -2582,11 +2697,14 @@
         <v>In Progess</v>
       </c>
       <c r="G48" s="24">
-        <v>0.15</v>
+        <v>0.7</v>
       </c>
       <c r="H48" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
+      </c>
+      <c r="I48" t="s">
+        <v>73</v>
       </c>
       <c r="L48" s="22">
         <v>0</v>
@@ -2603,8 +2721,11 @@
       <c r="P48" s="24">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q48" s="22">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="49" spans="2:17" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
         <v>61</v>
       </c>
@@ -2635,6 +2756,9 @@
         <v>1</v>
       </c>
       <c r="P49" s="24">
+        <v>1</v>
+      </c>
+      <c r="Q49" s="22">
         <v>1</v>
       </c>
     </row>
@@ -2714,19 +2838,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23963325-1FFB-4B92-8120-662513F10342}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2931,15 +3052,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2964,18 +3097,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/ContinuationProject/Status.xlsx
+++ b/ContinuationProject/Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\ContinuationProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C7CBE0B-9658-4ED3-8B6C-ADF7568EB7AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1742E3-594E-4753-8A65-28C62BEB70C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="4" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="76">
   <si>
     <t>DISC DEXPI Continuation Project - Status</t>
   </si>
@@ -88,9 +88,6 @@
     <t>Extraction of remaining information from the Excel, Drawio, and SVG sources and inclusion in DiscProfile RC 1</t>
   </si>
   <si>
-    <t>Currently working on information model for constraints</t>
-  </si>
-  <si>
     <t>Blueprint file examples</t>
   </si>
   <si>
@@ -134,9 +131,6 @@
   </si>
   <si>
     <t>Convert existing blueprint examples to DEXPI 2.0</t>
-  </si>
-  <si>
-    <t>Create blueprint examples for new requirements in both serialization formats.</t>
   </si>
   <si>
     <t>Document verification method.</t>
@@ -176,12 +170,6 @@
     <t>Label addition to profile</t>
   </si>
   <si>
-    <t>Text rotation, Label position, Link to attributes</t>
-  </si>
-  <si>
-    <t>Model given OK from Aibel. Need list of component type from Aibel with RDL.</t>
-  </si>
-  <si>
     <t>Need to add qualifier type to standard ? Discuss with Aibel.</t>
   </si>
   <si>
@@ -220,9 +208,6 @@
     <t>Agreed with Aibel that rules for which sub-type to use will be project specific linked to specific function types.</t>
   </si>
   <si>
-    <t>Model prepared and will be presented during workshop.</t>
-  </si>
-  <si>
     <t>Challenge with battery-limits, these are often drafted using vendor limiting 'boxes' connected via nozzles and overlapping signal lines. 
 Suggest to separate out tie-ins from battery-limits.</t>
   </si>
@@ -263,19 +248,38 @@
 Node directions/type/position</t>
   </si>
   <si>
-    <t>Exact text positions - fine adjustments</t>
-  </si>
-  <si>
     <t>13.10.2025</t>
   </si>
   <si>
-    <t>Some issues with original files.</t>
-  </si>
-  <si>
-    <t>tonia to check drafting standard for ht</t>
-  </si>
-  <si>
     <t>20.10.2025</t>
+  </si>
+  <si>
+    <t>27.10.2025</t>
+  </si>
+  <si>
+    <t>Waiting on name suggestions for sub-types</t>
+  </si>
+  <si>
+    <t>Add sub-types to SignalConveyingFunction</t>
+  </si>
+  <si>
+    <t>Checking html symbol info, type code enum &amp; node type discussion, finish including description.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Default L-&gt;R for not in-line elements.
+L-&gt;R for in-line or B-&gt;T </t>
+  </si>
+  <si>
+    <t>Create blueprint examples for  requirements in both serialization formats.</t>
+  </si>
+  <si>
+    <t>Good model - need to warn about minimum length for symbol</t>
+  </si>
+  <si>
+    <t>Available in DEXPI 2.0 xml</t>
+  </si>
+  <si>
+    <t>Not needed as can be managed in DEXPI 2.0</t>
   </si>
 </sst>
 </file>
@@ -405,7 +409,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
@@ -475,6 +479,9 @@
     </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -832,29 +839,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825F216F-6A2C-43F0-976D-4459909E096A}">
   <dimension ref="B1:BG49"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.86328125" customWidth="1"/>
-    <col min="2" max="2" width="45.3984375" customWidth="1"/>
-    <col min="3" max="3" width="64.3984375" customWidth="1"/>
-    <col min="4" max="4" width="33.3984375" customWidth="1"/>
-    <col min="5" max="5" width="16.59765625" style="20" customWidth="1"/>
-    <col min="6" max="6" width="14.3984375" customWidth="1"/>
-    <col min="7" max="7" width="25.86328125" customWidth="1"/>
+    <col min="1" max="1" width="5.85546875" customWidth="1"/>
+    <col min="2" max="2" width="38.85546875" customWidth="1"/>
+    <col min="3" max="3" width="38.5703125" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" style="20" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" customWidth="1"/>
+    <col min="7" max="7" width="25.85546875" customWidth="1"/>
     <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="34" customWidth="1"/>
-    <col min="10" max="10" width="18.1328125" style="22" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="16.86328125" style="22" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="36.5703125" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" style="22" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="16.85546875" style="22" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="15" style="22" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="19.86328125" style="22" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="17.73046875" style="22" customWidth="1"/>
+    <col min="13" max="13" width="19.85546875" style="22" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="17.7109375" style="22" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="16" style="22" customWidth="1"/>
-    <col min="16" max="16" width="16.3984375" customWidth="1"/>
-    <col min="17" max="17" width="15.73046875" style="22" customWidth="1"/>
-    <col min="18" max="36" width="9.1328125" style="22"/>
+    <col min="16" max="16" width="16.42578125" customWidth="1"/>
+    <col min="17" max="17" width="15.7109375" style="22" customWidth="1"/>
+    <col min="18" max="18" width="19.140625" style="22" customWidth="1"/>
+    <col min="19" max="36" width="9.140625" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:59" ht="34.9" x14ac:dyDescent="0.9">
+    <row r="1" spans="2:59" ht="35.25" x14ac:dyDescent="0.5">
       <c r="B1" s="16" t="s">
         <v>0</v>
       </c>
@@ -867,7 +875,7 @@
       <c r="I1" s="6"/>
       <c r="P1" s="26"/>
     </row>
-    <row r="2" spans="2:59" ht="9" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="2" spans="2:59" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="6"/>
       <c r="D2" s="1"/>
       <c r="E2" s="17"/>
@@ -877,56 +885,58 @@
       <c r="I2" s="6"/>
       <c r="P2" s="26"/>
     </row>
-    <row r="3" spans="2:59" ht="19.5" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:59" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E3" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J3" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="K3" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="K3" s="21" t="s">
-        <v>54</v>
-      </c>
       <c r="L3" s="21" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="M3" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="O3" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="N3" s="21" t="s">
+      <c r="P3" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q3" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="O3" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="P3" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q3" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="R3" s="20"/>
+      <c r="R3" s="27" t="s">
+        <v>67</v>
+      </c>
       <c r="S3" s="20"/>
       <c r="T3" s="20"/>
       <c r="U3" s="20"/>
@@ -969,7 +979,7 @@
       <c r="BF3" s="20"/>
       <c r="BG3" s="20"/>
     </row>
-    <row r="4" spans="2:59" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:59" ht="90" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>12</v>
       </c>
@@ -977,7 +987,7 @@
         <v>13</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E4" s="19">
         <v>46010</v>
@@ -987,15 +997,13 @@
         <v>In Progess</v>
       </c>
       <c r="G4" s="10">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="H4" s="11">
         <f>--(G4&gt;=1)</f>
         <v>0</v>
       </c>
-      <c r="I4" s="9" t="s">
-        <v>15</v>
-      </c>
+      <c r="I4" s="9"/>
       <c r="J4" s="23">
         <v>0.3</v>
       </c>
@@ -1020,8 +1028,11 @@
       <c r="Q4" s="22">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="5" spans="2:59" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="R4" s="22">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="5" spans="2:59" ht="45" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
         <v>12</v>
       </c>
@@ -1070,13 +1081,16 @@
       <c r="Q5" s="22">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="6" spans="2:59" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="R5" s="22">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="6" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="19">
@@ -1093,9 +1107,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="I6" s="9" t="s">
-        <v>44</v>
-      </c>
+      <c r="I6" s="9"/>
       <c r="J6" s="23">
         <v>0.9</v>
       </c>
@@ -1120,13 +1132,16 @@
       <c r="Q6" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="2:59" x14ac:dyDescent="0.45">
+      <c r="R6" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="19">
@@ -1157,13 +1172,16 @@
       <c r="Q7" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="2:59" x14ac:dyDescent="0.45">
+      <c r="R7" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="19">
@@ -1194,13 +1212,16 @@
       <c r="Q8" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="2:59" x14ac:dyDescent="0.45">
+      <c r="R8" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="19">
@@ -1223,20 +1244,23 @@
       <c r="Q9" s="22">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="10" spans="2:59" x14ac:dyDescent="0.45">
+      <c r="R9" s="22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="19">
         <v>45909</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G10" s="10">
         <v>1</v>
@@ -1268,16 +1292,19 @@
       <c r="Q10" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="2:59" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="R10" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:59" ht="45" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E11" s="19">
         <v>45917</v>
@@ -1294,7 +1321,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="J11" s="23">
         <v>0.6</v>
@@ -1320,13 +1347,16 @@
       <c r="Q11" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="2:59" x14ac:dyDescent="0.45">
+      <c r="R11" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="19">
@@ -1351,13 +1381,16 @@
       <c r="Q12" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="2:59" x14ac:dyDescent="0.45">
+      <c r="R12" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="19">
@@ -1385,13 +1418,16 @@
       <c r="Q13" s="22">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="14" spans="2:59" x14ac:dyDescent="0.45">
+      <c r="R13" s="22">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="14" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B14" s="9" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D14" s="9"/>
       <c r="E14" s="19">
@@ -1409,7 +1445,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J14" s="23">
         <v>1</v>
@@ -1435,13 +1471,16 @@
       <c r="Q14" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="2:59" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="R14" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="19">
@@ -1459,7 +1498,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="J15" s="23">
         <v>0.7</v>
@@ -1485,13 +1524,16 @@
       <c r="Q15" s="22">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="16" spans="2:59" x14ac:dyDescent="0.45">
+      <c r="R15" s="22">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="16" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="19">
@@ -1502,11 +1544,14 @@
         <v>In Progess</v>
       </c>
       <c r="G16" s="10">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="H16" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
+      </c>
+      <c r="I16" s="30" t="s">
+        <v>74</v>
       </c>
       <c r="J16" s="23">
         <v>0.2</v>
@@ -1532,13 +1577,16 @@
       <c r="Q16" s="22">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="17" spans="2:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="R16" s="22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="19">
@@ -1546,22 +1594,30 @@
       </c>
       <c r="F17" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G17" s="10"/>
+        <v>Complete</v>
+      </c>
+      <c r="G17" s="10">
+        <v>1</v>
+      </c>
       <c r="H17" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I17" s="30" t="s">
+        <v>75</v>
       </c>
       <c r="J17" s="23"/>
       <c r="P17" s="28"/>
-    </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="R17" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="19">
@@ -1579,12 +1635,12 @@
       <c r="J18" s="23"/>
       <c r="P18" s="28"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="19">
@@ -1602,12 +1658,12 @@
       <c r="J19" s="23"/>
       <c r="P19" s="28"/>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="19">
@@ -1625,12 +1681,12 @@
       <c r="J20" s="23"/>
       <c r="P20" s="28"/>
     </row>
-    <row r="21" spans="2:17" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:18" ht="105" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="19">
@@ -1648,7 +1704,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="J21" s="23"/>
       <c r="L21" s="22">
@@ -1669,13 +1725,16 @@
       <c r="Q21" s="22">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="22" spans="2:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="R21" s="22">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="19">
@@ -1711,13 +1770,16 @@
       <c r="Q22" s="22">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="R22" s="22">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="19">
@@ -1735,12 +1797,12 @@
       <c r="J23" s="23"/>
       <c r="P23" s="28"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="19">
@@ -1758,12 +1820,12 @@
       <c r="J24" s="23"/>
       <c r="P24" s="28"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B25" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="19">
@@ -1781,12 +1843,12 @@
       <c r="J25" s="23"/>
       <c r="P25" s="28"/>
     </row>
-    <row r="26" spans="2:17" ht="49.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:18" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="9" t="s">
         <v>2</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="19">
@@ -1804,7 +1866,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="J26" s="23">
         <v>0.7</v>
@@ -1830,13 +1892,16 @@
       <c r="Q26" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="R26" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B27" s="9" t="s">
         <v>2</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D27" s="12"/>
       <c r="E27" s="19">
@@ -1867,13 +1932,16 @@
       <c r="Q27" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="R27" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
         <v>2</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="19">
@@ -1898,13 +1966,16 @@
       <c r="Q28" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="R28" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
         <v>2</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D29" s="12"/>
       <c r="E29" s="19">
@@ -1927,13 +1998,16 @@
       <c r="Q29" s="22">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="30" spans="2:17" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="R29" s="22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D30" s="9"/>
       <c r="E30" s="19">
@@ -1941,17 +2015,17 @@
       </c>
       <c r="F30" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>In Progess</v>
+        <v>Complete</v>
       </c>
       <c r="G30" s="10">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H30" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>57</v>
+        <v>1</v>
+      </c>
+      <c r="I30" t="s">
+        <v>69</v>
       </c>
       <c r="J30" s="23"/>
       <c r="L30" s="22">
@@ -1972,13 +2046,16 @@
       <c r="Q30" s="22">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="31" spans="2:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="R30" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="19">
@@ -1989,13 +2066,15 @@
         <v>In Progess</v>
       </c>
       <c r="G31" s="10">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="H31" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I31" s="9"/>
+      <c r="I31" s="9" t="s">
+        <v>68</v>
+      </c>
       <c r="J31" s="23"/>
       <c r="L31" s="22">
         <v>0.5</v>
@@ -2015,13 +2094,16 @@
       <c r="Q31" s="22">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="R31" s="22">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="19">
@@ -2029,9 +2111,11 @@
       </c>
       <c r="F32" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G32" s="10"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G32" s="10">
+        <v>0.15</v>
+      </c>
       <c r="H32" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2039,13 +2123,16 @@
       <c r="I32" s="9"/>
       <c r="J32" s="23"/>
       <c r="P32" s="28"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="R32" s="22">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B33" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D33" s="9"/>
       <c r="E33" s="19">
@@ -2064,12 +2151,12 @@
       <c r="J33" s="23"/>
       <c r="P33" s="28"/>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B34" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="19">
@@ -2088,12 +2175,12 @@
       <c r="J34" s="23"/>
       <c r="P34" s="28"/>
     </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B35" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D35" s="9"/>
       <c r="E35" s="19">
@@ -2135,13 +2222,16 @@
       <c r="Q35" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="R35" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B36" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="19">
@@ -2172,13 +2262,16 @@
       <c r="Q36" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="R36" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B37" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D37" s="12"/>
       <c r="E37" s="19">
@@ -2206,13 +2299,16 @@
       <c r="Q37" s="22">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="38" spans="2:17" ht="57" x14ac:dyDescent="0.45">
+      <c r="R37" s="22">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="38" spans="2:18" ht="90" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="19">
@@ -2230,7 +2326,7 @@
         <v>1</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="J38" s="23">
         <v>0.85</v>
@@ -2256,13 +2352,16 @@
       <c r="Q38" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="R38" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" ht="30" x14ac:dyDescent="0.25">
       <c r="B39" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D39" s="9"/>
       <c r="E39" s="19">
@@ -2280,7 +2379,7 @@
         <v>1</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J39" s="23">
         <v>0.8</v>
@@ -2306,16 +2405,19 @@
       <c r="Q39" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="2:17" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="R39" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="2:18" ht="30" x14ac:dyDescent="0.25">
       <c r="B40" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E40" s="19">
         <v>45973</v>
@@ -2332,7 +2434,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="J40" s="23">
         <v>0.2</v>
@@ -2358,13 +2460,16 @@
       <c r="Q40" s="22">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="41" spans="2:17" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="R40" s="22">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="41" spans="2:18" ht="90" x14ac:dyDescent="0.25">
       <c r="B41" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D41" s="12"/>
       <c r="E41" s="19">
@@ -2382,7 +2487,7 @@
         <v>1</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J41" s="23">
         <v>0.6</v>
@@ -2408,13 +2513,16 @@
       <c r="Q41" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="R41" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B42" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D42" s="7"/>
       <c r="E42" s="19">
@@ -2456,13 +2564,16 @@
       <c r="Q42" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="R42" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D43" s="7"/>
       <c r="E43" s="19">
@@ -2504,13 +2615,16 @@
       <c r="Q43" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="R43" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="19">
@@ -2552,13 +2666,16 @@
       <c r="Q44" s="22">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="R44" s="22">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" ht="45" x14ac:dyDescent="0.25">
       <c r="B45" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="19">
@@ -2566,18 +2683,16 @@
       </c>
       <c r="F45" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>In Progess</v>
+        <v>Complete</v>
       </c>
       <c r="G45" s="13">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="H45" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I45" s="9" t="s">
-        <v>72</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I45" s="9"/>
       <c r="J45" s="23"/>
       <c r="P45" s="29">
         <v>0.1</v>
@@ -2585,13 +2700,16 @@
       <c r="Q45" s="22">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="R45" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B46" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="19">
@@ -2633,13 +2751,16 @@
       <c r="Q46" s="22">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="R46" s="22">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="19">
@@ -2681,13 +2802,16 @@
       <c r="Q47" s="22">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="R47" s="22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" ht="45" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E48" s="20">
         <v>46010</v>
@@ -2697,7 +2821,7 @@
         <v>In Progess</v>
       </c>
       <c r="G48" s="24">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H48" s="25">
         <f t="shared" si="1"/>
@@ -2724,13 +2848,16 @@
       <c r="Q48" s="22">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="49" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="R48" s="22">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="49" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E49" s="20">
         <v>45918</v>
@@ -2759,6 +2886,9 @@
         <v>1</v>
       </c>
       <c r="Q49" s="22">
+        <v>1</v>
+      </c>
+      <c r="R49" s="22">
         <v>1</v>
       </c>
     </row>
@@ -2838,16 +2968,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23963325-1FFB-4B92-8120-662513F10342}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3052,27 +3185,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3097,9 +3218,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/ContinuationProject/Status.xlsx
+++ b/ContinuationProject/Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\ContinuationProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1742E3-594E-4753-8A65-28C62BEB70C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66AC240B-B60B-4712-8AA0-BE04885A0148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="4" r:id="rId1"/>
@@ -409,7 +409,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
@@ -479,9 +479,6 @@
     </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -845,9 +842,9 @@
     <col min="2" max="2" width="38.85546875" customWidth="1"/>
     <col min="3" max="3" width="38.5703125" customWidth="1"/>
     <col min="4" max="4" width="19.28515625" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" style="20" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="20" customWidth="1"/>
     <col min="6" max="6" width="14.42578125" customWidth="1"/>
-    <col min="7" max="7" width="25.85546875" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" customWidth="1"/>
     <col min="8" max="8" width="7" customWidth="1"/>
     <col min="9" max="9" width="36.5703125" customWidth="1"/>
     <col min="10" max="10" width="18.140625" style="22" hidden="1" customWidth="1"/>
@@ -855,7 +852,7 @@
     <col min="12" max="12" width="15" style="22" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="19.85546875" style="22" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="17.7109375" style="22" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="16" style="22" customWidth="1"/>
+    <col min="15" max="15" width="16" style="22" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="16.42578125" customWidth="1"/>
     <col min="17" max="17" width="15.7109375" style="22" customWidth="1"/>
     <col min="18" max="18" width="19.140625" style="22" customWidth="1"/>
@@ -1225,7 +1222,7 @@
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="19">
-        <v>45870</v>
+        <v>45962</v>
       </c>
       <c r="F9" s="9" t="str">
         <f t="shared" si="0"/>
@@ -1550,7 +1547,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I16" s="30" t="s">
+      <c r="I16" s="6" t="s">
         <v>74</v>
       </c>
       <c r="J16" s="23">
@@ -1603,7 +1600,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="I17" s="30" t="s">
+      <c r="I17" s="6" t="s">
         <v>75</v>
       </c>
       <c r="J17" s="23"/>
@@ -1774,7 +1771,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:18" ht="30" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
         <v>8</v>
       </c>
@@ -1783,7 +1780,7 @@
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="19">
-        <v>45922</v>
+        <v>45952</v>
       </c>
       <c r="F23" s="9" t="str">
         <f t="shared" si="0"/>
@@ -1806,7 +1803,7 @@
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="19">
-        <v>45929</v>
+        <v>45959</v>
       </c>
       <c r="F24" s="9" t="str">
         <f t="shared" si="0"/>
@@ -1829,7 +1826,7 @@
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="19">
-        <v>45936</v>
+        <v>45967</v>
       </c>
       <c r="F25" s="9" t="str">
         <f t="shared" si="0"/>
@@ -1979,7 +1976,7 @@
       </c>
       <c r="D29" s="12"/>
       <c r="E29" s="19">
-        <v>45929</v>
+        <v>45959</v>
       </c>
       <c r="F29" s="9" t="str">
         <f t="shared" si="0"/>
@@ -2175,7 +2172,7 @@
       <c r="J34" s="23"/>
       <c r="P34" s="28"/>
     </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:18" ht="30" x14ac:dyDescent="0.25">
       <c r="B35" s="9" t="s">
         <v>37</v>
       </c>
@@ -2303,7 +2300,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="38" spans="2:18" ht="90" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:18" ht="75" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="s">
         <v>26</v>
       </c>
@@ -2356,7 +2353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="2:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B39" s="9" t="s">
         <v>26</v>
       </c>
@@ -2517,7 +2514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:18" ht="30" x14ac:dyDescent="0.25">
       <c r="B42" s="7" t="s">
         <v>28</v>
       </c>
@@ -2619,7 +2616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:18" ht="30" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
         <v>15</v>
       </c>
@@ -2755,7 +2752,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:18" ht="30" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
         <v>17</v>
       </c>
@@ -2975,12 +2972,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3185,15 +3179,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3218,18 +3224,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/ContinuationProject/Status.xlsx
+++ b/ContinuationProject/Status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\ContinuationProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\DISCDEXPI\ContinuationProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66AC240B-B60B-4712-8AA0-BE04885A0148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B70D159B-EEF6-4E6C-B883-09DA81377881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="4" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="78">
   <si>
     <t>DISC DEXPI Continuation Project - Status</t>
   </si>
@@ -149,13 +149,6 @@
   </si>
   <si>
     <t>Automate conversion and add to profile</t>
-  </si>
-  <si>
-    <t>Missing:
-Equipment connected to motor
-Thermowell as Sensorwell
-Proteus example for CustomInlineMeasuringElement
-DEXPI 2.0 examples</t>
   </si>
   <si>
     <t>Motor - Equipment Linking</t>
@@ -257,9 +250,6 @@
     <t>27.10.2025</t>
   </si>
   <si>
-    <t>Waiting on name suggestions for sub-types</t>
-  </si>
-  <si>
     <t>Add sub-types to SignalConveyingFunction</t>
   </si>
   <si>
@@ -273,13 +263,25 @@
     <t>Create blueprint examples for  requirements in both serialization formats.</t>
   </si>
   <si>
-    <t>Good model - need to warn about minimum length for symbol</t>
-  </si>
-  <si>
     <t>Available in DEXPI 2.0 xml</t>
   </si>
   <si>
     <t>Not needed as can be managed in DEXPI 2.0</t>
+  </si>
+  <si>
+    <t>03.11.2025</t>
+  </si>
+  <si>
+    <t>Line styles to be added.</t>
+  </si>
+  <si>
+    <t>Issue fixed from old versions in-progress</t>
+  </si>
+  <si>
+    <t>Keep as is with no new sub-types</t>
+  </si>
+  <si>
+    <t>Tonia to submit to Content team.</t>
   </si>
 </sst>
 </file>
@@ -840,7 +842,7 @@
   <cols>
     <col min="1" max="1" width="5.85546875" customWidth="1"/>
     <col min="2" max="2" width="38.85546875" customWidth="1"/>
-    <col min="3" max="3" width="38.5703125" customWidth="1"/>
+    <col min="3" max="3" width="56.7109375" customWidth="1"/>
     <col min="4" max="4" width="19.28515625" customWidth="1"/>
     <col min="5" max="5" width="14.5703125" style="20" customWidth="1"/>
     <col min="6" max="6" width="14.42578125" customWidth="1"/>
@@ -853,10 +855,11 @@
     <col min="13" max="13" width="19.85546875" style="22" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="17.7109375" style="22" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="16" style="22" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="16.42578125" customWidth="1"/>
+    <col min="16" max="16" width="16.42578125" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="15.7109375" style="22" customWidth="1"/>
     <col min="18" max="18" width="19.140625" style="22" customWidth="1"/>
-    <col min="19" max="36" width="9.140625" style="22"/>
+    <col min="19" max="19" width="15.42578125" style="22" customWidth="1"/>
+    <col min="20" max="36" width="9.140625" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:59" ht="35.25" x14ac:dyDescent="0.5">
@@ -893,48 +896,50 @@
         <v>34</v>
       </c>
       <c r="E3" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>43</v>
-      </c>
       <c r="K3" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="L3" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="L3" s="21" t="s">
-        <v>51</v>
-      </c>
       <c r="M3" s="21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P3" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q3" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="Q3" s="27" t="s">
+      <c r="R3" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="S3" s="20"/>
+      <c r="S3" s="27" t="s">
+        <v>73</v>
+      </c>
       <c r="T3" s="20"/>
       <c r="U3" s="20"/>
       <c r="V3" s="20"/>
@@ -984,7 +989,7 @@
         <v>13</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E4" s="19">
         <v>46010</v>
@@ -1000,7 +1005,9 @@
         <f>--(G4&gt;=1)</f>
         <v>0</v>
       </c>
-      <c r="I4" s="9"/>
+      <c r="I4" s="9" t="s">
+        <v>74</v>
+      </c>
       <c r="J4" s="23">
         <v>0.3</v>
       </c>
@@ -1026,6 +1033,9 @@
         <v>0.85</v>
       </c>
       <c r="R4" s="22">
+        <v>0.9</v>
+      </c>
+      <c r="S4" s="22">
         <v>0.9</v>
       </c>
     </row>
@@ -1045,14 +1055,14 @@
         <v>In Progess</v>
       </c>
       <c r="G5" s="10">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="H5" s="11">
         <f t="shared" ref="H5:H49" si="1">--(G5&gt;=1)</f>
         <v>0</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J5" s="23">
         <v>0.75</v>
@@ -1080,6 +1090,9 @@
       </c>
       <c r="R5" s="22">
         <v>0.95</v>
+      </c>
+      <c r="S5" s="22">
+        <v>0.97</v>
       </c>
     </row>
     <row r="6" spans="2:59" ht="30" x14ac:dyDescent="0.25">
@@ -1130,6 +1143,9 @@
         <v>1</v>
       </c>
       <c r="R6" s="22">
+        <v>1</v>
+      </c>
+      <c r="S6" s="22">
         <v>1</v>
       </c>
     </row>
@@ -1172,6 +1188,9 @@
       <c r="R7" s="22">
         <v>1</v>
       </c>
+      <c r="S7" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
@@ -1212,8 +1231,11 @@
       <c r="R8" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="2:59" x14ac:dyDescent="0.25">
+      <c r="S8" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
         <v>3</v>
       </c>
@@ -1229,13 +1251,15 @@
         <v>In Progess</v>
       </c>
       <c r="G9" s="10">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H9" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I9" s="9"/>
+      <c r="I9" s="9" t="s">
+        <v>75</v>
+      </c>
       <c r="J9" s="23"/>
       <c r="P9" s="28"/>
       <c r="Q9" s="22">
@@ -1244,6 +1268,9 @@
       <c r="R9" s="22">
         <v>0.1</v>
       </c>
+      <c r="S9" s="22">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="10" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
@@ -1257,7 +1284,7 @@
         <v>45909</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G10" s="10">
         <v>1</v>
@@ -1292,6 +1319,9 @@
       <c r="R10" s="22">
         <v>1</v>
       </c>
+      <c r="S10" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="2:59" ht="45" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
@@ -1301,7 +1331,7 @@
         <v>21</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E11" s="19">
         <v>45917</v>
@@ -1318,7 +1348,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J11" s="23">
         <v>0.6</v>
@@ -1345,6 +1375,9 @@
         <v>1</v>
       </c>
       <c r="R11" s="22">
+        <v>1</v>
+      </c>
+      <c r="S11" s="22">
         <v>1</v>
       </c>
     </row>
@@ -1381,8 +1414,11 @@
       <c r="R12" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="2:59" x14ac:dyDescent="0.25">
+      <c r="S12" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>5</v>
       </c>
@@ -1404,7 +1440,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I13" s="9"/>
+      <c r="I13" s="9" t="s">
+        <v>75</v>
+      </c>
       <c r="J13" s="23"/>
       <c r="O13" s="22">
         <v>0.4</v>
@@ -1418,13 +1456,16 @@
       <c r="R13" s="22">
         <v>0.15</v>
       </c>
+      <c r="S13" s="22">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="14" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B14" s="9" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" s="9"/>
       <c r="E14" s="19">
@@ -1442,7 +1483,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J14" s="23">
         <v>1</v>
@@ -1469,6 +1510,9 @@
         <v>1</v>
       </c>
       <c r="R14" s="22">
+        <v>1</v>
+      </c>
+      <c r="S14" s="22">
         <v>1</v>
       </c>
     </row>
@@ -1495,7 +1539,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J15" s="23">
         <v>0.7</v>
@@ -1522,6 +1566,9 @@
         <v>0.7</v>
       </c>
       <c r="R15" s="22">
+        <v>0.7</v>
+      </c>
+      <c r="S15" s="22">
         <v>0.7</v>
       </c>
     </row>
@@ -1548,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J16" s="23">
         <v>0.2</v>
@@ -1577,8 +1624,11 @@
       <c r="R16" s="22">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="17" spans="2:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S16" s="22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>7</v>
       </c>
@@ -1601,15 +1651,18 @@
         <v>1</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J17" s="23"/>
       <c r="P17" s="28"/>
       <c r="R17" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S17" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
         <v>7</v>
       </c>
@@ -1632,7 +1685,7 @@
       <c r="J18" s="23"/>
       <c r="P18" s="28"/>
     </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
         <v>7</v>
       </c>
@@ -1655,7 +1708,7 @@
       <c r="J19" s="23"/>
       <c r="P19" s="28"/>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>7</v>
       </c>
@@ -1678,7 +1731,7 @@
       <c r="J20" s="23"/>
       <c r="P20" s="28"/>
     </row>
-    <row r="21" spans="2:18" ht="105" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:19" ht="105" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
         <v>8</v>
       </c>
@@ -1701,7 +1754,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J21" s="23"/>
       <c r="L21" s="22">
@@ -1725,8 +1778,11 @@
       <c r="R21" s="22">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="22" spans="2:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S21" s="22">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="22" spans="2:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
         <v>8</v>
       </c>
@@ -1770,8 +1826,11 @@
       <c r="R22" s="22">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="23" spans="2:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="S22" s="22">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:19" ht="30" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
         <v>8</v>
       </c>
@@ -1794,7 +1853,7 @@
       <c r="J23" s="23"/>
       <c r="P23" s="28"/>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
         <v>8</v>
       </c>
@@ -1817,7 +1876,7 @@
       <c r="J24" s="23"/>
       <c r="P24" s="28"/>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B25" s="9" t="s">
         <v>8</v>
       </c>
@@ -1840,7 +1899,7 @@
       <c r="J25" s="23"/>
       <c r="P25" s="28"/>
     </row>
-    <row r="26" spans="2:18" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:19" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="9" t="s">
         <v>2</v>
       </c>
@@ -1863,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J26" s="23">
         <v>0.7</v>
@@ -1892,8 +1951,11 @@
       <c r="R26" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S26" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B27" s="9" t="s">
         <v>2</v>
       </c>
@@ -1932,8 +1994,11 @@
       <c r="R27" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S27" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
         <v>2</v>
       </c>
@@ -1966,8 +2031,11 @@
       <c r="R28" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S28" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
         <v>2</v>
       </c>
@@ -1980,14 +2048,14 @@
       </c>
       <c r="F29" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>In Progess</v>
+        <v>Complete</v>
       </c>
       <c r="G29" s="10">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="H29" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" s="9"/>
       <c r="J29" s="23"/>
@@ -1998,8 +2066,11 @@
       <c r="R29" s="22">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S29" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B30" s="9" t="s">
         <v>9</v>
       </c>
@@ -2022,7 +2093,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J30" s="23"/>
       <c r="L30" s="22">
@@ -2046,8 +2117,11 @@
       <c r="R30" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="2:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S30" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="9" t="s">
         <v>9</v>
       </c>
@@ -2060,17 +2134,17 @@
       </c>
       <c r="F31" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>In Progess</v>
+        <v>Complete</v>
       </c>
       <c r="G31" s="10">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="H31" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="J31" s="23"/>
       <c r="L31" s="22">
@@ -2094,8 +2168,11 @@
       <c r="R31" s="22">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S31" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B32" s="9" t="s">
         <v>9</v>
       </c>
@@ -2108,14 +2185,14 @@
       </c>
       <c r="F32" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>In Progess</v>
+        <v>Complete</v>
       </c>
       <c r="G32" s="10">
-        <v>0.15</v>
+        <v>1</v>
       </c>
       <c r="H32" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" s="9"/>
       <c r="J32" s="23"/>
@@ -2123,8 +2200,11 @@
       <c r="R32" s="22">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S32" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B33" s="9" t="s">
         <v>9</v>
       </c>
@@ -2137,18 +2217,23 @@
       </c>
       <c r="F33" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G33" s="10"/>
+        <v>Complete</v>
+      </c>
+      <c r="G33" s="10">
+        <v>1</v>
+      </c>
       <c r="H33" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" s="9"/>
       <c r="J33" s="23"/>
       <c r="P33" s="28"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S33" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B34" s="9" t="s">
         <v>9</v>
       </c>
@@ -2161,20 +2246,25 @@
       </c>
       <c r="F34" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G34" s="10"/>
+        <v>Complete</v>
+      </c>
+      <c r="G34" s="10">
+        <v>1</v>
+      </c>
       <c r="H34" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" s="9"/>
       <c r="J34" s="23"/>
       <c r="P34" s="28"/>
-    </row>
-    <row r="35" spans="2:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="S34" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" ht="30" x14ac:dyDescent="0.25">
       <c r="B35" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>21</v>
@@ -2222,10 +2312,13 @@
       <c r="R35" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S35" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B36" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>22</v>
@@ -2262,10 +2355,13 @@
       <c r="R36" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S36" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B37" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>23</v>
@@ -2299,13 +2395,16 @@
       <c r="R37" s="22">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="38" spans="2:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="S37" s="22">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="38" spans="2:19" ht="75" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="s">
         <v>26</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="19">
@@ -2323,7 +2422,7 @@
         <v>1</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J38" s="23">
         <v>0.85</v>
@@ -2352,8 +2451,11 @@
       <c r="R38" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S38" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B39" s="9" t="s">
         <v>26</v>
       </c>
@@ -2405,16 +2507,19 @@
       <c r="R39" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="2:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="S39" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="2:19" ht="30" x14ac:dyDescent="0.25">
       <c r="B40" s="9" t="s">
         <v>26</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E40" s="19">
         <v>45973</v>
@@ -2431,7 +2536,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J40" s="23">
         <v>0.2</v>
@@ -2460,8 +2565,11 @@
       <c r="R40" s="22">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="41" spans="2:18" ht="90" x14ac:dyDescent="0.25">
+      <c r="S40" s="22">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B41" s="9" t="s">
         <v>10</v>
       </c>
@@ -2483,9 +2591,7 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="I41" s="9" t="s">
-        <v>36</v>
-      </c>
+      <c r="I41" s="9"/>
       <c r="J41" s="23">
         <v>0.6</v>
       </c>
@@ -2513,8 +2619,11 @@
       <c r="R41" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="S41" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" ht="30" x14ac:dyDescent="0.25">
       <c r="B42" s="7" t="s">
         <v>28</v>
       </c>
@@ -2564,8 +2673,11 @@
       <c r="R42" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S42" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
         <v>11</v>
       </c>
@@ -2615,8 +2727,11 @@
       <c r="R43" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="S43" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" ht="30" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
         <v>15</v>
       </c>
@@ -2666,13 +2781,16 @@
       <c r="R44" s="22">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="S44" s="22">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" ht="45" x14ac:dyDescent="0.25">
       <c r="B45" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="19">
@@ -2700,8 +2818,11 @@
       <c r="R45" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S45" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B46" s="7" t="s">
         <v>16</v>
       </c>
@@ -2751,8 +2872,11 @@
       <c r="R46" s="22">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" ht="30" x14ac:dyDescent="0.25">
+      <c r="S46" s="22">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" ht="30" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
         <v>17</v>
       </c>
@@ -2802,13 +2926,16 @@
       <c r="R47" s="22">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="S47" s="22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" ht="45" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="E48" s="20">
         <v>46010</v>
@@ -2818,14 +2945,14 @@
         <v>In Progess</v>
       </c>
       <c r="G48" s="24">
-        <v>0.8</v>
+        <v>0.98</v>
       </c>
       <c r="H48" s="25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I48" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L48" s="22">
         <v>0</v>
@@ -2848,13 +2975,16 @@
       <c r="R48" s="22">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="49" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="S48" s="22">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="49" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
+        <v>55</v>
+      </c>
+      <c r="C49" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="E49" s="20">
         <v>45918</v>
@@ -2886,6 +3016,9 @@
         <v>1</v>
       </c>
       <c r="R49" s="22">
+        <v>1</v>
+      </c>
+      <c r="S49" s="22">
         <v>1</v>
       </c>
     </row>
@@ -2972,9 +3105,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3179,27 +3315,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3224,9 +3348,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/ContinuationProject/Status.xlsx
+++ b/ContinuationProject/Status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\DISCDEXPI\ContinuationProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B70D159B-EEF6-4E6C-B883-09DA81377881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CD6E28-4EAE-4DCE-95CF-F403904ACF5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
   </bookViews>
@@ -250,9 +250,6 @@
     <t>27.10.2025</t>
   </si>
   <si>
-    <t>Add sub-types to SignalConveyingFunction</t>
-  </si>
-  <si>
     <t>Checking html symbol info, type code enum &amp; node type discussion, finish including description.</t>
   </si>
   <si>
@@ -281,7 +278,10 @@
     <t>Keep as is with no new sub-types</t>
   </si>
   <si>
-    <t>Tonia to submit to Content team.</t>
+    <t>Not needed .. Use type attribute</t>
+  </si>
+  <si>
+    <t>No definition required in profile</t>
   </si>
 </sst>
 </file>
@@ -938,7 +938,7 @@
         <v>66</v>
       </c>
       <c r="S3" s="27" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T3" s="20"/>
       <c r="U3" s="20"/>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J4" s="23">
         <v>0.3</v>
@@ -1062,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J5" s="23">
         <v>0.75</v>
@@ -1258,7 +1258,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J9" s="23"/>
       <c r="P9" s="28"/>
@@ -1434,14 +1434,14 @@
         <v>In Progess</v>
       </c>
       <c r="G13" s="10">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="H13" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J13" s="23"/>
       <c r="O13" s="22">
@@ -1457,7 +1457,7 @@
         <v>0.15</v>
       </c>
       <c r="S13" s="22">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="14" spans="2:59" x14ac:dyDescent="0.25">
@@ -1595,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J16" s="23">
         <v>0.2</v>
@@ -1651,7 +1651,7 @@
         <v>1</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J17" s="23"/>
       <c r="P17" s="28"/>
@@ -1675,15 +1675,20 @@
       </c>
       <c r="F18" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G18" s="10"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G18" s="10">
+        <v>0.15</v>
+      </c>
       <c r="H18" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J18" s="23"/>
       <c r="P18" s="28"/>
+      <c r="S18" s="22">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
@@ -1698,15 +1703,23 @@
       </c>
       <c r="F19" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G19" s="10"/>
+        <v>Complete</v>
+      </c>
+      <c r="G19" s="10">
+        <v>1</v>
+      </c>
       <c r="H19" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="J19" s="23"/>
       <c r="P19" s="28"/>
+      <c r="S19" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
@@ -1721,15 +1734,20 @@
       </c>
       <c r="F20" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G20" s="10"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G20" s="10">
+        <v>0.2</v>
+      </c>
       <c r="H20" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J20" s="23"/>
       <c r="P20" s="28"/>
+      <c r="S20" s="22">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="21" spans="2:19" ht="105" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
@@ -2093,7 +2111,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="J30" s="23"/>
       <c r="L30" s="22">
@@ -2144,7 +2162,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J31" s="23"/>
       <c r="L31" s="22">
@@ -2536,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J40" s="23">
         <v>0.2</v>
@@ -2790,7 +2808,7 @@
         <v>15</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="19">
@@ -2892,7 +2910,7 @@
         <v>In Progess</v>
       </c>
       <c r="G47" s="13">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H47" s="11">
         <f t="shared" si="1"/>
@@ -2927,7 +2945,7 @@
         <v>0.5</v>
       </c>
       <c r="S47" s="22">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="48" spans="2:19" ht="45" x14ac:dyDescent="0.25">
@@ -2942,17 +2960,14 @@
       </c>
       <c r="F48" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>In Progess</v>
+        <v>Complete</v>
       </c>
       <c r="G48" s="24">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="H48" s="25">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I48" t="s">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="L48" s="22">
         <v>0</v>
@@ -2976,7 +2991,7 @@
         <v>0.8</v>
       </c>
       <c r="S48" s="22">
-        <v>0.98</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:19" x14ac:dyDescent="0.25">
@@ -3105,12 +3120,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3315,15 +3327,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3348,18 +3372,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/ContinuationProject/Status.xlsx
+++ b/ContinuationProject/Status.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\DISCDEXPI\ContinuationProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\ContinuationProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CD6E28-4EAE-4DCE-95CF-F403904ACF5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{164970BF-6145-4C88-A3F9-2A48DDDB460E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="81">
   <si>
     <t>DISC DEXPI Continuation Project - Status</t>
   </si>
@@ -250,9 +250,6 @@
     <t>27.10.2025</t>
   </si>
   <si>
-    <t>Checking html symbol info, type code enum &amp; node type discussion, finish including description.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Default L-&gt;R for not in-line elements.
 L-&gt;R for in-line or B-&gt;T </t>
   </si>
@@ -282,6 +279,18 @@
   </si>
   <si>
     <t>No definition required in profile</t>
+  </si>
+  <si>
+    <t>10.11.2025</t>
+  </si>
+  <si>
+    <t>Checking html symbol info, attr. Desc, FillLevel</t>
+  </si>
+  <si>
+    <t>Not yet pushed .. Persistent id missing</t>
+  </si>
+  <si>
+    <t>Persistant ID</t>
   </si>
 </sst>
 </file>
@@ -489,7 +498,7 @@
     <cellStyle name="Heading 1" xfId="3" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="4" builtinId="17"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
     <cellStyle name="Title" xfId="2" builtinId="15"/>
   </cellStyles>
   <dxfs count="1">
@@ -841,7 +850,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.85546875" customWidth="1"/>
-    <col min="2" max="2" width="38.85546875" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" customWidth="1"/>
     <col min="3" max="3" width="56.7109375" customWidth="1"/>
     <col min="4" max="4" width="19.28515625" customWidth="1"/>
     <col min="5" max="5" width="14.5703125" style="20" customWidth="1"/>
@@ -859,7 +868,8 @@
     <col min="17" max="17" width="15.7109375" style="22" customWidth="1"/>
     <col min="18" max="18" width="19.140625" style="22" customWidth="1"/>
     <col min="19" max="19" width="15.42578125" style="22" customWidth="1"/>
-    <col min="20" max="36" width="9.140625" style="22"/>
+    <col min="20" max="20" width="20.28515625" style="22" customWidth="1"/>
+    <col min="21" max="36" width="9.140625" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:59" ht="35.25" x14ac:dyDescent="0.5">
@@ -938,9 +948,11 @@
         <v>66</v>
       </c>
       <c r="S3" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="T3" s="20"/>
+        <v>71</v>
+      </c>
+      <c r="T3" s="27" t="s">
+        <v>77</v>
+      </c>
       <c r="U3" s="20"/>
       <c r="V3" s="20"/>
       <c r="W3" s="20"/>
@@ -999,14 +1011,14 @@
         <v>In Progess</v>
       </c>
       <c r="G4" s="10">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="H4" s="11">
         <f>--(G4&gt;=1)</f>
         <v>0</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J4" s="23">
         <v>0.3</v>
@@ -1038,8 +1050,11 @@
       <c r="S4" s="22">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="5" spans="2:59" ht="45" x14ac:dyDescent="0.25">
+      <c r="T4" s="22">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="5" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
         <v>12</v>
       </c>
@@ -1055,14 +1070,14 @@
         <v>In Progess</v>
       </c>
       <c r="G5" s="10">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="H5" s="11">
         <f t="shared" ref="H5:H49" si="1">--(G5&gt;=1)</f>
         <v>0</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="J5" s="23">
         <v>0.75</v>
@@ -1093,6 +1108,9 @@
       </c>
       <c r="S5" s="22">
         <v>0.97</v>
+      </c>
+      <c r="T5" s="22">
+        <v>0.98</v>
       </c>
     </row>
     <row r="6" spans="2:59" ht="30" x14ac:dyDescent="0.25">
@@ -1148,8 +1166,11 @@
       <c r="S6" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="2:59" x14ac:dyDescent="0.25">
+      <c r="T6" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
         <v>3</v>
       </c>
@@ -1191,6 +1212,9 @@
       <c r="S7" s="22">
         <v>1</v>
       </c>
+      <c r="T7" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
@@ -1234,6 +1258,9 @@
       <c r="S8" s="22">
         <v>1</v>
       </c>
+      <c r="T8" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
@@ -1251,14 +1278,14 @@
         <v>In Progess</v>
       </c>
       <c r="G9" s="10">
-        <v>0.2</v>
+        <v>0.95</v>
       </c>
       <c r="H9" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J9" s="23"/>
       <c r="P9" s="28"/>
@@ -1271,6 +1298,9 @@
       <c r="S9" s="22">
         <v>0.2</v>
       </c>
+      <c r="T9" s="22">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="10" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
@@ -1322,6 +1352,9 @@
       <c r="S10" s="22">
         <v>1</v>
       </c>
+      <c r="T10" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="2:59" ht="45" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
@@ -1380,6 +1413,9 @@
       <c r="S11" s="22">
         <v>1</v>
       </c>
+      <c r="T11" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
@@ -1417,6 +1453,9 @@
       <c r="S12" s="22">
         <v>1</v>
       </c>
+      <c r="T12" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
@@ -1441,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J13" s="23"/>
       <c r="O13" s="22">
@@ -1459,6 +1498,9 @@
       <c r="S13" s="22">
         <v>0.2</v>
       </c>
+      <c r="T13" s="22">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="14" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B14" s="9" t="s">
@@ -1515,6 +1557,9 @@
       <c r="S14" s="22">
         <v>1</v>
       </c>
+      <c r="T14" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
@@ -1571,6 +1616,9 @@
       <c r="S15" s="22">
         <v>0.7</v>
       </c>
+      <c r="T15" s="22">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="16" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
@@ -1595,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J16" s="23">
         <v>0.2</v>
@@ -1627,8 +1675,11 @@
       <c r="S16" s="22">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="17" spans="2:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T16" s="22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>7</v>
       </c>
@@ -1651,7 +1702,7 @@
         <v>1</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J17" s="23"/>
       <c r="P17" s="28"/>
@@ -1661,8 +1712,11 @@
       <c r="S17" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T17" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
         <v>7</v>
       </c>
@@ -1689,8 +1743,11 @@
       <c r="S18" s="22">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T18" s="22">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
         <v>7</v>
       </c>
@@ -1713,15 +1770,18 @@
         <v>1</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J19" s="23"/>
       <c r="P19" s="28"/>
       <c r="S19" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T19" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>7</v>
       </c>
@@ -1748,8 +1808,11 @@
       <c r="S20" s="22">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="21" spans="2:19" ht="105" x14ac:dyDescent="0.25">
+      <c r="T20" s="22">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:20" ht="105" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
         <v>8</v>
       </c>
@@ -1799,8 +1862,11 @@
       <c r="S21" s="22">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="22" spans="2:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T21" s="22">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="22" spans="2:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
         <v>8</v>
       </c>
@@ -1816,7 +1882,7 @@
         <v>In Progess</v>
       </c>
       <c r="G22" s="10">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="H22" s="11">
         <f t="shared" si="1"/>
@@ -1847,8 +1913,11 @@
       <c r="S22" s="22">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="23" spans="2:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T22" s="22">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="23" spans="2:20" ht="30" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
         <v>8</v>
       </c>
@@ -1871,7 +1940,7 @@
       <c r="J23" s="23"/>
       <c r="P23" s="28"/>
     </row>
-    <row r="24" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
         <v>8</v>
       </c>
@@ -1894,7 +1963,7 @@
       <c r="J24" s="23"/>
       <c r="P24" s="28"/>
     </row>
-    <row r="25" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B25" s="9" t="s">
         <v>8</v>
       </c>
@@ -1917,7 +1986,7 @@
       <c r="J25" s="23"/>
       <c r="P25" s="28"/>
     </row>
-    <row r="26" spans="2:19" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:20" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="9" t="s">
         <v>2</v>
       </c>
@@ -1972,8 +2041,11 @@
       <c r="S26" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T26" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B27" s="9" t="s">
         <v>2</v>
       </c>
@@ -2015,8 +2087,11 @@
       <c r="S27" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T27" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
         <v>2</v>
       </c>
@@ -2052,8 +2127,11 @@
       <c r="S28" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T28" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
         <v>2</v>
       </c>
@@ -2087,8 +2165,11 @@
       <c r="S29" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T29" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B30" s="9" t="s">
         <v>9</v>
       </c>
@@ -2111,7 +2192,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J30" s="23"/>
       <c r="L30" s="22">
@@ -2138,8 +2219,11 @@
       <c r="S30" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="2:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T30" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="9" t="s">
         <v>9</v>
       </c>
@@ -2162,7 +2246,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J31" s="23"/>
       <c r="L31" s="22">
@@ -2189,8 +2273,11 @@
       <c r="S31" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T31" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B32" s="9" t="s">
         <v>9</v>
       </c>
@@ -2221,8 +2308,11 @@
       <c r="S32" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T32" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B33" s="9" t="s">
         <v>9</v>
       </c>
@@ -2250,8 +2340,11 @@
       <c r="S33" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T33" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B34" s="9" t="s">
         <v>9</v>
       </c>
@@ -2279,8 +2372,11 @@
       <c r="S34" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T34" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B35" s="9" t="s">
         <v>36</v>
       </c>
@@ -2333,8 +2429,11 @@
       <c r="S35" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T35" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B36" s="9" t="s">
         <v>36</v>
       </c>
@@ -2376,8 +2475,11 @@
       <c r="S36" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T36" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B37" s="9" t="s">
         <v>36</v>
       </c>
@@ -2393,13 +2495,15 @@
         <v>In Progess</v>
       </c>
       <c r="G37" s="10">
-        <v>0.4</v>
+        <v>0.95</v>
       </c>
       <c r="H37" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I37" s="9"/>
+      <c r="I37" s="9" t="s">
+        <v>80</v>
+      </c>
       <c r="J37" s="23"/>
       <c r="O37" s="22">
         <v>0.4</v>
@@ -2416,8 +2520,11 @@
       <c r="S37" s="22">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="38" spans="2:19" ht="75" x14ac:dyDescent="0.25">
+      <c r="T37" s="22">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="38" spans="2:20" ht="75" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="s">
         <v>26</v>
       </c>
@@ -2472,8 +2579,11 @@
       <c r="S38" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T38" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B39" s="9" t="s">
         <v>26</v>
       </c>
@@ -2528,8 +2638,11 @@
       <c r="S39" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="2:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T39" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="2:20" ht="30" x14ac:dyDescent="0.25">
       <c r="B40" s="9" t="s">
         <v>26</v>
       </c>
@@ -2554,7 +2667,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J40" s="23">
         <v>0.2</v>
@@ -2586,8 +2699,11 @@
       <c r="S40" s="22">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T40" s="22">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B41" s="9" t="s">
         <v>10</v>
       </c>
@@ -2640,8 +2756,11 @@
       <c r="S41" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T41" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B42" s="7" t="s">
         <v>28</v>
       </c>
@@ -2694,8 +2813,11 @@
       <c r="S42" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T42" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
         <v>11</v>
       </c>
@@ -2748,8 +2870,11 @@
       <c r="S43" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T43" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
         <v>15</v>
       </c>
@@ -2802,13 +2927,16 @@
       <c r="S44" s="22">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="T44" s="22">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" ht="30" x14ac:dyDescent="0.25">
       <c r="B45" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="19">
@@ -2839,8 +2967,11 @@
       <c r="S45" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T45" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B46" s="7" t="s">
         <v>16</v>
       </c>
@@ -2893,8 +3024,11 @@
       <c r="S46" s="22">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="T46" s="22">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
         <v>17</v>
       </c>
@@ -2947,8 +3081,11 @@
       <c r="S47" s="22">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="T47" s="22">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" ht="45" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>53</v>
       </c>
@@ -2993,8 +3130,11 @@
       <c r="S48" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="T48" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>55</v>
       </c>
@@ -3034,6 +3174,9 @@
         <v>1</v>
       </c>
       <c r="S49" s="22">
+        <v>1</v>
+      </c>
+      <c r="T49" s="22">
         <v>1</v>
       </c>
     </row>
@@ -3120,9 +3263,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3327,27 +3473,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3372,9 +3506,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/ContinuationProject/Status.xlsx
+++ b/ContinuationProject/Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\ContinuationProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{164970BF-6145-4C88-A3F9-2A48DDDB460E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB761F2-A627-4DFD-B945-51B79C60C234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="4" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="81">
   <si>
     <t>DISC DEXPI Continuation Project - Status</t>
   </si>
@@ -266,9 +266,6 @@
     <t>03.11.2025</t>
   </si>
   <si>
-    <t>Line styles to be added.</t>
-  </si>
-  <si>
     <t>Issue fixed from old versions in-progress</t>
   </si>
   <si>
@@ -284,13 +281,16 @@
     <t>10.11.2025</t>
   </si>
   <si>
-    <t>Checking html symbol info, attr. Desc, FillLevel</t>
-  </si>
-  <si>
-    <t>Not yet pushed .. Persistent id missing</t>
-  </si>
-  <si>
-    <t>Persistant ID</t>
+    <t>17.11.2025</t>
+  </si>
+  <si>
+    <t>Line styles to be added - temporary work around</t>
+  </si>
+  <si>
+    <t>Filllevel rule/line style/rotation of label</t>
+  </si>
+  <si>
+    <t>To be pushed</t>
   </si>
 </sst>
 </file>
@@ -498,7 +498,7 @@
     <cellStyle name="Heading 1" xfId="3" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="4" builtinId="17"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
     <cellStyle name="Title" xfId="2" builtinId="15"/>
   </cellStyles>
   <dxfs count="1">
@@ -865,11 +865,12 @@
     <col min="14" max="14" width="17.7109375" style="22" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="16" style="22" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="16.42578125" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="15.7109375" style="22" customWidth="1"/>
+    <col min="17" max="17" width="15.7109375" style="22" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="19.140625" style="22" customWidth="1"/>
     <col min="19" max="19" width="15.42578125" style="22" customWidth="1"/>
     <col min="20" max="20" width="20.28515625" style="22" customWidth="1"/>
-    <col min="21" max="36" width="9.140625" style="22"/>
+    <col min="21" max="21" width="20.85546875" style="22" customWidth="1"/>
+    <col min="22" max="36" width="9.140625" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:59" ht="35.25" x14ac:dyDescent="0.5">
@@ -951,9 +952,11 @@
         <v>71</v>
       </c>
       <c r="T3" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="U3" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="U3" s="20"/>
       <c r="V3" s="20"/>
       <c r="W3" s="20"/>
       <c r="X3" s="20"/>
@@ -1011,14 +1014,14 @@
         <v>In Progess</v>
       </c>
       <c r="G4" s="10">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="H4" s="11">
         <f>--(G4&gt;=1)</f>
         <v>0</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J4" s="23">
         <v>0.3</v>
@@ -1052,6 +1055,9 @@
       </c>
       <c r="T4" s="22">
         <v>0.95</v>
+      </c>
+      <c r="U4" s="22">
+        <v>0.98</v>
       </c>
     </row>
     <row r="5" spans="2:59" ht="30" x14ac:dyDescent="0.25">
@@ -1077,7 +1083,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J5" s="23">
         <v>0.75</v>
@@ -1110,6 +1116,9 @@
         <v>0.97</v>
       </c>
       <c r="T5" s="22">
+        <v>0.98</v>
+      </c>
+      <c r="U5" s="22">
         <v>0.98</v>
       </c>
     </row>
@@ -1167,6 +1176,9 @@
         <v>1</v>
       </c>
       <c r="T6" s="22">
+        <v>1</v>
+      </c>
+      <c r="U6" s="22">
         <v>1</v>
       </c>
     </row>
@@ -1215,6 +1227,9 @@
       <c r="T7" s="22">
         <v>1</v>
       </c>
+      <c r="U7" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
@@ -1261,6 +1276,9 @@
       <c r="T8" s="22">
         <v>1</v>
       </c>
+      <c r="U8" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
@@ -1278,14 +1296,14 @@
         <v>In Progess</v>
       </c>
       <c r="G9" s="10">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="H9" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J9" s="23"/>
       <c r="P9" s="28"/>
@@ -1301,6 +1319,9 @@
       <c r="T9" s="22">
         <v>0.95</v>
       </c>
+      <c r="U9" s="22">
+        <v>0.99</v>
+      </c>
     </row>
     <row r="10" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
@@ -1355,6 +1376,9 @@
       <c r="T10" s="22">
         <v>1</v>
       </c>
+      <c r="U10" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="2:59" ht="45" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
@@ -1416,6 +1440,9 @@
       <c r="T11" s="22">
         <v>1</v>
       </c>
+      <c r="U11" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
@@ -1456,6 +1483,9 @@
       <c r="T12" s="22">
         <v>1</v>
       </c>
+      <c r="U12" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
@@ -1473,14 +1503,14 @@
         <v>In Progess</v>
       </c>
       <c r="G13" s="10">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H13" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J13" s="23"/>
       <c r="O13" s="22">
@@ -1501,6 +1531,9 @@
       <c r="T13" s="22">
         <v>0.2</v>
       </c>
+      <c r="U13" s="22">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="14" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B14" s="9" t="s">
@@ -1560,6 +1593,9 @@
       <c r="T14" s="22">
         <v>1</v>
       </c>
+      <c r="U14" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
@@ -1619,6 +1655,9 @@
       <c r="T15" s="22">
         <v>0.7</v>
       </c>
+      <c r="U15" s="22">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="16" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
@@ -1636,7 +1675,7 @@
         <v>In Progess</v>
       </c>
       <c r="G16" s="10">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H16" s="11">
         <f t="shared" si="1"/>
@@ -1678,8 +1717,11 @@
       <c r="T16" s="22">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="17" spans="2:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U16" s="22">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="17" spans="2:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>7</v>
       </c>
@@ -1715,8 +1757,11 @@
       <c r="T17" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U17" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
         <v>7</v>
       </c>
@@ -1746,8 +1791,11 @@
       <c r="T18" s="22">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U18" s="22">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
         <v>7</v>
       </c>
@@ -1770,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J19" s="23"/>
       <c r="P19" s="28"/>
@@ -1780,8 +1828,11 @@
       <c r="T19" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U19" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>7</v>
       </c>
@@ -1811,8 +1862,11 @@
       <c r="T20" s="22">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="21" spans="2:20" ht="105" x14ac:dyDescent="0.25">
+      <c r="U20" s="22">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:21" ht="105" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
         <v>8</v>
       </c>
@@ -1865,8 +1919,11 @@
       <c r="T21" s="22">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="22" spans="2:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U21" s="22">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="22" spans="2:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
         <v>8</v>
       </c>
@@ -1916,8 +1973,11 @@
       <c r="T22" s="22">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="23" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="U22" s="22">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="23" spans="2:21" ht="30" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
         <v>8</v>
       </c>
@@ -1930,17 +1990,22 @@
       </c>
       <c r="F23" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G23" s="10"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G23" s="10">
+        <v>0.1</v>
+      </c>
       <c r="H23" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J23" s="23"/>
       <c r="P23" s="28"/>
-    </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U23" s="22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
         <v>8</v>
       </c>
@@ -1963,7 +2028,7 @@
       <c r="J24" s="23"/>
       <c r="P24" s="28"/>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B25" s="9" t="s">
         <v>8</v>
       </c>
@@ -1986,7 +2051,7 @@
       <c r="J25" s="23"/>
       <c r="P25" s="28"/>
     </row>
-    <row r="26" spans="2:20" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:21" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="9" t="s">
         <v>2</v>
       </c>
@@ -2044,8 +2109,11 @@
       <c r="T26" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U26" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B27" s="9" t="s">
         <v>2</v>
       </c>
@@ -2090,8 +2158,11 @@
       <c r="T27" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U27" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
         <v>2</v>
       </c>
@@ -2130,8 +2201,11 @@
       <c r="T28" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U28" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
         <v>2</v>
       </c>
@@ -2168,8 +2242,11 @@
       <c r="T29" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U29" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B30" s="9" t="s">
         <v>9</v>
       </c>
@@ -2192,7 +2269,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J30" s="23"/>
       <c r="L30" s="22">
@@ -2222,8 +2299,11 @@
       <c r="T30" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="2:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U30" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="9" t="s">
         <v>9</v>
       </c>
@@ -2246,7 +2326,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J31" s="23"/>
       <c r="L31" s="22">
@@ -2276,8 +2356,11 @@
       <c r="T31" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U31" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B32" s="9" t="s">
         <v>9</v>
       </c>
@@ -2311,8 +2394,11 @@
       <c r="T32" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U32" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B33" s="9" t="s">
         <v>9</v>
       </c>
@@ -2343,8 +2429,11 @@
       <c r="T33" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U33" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B34" s="9" t="s">
         <v>9</v>
       </c>
@@ -2375,8 +2464,11 @@
       <c r="T34" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U34" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B35" s="9" t="s">
         <v>36</v>
       </c>
@@ -2432,8 +2524,11 @@
       <c r="T35" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U35" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B36" s="9" t="s">
         <v>36</v>
       </c>
@@ -2478,8 +2573,11 @@
       <c r="T36" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U36" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B37" s="9" t="s">
         <v>36</v>
       </c>
@@ -2495,7 +2593,7 @@
         <v>In Progess</v>
       </c>
       <c r="G37" s="10">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="H37" s="11">
         <f t="shared" si="1"/>
@@ -2523,8 +2621,11 @@
       <c r="T37" s="22">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="38" spans="2:20" ht="75" x14ac:dyDescent="0.25">
+      <c r="U37" s="22">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="38" spans="2:21" ht="75" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="s">
         <v>26</v>
       </c>
@@ -2582,8 +2683,11 @@
       <c r="T38" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U38" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B39" s="9" t="s">
         <v>26</v>
       </c>
@@ -2641,8 +2745,11 @@
       <c r="T39" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="U39" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="2:21" ht="30" x14ac:dyDescent="0.25">
       <c r="B40" s="9" t="s">
         <v>26</v>
       </c>
@@ -2702,8 +2809,11 @@
       <c r="T40" s="22">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U40" s="22">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="41" spans="2:21" ht="30" x14ac:dyDescent="0.25">
       <c r="B41" s="9" t="s">
         <v>10</v>
       </c>
@@ -2759,8 +2869,11 @@
       <c r="T41" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U41" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B42" s="7" t="s">
         <v>28</v>
       </c>
@@ -2816,8 +2929,11 @@
       <c r="T42" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U42" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
         <v>11</v>
       </c>
@@ -2873,8 +2989,11 @@
       <c r="T43" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U43" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
         <v>15</v>
       </c>
@@ -2930,8 +3049,11 @@
       <c r="T44" s="22">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="U44" s="22">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" ht="30" x14ac:dyDescent="0.25">
       <c r="B45" s="7" t="s">
         <v>15</v>
       </c>
@@ -2970,8 +3092,11 @@
       <c r="T45" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U45" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B46" s="7" t="s">
         <v>16</v>
       </c>
@@ -3027,8 +3152,11 @@
       <c r="T46" s="22">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U46" s="22">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
         <v>17</v>
       </c>
@@ -3084,8 +3212,11 @@
       <c r="T47" s="22">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" ht="45" x14ac:dyDescent="0.25">
+      <c r="U47" s="22">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" ht="45" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>53</v>
       </c>
@@ -3133,8 +3264,11 @@
       <c r="T48" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="U48" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>55</v>
       </c>
@@ -3177,6 +3311,9 @@
         <v>1</v>
       </c>
       <c r="T49" s="22">
+        <v>1</v>
+      </c>
+      <c r="U49" s="22">
         <v>1</v>
       </c>
     </row>
@@ -3263,15 +3400,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100C3422A7FFD03AF47B40E3148D61510DD" ma:contentTypeVersion="10" ma:contentTypeDescription="Opprett et nytt dokument." ma:contentTypeScope="" ma:versionID="93a5827b91256c075a5bcdb454d162de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0" xmlns:ns3="b6192152-6ac4-477a-b62a-2f500fcdf3b6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="13127a08f307124b01356346b67d6a81" ns2:_="" ns3:_="">
     <xsd:import namespace="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
@@ -3472,6 +3600,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -3479,14 +3616,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CED3C9C-630D-4C4B-A736-44AEC9EEC0A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3501,6 +3630,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/ContinuationProject/Status.xlsx
+++ b/ContinuationProject/Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\ContinuationProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB761F2-A627-4DFD-B945-51B79C60C234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FADC31-FC4A-45A6-ADD1-51E7B60260F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="4" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="82">
   <si>
     <t>DISC DEXPI Continuation Project - Status</t>
   </si>
@@ -161,9 +161,6 @@
   </si>
   <si>
     <t>Label addition to profile</t>
-  </si>
-  <si>
-    <t>Need to add qualifier type to standard ? Discuss with Aibel.</t>
   </si>
   <si>
     <t>Target Date</t>
@@ -257,9 +254,6 @@
     <t>Create blueprint examples for  requirements in both serialization formats.</t>
   </si>
   <si>
-    <t>Available in DEXPI 2.0 xml</t>
-  </si>
-  <si>
     <t>Not needed as can be managed in DEXPI 2.0</t>
   </si>
   <si>
@@ -291,6 +285,15 @@
   </si>
   <si>
     <t>To be pushed</t>
+  </si>
+  <si>
+    <t>24.11.2025</t>
+  </si>
+  <si>
+    <t>Aibel is happy with DEXPI 2.0 way of managing this.</t>
+  </si>
+  <si>
+    <t>Available in DEXPI 2.0 xml. This is an issue for DEXPI group particularly for the overall conceptual model .. How shall OPCs be managed. (Signal &amp; Piping)</t>
   </si>
 </sst>
 </file>
@@ -498,7 +501,7 @@
     <cellStyle name="Heading 1" xfId="3" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="4" builtinId="17"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
     <cellStyle name="Title" xfId="2" builtinId="15"/>
   </cellStyles>
   <dxfs count="1">
@@ -852,7 +855,7 @@
     <col min="1" max="1" width="5.85546875" customWidth="1"/>
     <col min="2" max="2" width="28.140625" customWidth="1"/>
     <col min="3" max="3" width="56.7109375" customWidth="1"/>
-    <col min="4" max="4" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="29.7109375" customWidth="1"/>
     <col min="5" max="5" width="14.5703125" style="20" customWidth="1"/>
     <col min="6" max="6" width="14.42578125" customWidth="1"/>
     <col min="7" max="7" width="19.7109375" customWidth="1"/>
@@ -866,11 +869,12 @@
     <col min="15" max="15" width="16" style="22" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="16.42578125" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="15.7109375" style="22" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="19.140625" style="22" customWidth="1"/>
+    <col min="18" max="18" width="19.140625" style="22" hidden="1" customWidth="1"/>
     <col min="19" max="19" width="15.42578125" style="22" customWidth="1"/>
     <col min="20" max="20" width="20.28515625" style="22" customWidth="1"/>
-    <col min="21" max="21" width="20.85546875" style="22" customWidth="1"/>
-    <col min="22" max="36" width="9.140625" style="22"/>
+    <col min="21" max="21" width="13.85546875" style="22" customWidth="1"/>
+    <col min="22" max="22" width="15.5703125" style="22" customWidth="1"/>
+    <col min="23" max="36" width="9.140625" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:59" ht="35.25" x14ac:dyDescent="0.5">
@@ -907,57 +911,59 @@
         <v>34</v>
       </c>
       <c r="E3" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>42</v>
-      </c>
       <c r="K3" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="L3" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="21" t="s">
-        <v>50</v>
-      </c>
       <c r="M3" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N3" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O3" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P3" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q3" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="Q3" s="27" t="s">
+      <c r="R3" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="R3" s="27" t="s">
-        <v>66</v>
-      </c>
       <c r="S3" s="27" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="T3" s="27" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="U3" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="V3" s="20"/>
+        <v>75</v>
+      </c>
+      <c r="V3" s="27" t="s">
+        <v>79</v>
+      </c>
       <c r="W3" s="20"/>
       <c r="X3" s="20"/>
       <c r="Y3" s="20"/>
@@ -996,7 +1002,7 @@
       <c r="BF3" s="20"/>
       <c r="BG3" s="20"/>
     </row>
-    <row r="4" spans="2:59" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:59" ht="45" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>12</v>
       </c>
@@ -1004,7 +1010,7 @@
         <v>13</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E4" s="19">
         <v>46010</v>
@@ -1021,7 +1027,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J4" s="23">
         <v>0.3</v>
@@ -1057,6 +1063,9 @@
         <v>0.95</v>
       </c>
       <c r="U4" s="22">
+        <v>0.98</v>
+      </c>
+      <c r="V4" s="22">
         <v>0.98</v>
       </c>
     </row>
@@ -1083,7 +1092,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J5" s="23">
         <v>0.75</v>
@@ -1119,6 +1128,9 @@
         <v>0.98</v>
       </c>
       <c r="U5" s="22">
+        <v>0.98</v>
+      </c>
+      <c r="V5" s="22">
         <v>0.98</v>
       </c>
     </row>
@@ -1179,6 +1191,9 @@
         <v>1</v>
       </c>
       <c r="U6" s="22">
+        <v>1</v>
+      </c>
+      <c r="V6" s="22">
         <v>1</v>
       </c>
     </row>
@@ -1230,6 +1245,9 @@
       <c r="U7" s="22">
         <v>1</v>
       </c>
+      <c r="V7" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
@@ -1279,6 +1297,9 @@
       <c r="U8" s="22">
         <v>1</v>
       </c>
+      <c r="V8" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
@@ -1303,7 +1324,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J9" s="23"/>
       <c r="P9" s="28"/>
@@ -1322,6 +1343,9 @@
       <c r="U9" s="22">
         <v>0.99</v>
       </c>
+      <c r="V9" s="22">
+        <v>0.99</v>
+      </c>
     </row>
     <row r="10" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
@@ -1335,7 +1359,7 @@
         <v>45909</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G10" s="10">
         <v>1</v>
@@ -1379,6 +1403,9 @@
       <c r="U10" s="22">
         <v>1</v>
       </c>
+      <c r="V10" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="2:59" ht="45" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
@@ -1388,7 +1415,7 @@
         <v>21</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E11" s="19">
         <v>45917</v>
@@ -1405,7 +1432,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J11" s="23">
         <v>0.6</v>
@@ -1441,6 +1468,9 @@
         <v>1</v>
       </c>
       <c r="U11" s="22">
+        <v>1</v>
+      </c>
+      <c r="V11" s="22">
         <v>1</v>
       </c>
     </row>
@@ -1486,6 +1516,9 @@
       <c r="U12" s="22">
         <v>1</v>
       </c>
+      <c r="V12" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
@@ -1503,14 +1536,14 @@
         <v>In Progess</v>
       </c>
       <c r="G13" s="10">
-        <v>0.3</v>
+        <v>0.95</v>
       </c>
       <c r="H13" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J13" s="23"/>
       <c r="O13" s="22">
@@ -1534,6 +1567,9 @@
       <c r="U13" s="22">
         <v>0.3</v>
       </c>
+      <c r="V13" s="22">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="14" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B14" s="9" t="s">
@@ -1596,6 +1632,9 @@
       <c r="U14" s="22">
         <v>1</v>
       </c>
+      <c r="V14" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
@@ -1610,17 +1649,17 @@
       </c>
       <c r="F15" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>In Progess</v>
+        <v>Complete</v>
       </c>
       <c r="G15" s="10">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="H15" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="J15" s="23">
         <v>0.7</v>
@@ -1658,8 +1697,11 @@
       <c r="U15" s="22">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="16" spans="2:59" ht="30" x14ac:dyDescent="0.25">
+      <c r="V15" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:59" ht="75" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
         <v>7</v>
       </c>
@@ -1672,17 +1714,17 @@
       </c>
       <c r="F16" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>In Progess</v>
+        <v>Complete</v>
       </c>
       <c r="G16" s="10">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="H16" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="J16" s="23">
         <v>0.2</v>
@@ -1720,8 +1762,11 @@
       <c r="U16" s="22">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="17" spans="2:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V16" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>7</v>
       </c>
@@ -1744,7 +1789,7 @@
         <v>1</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J17" s="23"/>
       <c r="P17" s="28"/>
@@ -1760,8 +1805,11 @@
       <c r="U17" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V17" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
         <v>7</v>
       </c>
@@ -1794,8 +1842,11 @@
       <c r="U18" s="22">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V18" s="22">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
         <v>7</v>
       </c>
@@ -1818,7 +1869,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J19" s="23"/>
       <c r="P19" s="28"/>
@@ -1831,8 +1882,11 @@
       <c r="U19" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V19" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>7</v>
       </c>
@@ -1865,8 +1919,11 @@
       <c r="U20" s="22">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="21" spans="2:21" ht="105" x14ac:dyDescent="0.25">
+      <c r="V20" s="22">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22" ht="105" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
         <v>8</v>
       </c>
@@ -1889,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J21" s="23"/>
       <c r="L21" s="22">
@@ -1922,8 +1979,11 @@
       <c r="U21" s="22">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="22" spans="2:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V21" s="22">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
         <v>8</v>
       </c>
@@ -1976,8 +2036,11 @@
       <c r="U22" s="22">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="23" spans="2:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="V22" s="22">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
         <v>8</v>
       </c>
@@ -2004,8 +2067,11 @@
       <c r="U23" s="22">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V23" s="22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
         <v>8</v>
       </c>
@@ -2028,7 +2094,7 @@
       <c r="J24" s="23"/>
       <c r="P24" s="28"/>
     </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B25" s="9" t="s">
         <v>8</v>
       </c>
@@ -2051,7 +2117,7 @@
       <c r="J25" s="23"/>
       <c r="P25" s="28"/>
     </row>
-    <row r="26" spans="2:21" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:22" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="9" t="s">
         <v>2</v>
       </c>
@@ -2074,7 +2140,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J26" s="23">
         <v>0.7</v>
@@ -2112,8 +2178,11 @@
       <c r="U26" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V26" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B27" s="9" t="s">
         <v>2</v>
       </c>
@@ -2161,8 +2230,11 @@
       <c r="U27" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V27" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
         <v>2</v>
       </c>
@@ -2204,8 +2276,11 @@
       <c r="U28" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V28" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
         <v>2</v>
       </c>
@@ -2245,8 +2320,11 @@
       <c r="U29" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V29" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B30" s="9" t="s">
         <v>9</v>
       </c>
@@ -2269,7 +2347,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J30" s="23"/>
       <c r="L30" s="22">
@@ -2302,8 +2380,11 @@
       <c r="U30" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="2:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V30" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="9" t="s">
         <v>9</v>
       </c>
@@ -2326,7 +2407,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J31" s="23"/>
       <c r="L31" s="22">
@@ -2359,8 +2440,11 @@
       <c r="U31" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V31" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B32" s="9" t="s">
         <v>9</v>
       </c>
@@ -2397,8 +2481,11 @@
       <c r="U32" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V32" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B33" s="9" t="s">
         <v>9</v>
       </c>
@@ -2432,8 +2519,11 @@
       <c r="U33" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V33" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B34" s="9" t="s">
         <v>9</v>
       </c>
@@ -2467,8 +2557,11 @@
       <c r="U34" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V34" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B35" s="9" t="s">
         <v>36</v>
       </c>
@@ -2527,8 +2620,11 @@
       <c r="U35" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V35" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B36" s="9" t="s">
         <v>36</v>
       </c>
@@ -2576,8 +2672,11 @@
       <c r="U36" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V36" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B37" s="9" t="s">
         <v>36</v>
       </c>
@@ -2600,7 +2699,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J37" s="23"/>
       <c r="O37" s="22">
@@ -2624,13 +2723,16 @@
       <c r="U37" s="22">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="38" spans="2:21" ht="75" x14ac:dyDescent="0.25">
+      <c r="V37" s="22">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="38" spans="2:22" ht="75" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="s">
         <v>26</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="19">
@@ -2648,7 +2750,7 @@
         <v>1</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J38" s="23">
         <v>0.85</v>
@@ -2686,8 +2788,11 @@
       <c r="U38" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V38" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B39" s="9" t="s">
         <v>26</v>
       </c>
@@ -2748,8 +2853,11 @@
       <c r="U39" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="2:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="V39" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="2:22" ht="30" x14ac:dyDescent="0.25">
       <c r="B40" s="9" t="s">
         <v>26</v>
       </c>
@@ -2757,7 +2865,7 @@
         <v>39</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E40" s="19">
         <v>45973</v>
@@ -2774,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J40" s="23">
         <v>0.2</v>
@@ -2812,8 +2920,11 @@
       <c r="U40" s="22">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="41" spans="2:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="V40" s="22">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="41" spans="2:22" ht="30" x14ac:dyDescent="0.25">
       <c r="B41" s="9" t="s">
         <v>10</v>
       </c>
@@ -2872,8 +2983,11 @@
       <c r="U41" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V41" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B42" s="7" t="s">
         <v>28</v>
       </c>
@@ -2932,8 +3046,11 @@
       <c r="U42" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V42" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
         <v>11</v>
       </c>
@@ -2992,8 +3109,11 @@
       <c r="U43" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V43" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
         <v>15</v>
       </c>
@@ -3052,13 +3172,16 @@
       <c r="U44" s="22">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="V44" s="22">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" ht="30" x14ac:dyDescent="0.25">
       <c r="B45" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="19">
@@ -3095,8 +3218,11 @@
       <c r="U45" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V45" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B46" s="7" t="s">
         <v>16</v>
       </c>
@@ -3155,8 +3281,11 @@
       <c r="U46" s="22">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V46" s="22">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
         <v>17</v>
       </c>
@@ -3215,13 +3344,16 @@
       <c r="U47" s="22">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="V47" s="22">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" ht="45" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
+        <v>52</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="E48" s="20">
         <v>46010</v>
@@ -3267,13 +3399,16 @@
       <c r="U48" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V48" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
+        <v>54</v>
+      </c>
+      <c r="C49" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>56</v>
       </c>
       <c r="E49" s="20">
         <v>45918</v>
@@ -3314,6 +3449,9 @@
         <v>1</v>
       </c>
       <c r="U49" s="22">
+        <v>1</v>
+      </c>
+      <c r="V49" s="22">
         <v>1</v>
       </c>
     </row>
@@ -3400,6 +3538,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100C3422A7FFD03AF47B40E3148D61510DD" ma:contentTypeVersion="10" ma:contentTypeDescription="Opprett et nytt dokument." ma:contentTypeScope="" ma:versionID="93a5827b91256c075a5bcdb454d162de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0" xmlns:ns3="b6192152-6ac4-477a-b62a-2f500fcdf3b6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="13127a08f307124b01356346b67d6a81" ns2:_="" ns3:_="">
     <xsd:import namespace="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
@@ -3600,22 +3753,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CED3C9C-630D-4C4B-A736-44AEC9EEC0A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3632,29 +3795,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/ContinuationProject/Status.xlsx
+++ b/ContinuationProject/Status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\ContinuationProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FADC31-FC4A-45A6-ADD1-51E7B60260F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9EFFD8C-F3BD-4122-9522-959E26BE5CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="4" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="86">
   <si>
     <t>DISC DEXPI Continuation Project - Status</t>
   </si>
@@ -260,9 +260,6 @@
     <t>03.11.2025</t>
   </si>
   <si>
-    <t>Issue fixed from old versions in-progress</t>
-  </si>
-  <si>
     <t>Keep as is with no new sub-types</t>
   </si>
   <si>
@@ -294,6 +291,22 @@
   </si>
   <si>
     <t>Available in DEXPI 2.0 xml. This is an issue for DEXPI group particularly for the overall conceptual model .. How shall OPCs be managed. (Signal &amp; Piping)</t>
+  </si>
+  <si>
+    <t>01.12.2025</t>
+  </si>
+  <si>
+    <t>To be delivered with Profile 3 due to NuclearSource</t>
+  </si>
+  <si>
+    <t>To be delivered with Profile 3 - need to change all other versions for reference info</t>
+  </si>
+  <si>
+    <t>Include example in Blueprint files - package only as new propertybreak model includes tie-ins.</t>
+  </si>
+  <si>
+    <t>Tonia to create ver 13 with custom equipment package &amp; joints. Tiein example not needed as this is covered by propertybreak.
+Update to existing propertybreak to cover model Profile 3</t>
   </si>
 </sst>
 </file>
@@ -303,7 +316,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;Done&quot;;&quot;&quot;;&quot;&quot;"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -362,6 +375,14 @@
       <color theme="3"/>
       <name val="Bookman Old Style"/>
       <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -423,7 +444,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
@@ -494,6 +515,7 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Date" xfId="6" xr:uid="{2ABB41C5-3CC8-4E1C-85D9-965CF83E22BD}"/>
@@ -501,7 +523,7 @@
     <cellStyle name="Heading 1" xfId="3" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="4" builtinId="17"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
     <cellStyle name="Title" xfId="2" builtinId="15"/>
   </cellStyles>
   <dxfs count="1">
@@ -850,34 +872,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825F216F-6A2C-43F0-976D-4459909E096A}">
   <dimension ref="B1:BG49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="5.85546875" customWidth="1"/>
-    <col min="2" max="2" width="28.140625" customWidth="1"/>
-    <col min="3" max="3" width="56.7109375" customWidth="1"/>
-    <col min="4" max="4" width="29.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="20" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" customWidth="1"/>
+    <col min="1" max="1" width="5.86328125" customWidth="1"/>
+    <col min="2" max="2" width="28.1328125" customWidth="1"/>
+    <col min="3" max="3" width="56.73046875" customWidth="1"/>
+    <col min="4" max="4" width="29.73046875" customWidth="1"/>
+    <col min="5" max="5" width="14.59765625" style="20" customWidth="1"/>
+    <col min="6" max="6" width="14.3984375" customWidth="1"/>
+    <col min="7" max="7" width="19.73046875" customWidth="1"/>
     <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="36.5703125" customWidth="1"/>
-    <col min="10" max="10" width="18.140625" style="22" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="16.85546875" style="22" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="36.59765625" customWidth="1"/>
+    <col min="10" max="10" width="18.1328125" style="22" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="16.86328125" style="22" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="15" style="22" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="19.85546875" style="22" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="17.7109375" style="22" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="19.86328125" style="22" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="17.73046875" style="22" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="16" style="22" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="16.42578125" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="15.7109375" style="22" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="19.140625" style="22" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="15.42578125" style="22" customWidth="1"/>
-    <col min="20" max="20" width="20.28515625" style="22" customWidth="1"/>
-    <col min="21" max="21" width="13.85546875" style="22" customWidth="1"/>
-    <col min="22" max="22" width="15.5703125" style="22" customWidth="1"/>
-    <col min="23" max="36" width="9.140625" style="22"/>
+    <col min="16" max="16" width="16.3984375" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="15.73046875" style="22" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="19.1328125" style="22" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="15.3984375" style="22" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="20.265625" style="22" customWidth="1"/>
+    <col min="21" max="21" width="13.86328125" style="22" customWidth="1"/>
+    <col min="22" max="22" width="15.59765625" style="22" customWidth="1"/>
+    <col min="23" max="23" width="14.59765625" style="22" customWidth="1"/>
+    <col min="24" max="36" width="9.1328125" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:59" ht="35.25" x14ac:dyDescent="0.5">
+    <row r="1" spans="2:59" ht="34.9" x14ac:dyDescent="0.9">
       <c r="B1" s="16" t="s">
         <v>0</v>
       </c>
@@ -890,7 +913,7 @@
       <c r="I1" s="6"/>
       <c r="P1" s="26"/>
     </row>
-    <row r="2" spans="2:59" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:59" ht="9" customHeight="1" x14ac:dyDescent="0.7">
       <c r="C2" s="6"/>
       <c r="D2" s="1"/>
       <c r="E2" s="17"/>
@@ -900,7 +923,7 @@
       <c r="I2" s="6"/>
       <c r="P2" s="26"/>
     </row>
-    <row r="3" spans="2:59" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:59" ht="19.5" x14ac:dyDescent="0.6">
       <c r="B3" s="2" t="s">
         <v>19</v>
       </c>
@@ -956,15 +979,17 @@
         <v>69</v>
       </c>
       <c r="T3" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="U3" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="U3" s="27" t="s">
-        <v>75</v>
-      </c>
       <c r="V3" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="W3" s="20"/>
+        <v>78</v>
+      </c>
+      <c r="W3" s="30" t="s">
+        <v>81</v>
+      </c>
       <c r="X3" s="20"/>
       <c r="Y3" s="20"/>
       <c r="Z3" s="20"/>
@@ -1002,7 +1027,7 @@
       <c r="BF3" s="20"/>
       <c r="BG3" s="20"/>
     </row>
-    <row r="4" spans="2:59" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:59" ht="42.75" x14ac:dyDescent="0.45">
       <c r="B4" s="9" t="s">
         <v>12</v>
       </c>
@@ -1017,17 +1042,17 @@
       </c>
       <c r="F4" s="9" t="str">
         <f>IF(G4=1,"Complete",IF(G4&lt;&gt;0,"In Progess","Not Started"))</f>
-        <v>In Progess</v>
+        <v>Complete</v>
       </c>
       <c r="G4" s="10">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="H4" s="11">
         <f>--(G4&gt;=1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J4" s="23">
         <v>0.3</v>
@@ -1068,8 +1093,11 @@
       <c r="V4" s="22">
         <v>0.98</v>
       </c>
-    </row>
-    <row r="5" spans="2:59" ht="30" x14ac:dyDescent="0.25">
+      <c r="W4" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:59" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B5" s="9" t="s">
         <v>12</v>
       </c>
@@ -1085,14 +1113,14 @@
         <v>In Progess</v>
       </c>
       <c r="G5" s="10">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="H5" s="11">
         <f t="shared" ref="H5:H49" si="1">--(G5&gt;=1)</f>
         <v>0</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J5" s="23">
         <v>0.75</v>
@@ -1133,8 +1161,11 @@
       <c r="V5" s="22">
         <v>0.98</v>
       </c>
-    </row>
-    <row r="6" spans="2:59" ht="30" x14ac:dyDescent="0.25">
+      <c r="W5" s="22">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="6" spans="2:59" x14ac:dyDescent="0.45">
       <c r="B6" s="9" t="s">
         <v>3</v>
       </c>
@@ -1196,8 +1227,11 @@
       <c r="V6" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="2:59" ht="30" x14ac:dyDescent="0.25">
+      <c r="W6" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:59" x14ac:dyDescent="0.45">
       <c r="B7" s="9" t="s">
         <v>3</v>
       </c>
@@ -1248,8 +1282,11 @@
       <c r="V7" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="2:59" x14ac:dyDescent="0.25">
+      <c r="W7" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:59" x14ac:dyDescent="0.45">
       <c r="B8" s="9" t="s">
         <v>3</v>
       </c>
@@ -1300,8 +1337,11 @@
       <c r="V8" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="2:59" ht="30" x14ac:dyDescent="0.25">
+      <c r="W8" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:59" x14ac:dyDescent="0.45">
       <c r="B9" s="9" t="s">
         <v>3</v>
       </c>
@@ -1324,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J9" s="23"/>
       <c r="P9" s="28"/>
@@ -1346,8 +1386,11 @@
       <c r="V9" s="22">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="10" spans="2:59" x14ac:dyDescent="0.25">
+      <c r="W9" s="22">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="10" spans="2:59" x14ac:dyDescent="0.45">
       <c r="B10" s="9" t="s">
         <v>4</v>
       </c>
@@ -1406,8 +1449,11 @@
       <c r="V10" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="2:59" ht="45" x14ac:dyDescent="0.25">
+      <c r="W10" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:59" ht="42.75" x14ac:dyDescent="0.45">
       <c r="B11" s="9" t="s">
         <v>5</v>
       </c>
@@ -1473,8 +1519,11 @@
       <c r="V11" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="2:59" x14ac:dyDescent="0.25">
+      <c r="W11" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:59" x14ac:dyDescent="0.45">
       <c r="B12" s="9" t="s">
         <v>5</v>
       </c>
@@ -1519,8 +1568,11 @@
       <c r="V12" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="2:59" ht="30" x14ac:dyDescent="0.25">
+      <c r="W12" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:59" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B13" s="9" t="s">
         <v>5</v>
       </c>
@@ -1536,14 +1588,14 @@
         <v>In Progess</v>
       </c>
       <c r="G13" s="10">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="H13" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="J13" s="23"/>
       <c r="O13" s="22">
@@ -1570,8 +1622,11 @@
       <c r="V13" s="22">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="14" spans="2:59" x14ac:dyDescent="0.25">
+      <c r="W13" s="22">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="14" spans="2:59" x14ac:dyDescent="0.45">
       <c r="B14" s="9" t="s">
         <v>6</v>
       </c>
@@ -1635,8 +1690,11 @@
       <c r="V14" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="2:59" ht="30" x14ac:dyDescent="0.25">
+      <c r="W14" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:59" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B15" s="9" t="s">
         <v>6</v>
       </c>
@@ -1659,7 +1717,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J15" s="23">
         <v>0.7</v>
@@ -1700,8 +1758,11 @@
       <c r="V15" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="2:59" ht="75" x14ac:dyDescent="0.25">
+      <c r="W15" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:59" ht="57" x14ac:dyDescent="0.45">
       <c r="B16" s="9" t="s">
         <v>7</v>
       </c>
@@ -1724,7 +1785,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J16" s="23">
         <v>0.2</v>
@@ -1765,8 +1826,11 @@
       <c r="V16" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="2:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W16" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B17" s="9" t="s">
         <v>7</v>
       </c>
@@ -1808,8 +1872,11 @@
       <c r="V17" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="W17" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B18" s="9" t="s">
         <v>7</v>
       </c>
@@ -1845,8 +1912,11 @@
       <c r="V18" s="22">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="19" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="W18" s="22">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="19" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B19" s="9" t="s">
         <v>7</v>
       </c>
@@ -1869,7 +1939,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J19" s="23"/>
       <c r="P19" s="28"/>
@@ -1885,8 +1955,11 @@
       <c r="V19" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="W19" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:23" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B20" s="9" t="s">
         <v>7</v>
       </c>
@@ -1902,11 +1975,14 @@
         <v>In Progess</v>
       </c>
       <c r="G20" s="10">
-        <v>0.2</v>
+        <v>0.98</v>
       </c>
       <c r="H20" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="J20" s="23"/>
       <c r="P20" s="28"/>
@@ -1922,8 +1998,11 @@
       <c r="V20" s="22">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="21" spans="2:22" ht="105" x14ac:dyDescent="0.25">
+      <c r="W20" s="22">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="21" spans="2:23" ht="85.5" x14ac:dyDescent="0.45">
       <c r="B21" s="9" t="s">
         <v>8</v>
       </c>
@@ -1982,8 +2061,11 @@
       <c r="V21" s="22">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="22" spans="2:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W21" s="22">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="22" spans="2:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B22" s="9" t="s">
         <v>8</v>
       </c>
@@ -2039,8 +2121,11 @@
       <c r="V22" s="22">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="23" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="W22" s="22">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="23" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B23" s="9" t="s">
         <v>8</v>
       </c>
@@ -2070,8 +2155,11 @@
       <c r="V23" s="22">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="24" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="W23" s="22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B24" s="9" t="s">
         <v>8</v>
       </c>
@@ -2094,12 +2182,12 @@
       <c r="J24" s="23"/>
       <c r="P24" s="28"/>
     </row>
-    <row r="25" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:23" ht="71.25" x14ac:dyDescent="0.45">
       <c r="B25" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="19">
@@ -2114,10 +2202,13 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="I25" s="6" t="s">
+        <v>85</v>
+      </c>
       <c r="J25" s="23"/>
       <c r="P25" s="28"/>
     </row>
-    <row r="26" spans="2:22" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:23" ht="49.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B26" s="9" t="s">
         <v>2</v>
       </c>
@@ -2181,8 +2272,11 @@
       <c r="V26" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="W26" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B27" s="9" t="s">
         <v>2</v>
       </c>
@@ -2233,8 +2327,11 @@
       <c r="V27" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="W27" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B28" s="9" t="s">
         <v>2</v>
       </c>
@@ -2279,8 +2376,11 @@
       <c r="V28" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="W28" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B29" s="9" t="s">
         <v>2</v>
       </c>
@@ -2323,8 +2423,11 @@
       <c r="V29" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="W29" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B30" s="9" t="s">
         <v>9</v>
       </c>
@@ -2347,7 +2450,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J30" s="23"/>
       <c r="L30" s="22">
@@ -2383,8 +2486,11 @@
       <c r="V30" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="2:22" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W30" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B31" s="9" t="s">
         <v>9</v>
       </c>
@@ -2407,7 +2513,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J31" s="23"/>
       <c r="L31" s="22">
@@ -2443,8 +2549,11 @@
       <c r="V31" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="W31" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B32" s="9" t="s">
         <v>9</v>
       </c>
@@ -2484,8 +2593,11 @@
       <c r="V32" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="W32" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B33" s="9" t="s">
         <v>9</v>
       </c>
@@ -2522,8 +2634,11 @@
       <c r="V33" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="W33" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B34" s="9" t="s">
         <v>9</v>
       </c>
@@ -2560,8 +2675,11 @@
       <c r="V34" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="W34" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B35" s="9" t="s">
         <v>36</v>
       </c>
@@ -2623,8 +2741,11 @@
       <c r="V35" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="W35" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B36" s="9" t="s">
         <v>36</v>
       </c>
@@ -2675,8 +2796,11 @@
       <c r="V36" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="W36" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B37" s="9" t="s">
         <v>36</v>
       </c>
@@ -2699,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J37" s="23"/>
       <c r="O37" s="22">
@@ -2726,8 +2850,11 @@
       <c r="V37" s="22">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="38" spans="2:22" ht="75" x14ac:dyDescent="0.25">
+      <c r="W37" s="22">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="38" spans="2:23" ht="57" x14ac:dyDescent="0.45">
       <c r="B38" s="9" t="s">
         <v>26</v>
       </c>
@@ -2791,8 +2918,11 @@
       <c r="V38" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="W38" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B39" s="9" t="s">
         <v>26</v>
       </c>
@@ -2856,8 +2986,11 @@
       <c r="V39" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="2:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="W39" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="2:23" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B40" s="9" t="s">
         <v>26</v>
       </c>
@@ -2923,8 +3056,11 @@
       <c r="V40" s="22">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="41" spans="2:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="W40" s="22">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B41" s="9" t="s">
         <v>10</v>
       </c>
@@ -2986,8 +3122,11 @@
       <c r="V41" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="W41" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B42" s="7" t="s">
         <v>28</v>
       </c>
@@ -3049,8 +3188,11 @@
       <c r="V42" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="W42" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B43" s="7" t="s">
         <v>11</v>
       </c>
@@ -3112,8 +3254,11 @@
       <c r="V43" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="W43" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B44" s="7" t="s">
         <v>15</v>
       </c>
@@ -3175,8 +3320,11 @@
       <c r="V44" s="22">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="W44" s="22">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B45" s="7" t="s">
         <v>15</v>
       </c>
@@ -3221,8 +3369,11 @@
       <c r="V45" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="W45" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B46" s="7" t="s">
         <v>16</v>
       </c>
@@ -3284,8 +3435,11 @@
       <c r="V46" s="22">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="W46" s="22">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B47" s="7" t="s">
         <v>17</v>
       </c>
@@ -3347,8 +3501,11 @@
       <c r="V47" s="22">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="W47" s="22">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" ht="42.75" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
         <v>52</v>
       </c>
@@ -3402,8 +3559,11 @@
       <c r="V48" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="W48" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:23" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
         <v>54</v>
       </c>
@@ -3452,6 +3612,9 @@
         <v>1</v>
       </c>
       <c r="V49" s="22">
+        <v>1</v>
+      </c>
+      <c r="W49" s="22">
         <v>1</v>
       </c>
     </row>
@@ -3531,28 +3694,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23963325-1FFB-4B92-8120-662513F10342}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100C3422A7FFD03AF47B40E3148D61510DD" ma:contentTypeVersion="10" ma:contentTypeDescription="Opprett et nytt dokument." ma:contentTypeScope="" ma:versionID="93a5827b91256c075a5bcdb454d162de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0" xmlns:ns3="b6192152-6ac4-477a-b62a-2f500fcdf3b6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="13127a08f307124b01356346b67d6a81" ns2:_="" ns3:_="">
     <xsd:import namespace="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
@@ -3753,32 +3901,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CED3C9C-630D-4C4B-A736-44AEC9EEC0A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3795,4 +3933,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/ContinuationProject/Status.xlsx
+++ b/ContinuationProject/Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\ContinuationProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9EFFD8C-F3BD-4122-9522-959E26BE5CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD5E4A89-837F-4A43-BAB3-2E69F020F183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="4" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="88">
   <si>
     <t>DISC DEXPI Continuation Project - Status</t>
   </si>
@@ -307,6 +307,12 @@
   <si>
     <t>Tonia to create ver 13 with custom equipment package &amp; joints. Tiein example not needed as this is covered by propertybreak.
 Update to existing propertybreak to cover model Profile 3</t>
+  </si>
+  <si>
+    <t>Complete Workshop 12</t>
+  </si>
+  <si>
+    <t>12.12.2025</t>
   </si>
 </sst>
 </file>
@@ -871,36 +877,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825F216F-6A2C-43F0-976D-4459909E096A}">
-  <dimension ref="B1:BG49"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="B1:BG50"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.86328125" customWidth="1"/>
-    <col min="2" max="2" width="28.1328125" customWidth="1"/>
-    <col min="3" max="3" width="56.73046875" customWidth="1"/>
-    <col min="4" max="4" width="29.73046875" customWidth="1"/>
-    <col min="5" max="5" width="14.59765625" style="20" customWidth="1"/>
-    <col min="6" max="6" width="14.3984375" customWidth="1"/>
-    <col min="7" max="7" width="19.73046875" customWidth="1"/>
+    <col min="1" max="1" width="5.85546875" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" customWidth="1"/>
+    <col min="3" max="3" width="56.7109375" customWidth="1"/>
+    <col min="4" max="4" width="29.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="20" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" customWidth="1"/>
     <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="36.59765625" customWidth="1"/>
-    <col min="10" max="10" width="18.1328125" style="22" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="16.86328125" style="22" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="36.5703125" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" style="22" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="16.85546875" style="22" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="15" style="22" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="19.86328125" style="22" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="17.73046875" style="22" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="19.85546875" style="22" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="17.7109375" style="22" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="16" style="22" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="16.3984375" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="15.73046875" style="22" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="19.1328125" style="22" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="15.3984375" style="22" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="20.265625" style="22" customWidth="1"/>
-    <col min="21" max="21" width="13.86328125" style="22" customWidth="1"/>
-    <col min="22" max="22" width="15.59765625" style="22" customWidth="1"/>
-    <col min="23" max="23" width="14.59765625" style="22" customWidth="1"/>
-    <col min="24" max="36" width="9.1328125" style="22"/>
+    <col min="16" max="16" width="16.42578125" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="15.7109375" style="22" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="19.140625" style="22" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="15.42578125" style="22" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="20.28515625" style="22" customWidth="1"/>
+    <col min="21" max="21" width="13.85546875" style="22" customWidth="1"/>
+    <col min="22" max="22" width="15.5703125" style="22" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="22" customWidth="1"/>
+    <col min="24" max="24" width="16.85546875" style="22" customWidth="1"/>
+    <col min="25" max="36" width="9.140625" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:59" ht="34.9" x14ac:dyDescent="0.9">
+    <row r="1" spans="2:59" ht="35.25" x14ac:dyDescent="0.5">
       <c r="B1" s="16" t="s">
         <v>0</v>
       </c>
@@ -913,7 +920,7 @@
       <c r="I1" s="6"/>
       <c r="P1" s="26"/>
     </row>
-    <row r="2" spans="2:59" ht="9" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="2" spans="2:59" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="6"/>
       <c r="D2" s="1"/>
       <c r="E2" s="17"/>
@@ -923,7 +930,7 @@
       <c r="I2" s="6"/>
       <c r="P2" s="26"/>
     </row>
-    <row r="3" spans="2:59" ht="19.5" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:59" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
         <v>19</v>
       </c>
@@ -990,7 +997,9 @@
       <c r="W3" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="X3" s="20"/>
+      <c r="X3" s="30" t="s">
+        <v>87</v>
+      </c>
       <c r="Y3" s="20"/>
       <c r="Z3" s="20"/>
       <c r="AA3" s="20"/>
@@ -1027,7 +1036,7 @@
       <c r="BF3" s="20"/>
       <c r="BG3" s="20"/>
     </row>
-    <row r="4" spans="2:59" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:59" ht="45" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>12</v>
       </c>
@@ -1097,7 +1106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:59" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
         <v>12</v>
       </c>
@@ -1165,7 +1174,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="6" spans="2:59" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>3</v>
       </c>
@@ -1231,7 +1240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:59" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
         <v>3</v>
       </c>
@@ -1286,7 +1295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:59" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
         <v>3</v>
       </c>
@@ -1341,7 +1350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:59" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
         <v>3</v>
       </c>
@@ -1390,7 +1399,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="10" spans="2:59" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
         <v>4</v>
       </c>
@@ -1453,7 +1462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:59" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:59" ht="45" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
         <v>5</v>
       </c>
@@ -1523,7 +1532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="2:59" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
         <v>5</v>
       </c>
@@ -1572,7 +1581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="2:59" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>5</v>
       </c>
@@ -1626,7 +1635,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="14" spans="2:59" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B14" s="9" t="s">
         <v>6</v>
       </c>
@@ -1694,7 +1703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:59" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
         <v>6</v>
       </c>
@@ -1762,7 +1771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="2:59" ht="57" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:59" ht="75" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
         <v>7</v>
       </c>
@@ -1830,7 +1839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>7</v>
       </c>
@@ -1876,7 +1885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
         <v>7</v>
       </c>
@@ -1916,7 +1925,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="19" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
         <v>7</v>
       </c>
@@ -1959,7 +1968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:23" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:23" ht="45" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>7</v>
       </c>
@@ -2002,7 +2011,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="21" spans="2:23" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:23" ht="90" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
         <v>8</v>
       </c>
@@ -2015,14 +2024,14 @@
       </c>
       <c r="F21" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>In Progess</v>
+        <v>Complete</v>
       </c>
       <c r="G21" s="10">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H21" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>51</v>
@@ -2065,7 +2074,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="22" spans="2:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
         <v>8</v>
       </c>
@@ -2078,14 +2087,14 @@
       </c>
       <c r="F22" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>In Progess</v>
+        <v>Complete</v>
       </c>
       <c r="G22" s="10">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="H22" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="23"/>
       <c r="L22" s="22">
@@ -2125,7 +2134,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="23" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
         <v>8</v>
       </c>
@@ -2159,7 +2168,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="24" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
         <v>8</v>
       </c>
@@ -2182,7 +2191,7 @@
       <c r="J24" s="23"/>
       <c r="P24" s="28"/>
     </row>
-    <row r="25" spans="2:23" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:23" ht="90" x14ac:dyDescent="0.25">
       <c r="B25" s="9" t="s">
         <v>8</v>
       </c>
@@ -2195,9 +2204,11 @@
       </c>
       <c r="F25" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>Not Started</v>
-      </c>
-      <c r="G25" s="10"/>
+        <v>In Progess</v>
+      </c>
+      <c r="G25" s="10">
+        <v>0.15</v>
+      </c>
       <c r="H25" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -2208,7 +2219,7 @@
       <c r="J25" s="23"/>
       <c r="P25" s="28"/>
     </row>
-    <row r="26" spans="2:23" ht="49.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:23" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="9" t="s">
         <v>2</v>
       </c>
@@ -2276,7 +2287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B27" s="9" t="s">
         <v>2</v>
       </c>
@@ -2331,7 +2342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
         <v>2</v>
       </c>
@@ -2380,7 +2391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
         <v>2</v>
       </c>
@@ -2427,7 +2438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B30" s="9" t="s">
         <v>9</v>
       </c>
@@ -2490,7 +2501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="2:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="9" t="s">
         <v>9</v>
       </c>
@@ -2553,7 +2564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B32" s="9" t="s">
         <v>9</v>
       </c>
@@ -2597,7 +2608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B33" s="9" t="s">
         <v>9</v>
       </c>
@@ -2638,7 +2649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B34" s="9" t="s">
         <v>9</v>
       </c>
@@ -2679,7 +2690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B35" s="9" t="s">
         <v>36</v>
       </c>
@@ -2745,7 +2756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B36" s="9" t="s">
         <v>36</v>
       </c>
@@ -2800,7 +2811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B37" s="9" t="s">
         <v>36</v>
       </c>
@@ -2854,7 +2865,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="38" spans="2:23" ht="57" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:23" ht="75" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="s">
         <v>26</v>
       </c>
@@ -2922,7 +2933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B39" s="9" t="s">
         <v>26</v>
       </c>
@@ -2990,7 +3001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="2:23" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:23" ht="30" x14ac:dyDescent="0.25">
       <c r="B40" s="9" t="s">
         <v>26</v>
       </c>
@@ -3060,7 +3071,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:23" ht="30" x14ac:dyDescent="0.25">
       <c r="B41" s="9" t="s">
         <v>10</v>
       </c>
@@ -3126,7 +3137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B42" s="7" t="s">
         <v>28</v>
       </c>
@@ -3192,7 +3203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
         <v>11</v>
       </c>
@@ -3258,7 +3269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
         <v>15</v>
       </c>
@@ -3324,7 +3335,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="45" spans="2:23" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:23" ht="30" x14ac:dyDescent="0.25">
       <c r="B45" s="7" t="s">
         <v>15</v>
       </c>
@@ -3373,7 +3384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B46" s="7" t="s">
         <v>16</v>
       </c>
@@ -3439,7 +3450,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
         <v>17</v>
       </c>
@@ -3455,7 +3466,7 @@
         <v>In Progess</v>
       </c>
       <c r="G47" s="13">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="H47" s="11">
         <f t="shared" si="1"/>
@@ -3505,7 +3516,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="48" spans="2:23" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:23" ht="45" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>52</v>
       </c>
@@ -3563,7 +3574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="2:23" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>54</v>
       </c>
@@ -3618,9 +3629,52 @@
         <v>1</v>
       </c>
     </row>
+    <row r="50" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>86</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E50" s="20">
+        <v>45980</v>
+      </c>
+      <c r="F50" s="9" t="str">
+        <f t="shared" ref="F50" si="4">IF(G50=1,"Complete",IF(G50&lt;&gt;0,"In Progess","Not Started"))</f>
+        <v>Complete</v>
+      </c>
+      <c r="G50" s="24">
+        <v>1</v>
+      </c>
+      <c r="H50" s="25">
+        <f t="shared" ref="H50" si="5">--(G50&gt;=1)</f>
+        <v>1</v>
+      </c>
+      <c r="M50" s="22">
+        <v>1</v>
+      </c>
+      <c r="N50" s="22">
+        <v>1</v>
+      </c>
+      <c r="O50" s="22">
+        <v>1</v>
+      </c>
+      <c r="P50" s="24">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="22">
+        <v>1</v>
+      </c>
+      <c r="R50" s="22">
+        <v>1</v>
+      </c>
+      <c r="S50" s="22">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B3:BG47" xr:uid="{825F216F-6A2C-43F0-976D-4459909E096A}"/>
-  <conditionalFormatting sqref="G4:G49">
+  <conditionalFormatting sqref="G4:G50">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -3642,7 +3696,7 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Start Date in this column under this heading" sqref="J3" xr:uid="{B097AD3D-83FE-4DB6-8AA6-82D58880DEE8}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Icon indicator for task completion in this column under this heading is automatically updated as tasks complete" sqref="H3" xr:uid="{E57FD015-A334-4A3D-9540-92E1D8A918A9}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Task in this column under this heading. Use heading filters to find specific entries" sqref="B3:D3" xr:uid="{6FDCA3F5-F6F1-45FB-8AE7-E90C5E60E365}"/>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Select entry from the list. Select CANCEL, then press ALT+DOWN ARROW to navigate the list. Select ENTER to make selection" sqref="F4:F49" xr:uid="{90892BC2-20A5-4151-9864-7558336C2FE7}">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Select entry from the list. Select CANCEL, then press ALT+DOWN ARROW to navigate the list. Select ENTER to make selection" sqref="F4:F50" xr:uid="{90892BC2-20A5-4151-9864-7558336C2FE7}">
       <formula1>"Not Started, In Progress, Deferred, Complete"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3664,7 +3718,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>G4:G49</xm:sqref>
+          <xm:sqref>G4:G50</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="22" id="{E713B901-0E7B-40B8-A534-1C73C66CF397}">
@@ -3683,7 +3737,7 @@
               <x14:cfIcon iconSet="3Symbols" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>H4:H49</xm:sqref>
+          <xm:sqref>H4:H50</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -3694,7 +3748,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23963325-1FFB-4B92-8120-662513F10342}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3902,18 +3956,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3936,14 +3990,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -3958,4 +4004,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/ContinuationProject/Status.xlsx
+++ b/ContinuationProject/Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\ContinuationProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD5E4A89-837F-4A43-BAB3-2E69F020F183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1F1D40B-BBD6-43B9-8F89-DC2410AA2CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{975D681B-08B9-4F16-AF36-2B35AB80030D}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="4" r:id="rId1"/>
@@ -899,7 +899,7 @@
     <col min="17" max="17" width="15.7109375" style="22" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="19.140625" style="22" hidden="1" customWidth="1"/>
     <col min="19" max="19" width="15.42578125" style="22" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="20.28515625" style="22" customWidth="1"/>
+    <col min="20" max="20" width="20.28515625" style="22" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13.85546875" style="22" customWidth="1"/>
     <col min="22" max="22" width="15.5703125" style="22" customWidth="1"/>
     <col min="23" max="23" width="14.5703125" style="22" customWidth="1"/>
@@ -1105,6 +1105,9 @@
       <c r="W4" s="22">
         <v>1</v>
       </c>
+      <c r="X4" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
@@ -1173,6 +1176,9 @@
       <c r="W5" s="22">
         <v>0.99</v>
       </c>
+      <c r="X5" s="22">
+        <v>0.99</v>
+      </c>
     </row>
     <row r="6" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
@@ -1237,6 +1243,9 @@
         <v>1</v>
       </c>
       <c r="W6" s="22">
+        <v>1</v>
+      </c>
+      <c r="X6" s="22">
         <v>1</v>
       </c>
     </row>
@@ -1294,6 +1303,9 @@
       <c r="W7" s="22">
         <v>1</v>
       </c>
+      <c r="X7" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
@@ -1349,6 +1361,9 @@
       <c r="W8" s="22">
         <v>1</v>
       </c>
+      <c r="X8" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
@@ -1398,6 +1413,9 @@
       <c r="W9" s="22">
         <v>0.99</v>
       </c>
+      <c r="X9" s="22">
+        <v>0.99</v>
+      </c>
     </row>
     <row r="10" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
@@ -1461,6 +1479,9 @@
       <c r="W10" s="22">
         <v>1</v>
       </c>
+      <c r="X10" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="2:59" ht="45" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
@@ -1531,6 +1552,9 @@
       <c r="W11" s="22">
         <v>1</v>
       </c>
+      <c r="X11" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
@@ -1580,6 +1604,9 @@
       <c r="W12" s="22">
         <v>1</v>
       </c>
+      <c r="X12" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
@@ -1634,6 +1661,9 @@
       <c r="W13" s="22">
         <v>0.98</v>
       </c>
+      <c r="X13" s="22">
+        <v>0.98</v>
+      </c>
     </row>
     <row r="14" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B14" s="9" t="s">
@@ -1702,6 +1732,9 @@
       <c r="W14" s="22">
         <v>1</v>
       </c>
+      <c r="X14" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="2:59" ht="30" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
@@ -1770,6 +1803,9 @@
       <c r="W15" s="22">
         <v>1</v>
       </c>
+      <c r="X15" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="2:59" ht="75" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
@@ -1838,8 +1874,11 @@
       <c r="W16" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="2:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="X16" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>7</v>
       </c>
@@ -1884,8 +1923,11 @@
       <c r="W17" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X17" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
         <v>7</v>
       </c>
@@ -1924,8 +1966,11 @@
       <c r="W18" s="22">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="19" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X18" s="22">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="19" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
         <v>7</v>
       </c>
@@ -1967,8 +2012,11 @@
       <c r="W19" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="2:23" ht="45" x14ac:dyDescent="0.25">
+      <c r="X19" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:24" ht="45" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>7</v>
       </c>
@@ -2010,8 +2058,11 @@
       <c r="W20" s="22">
         <v>0.98</v>
       </c>
-    </row>
-    <row r="21" spans="2:23" ht="90" x14ac:dyDescent="0.25">
+      <c r="X20" s="22">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="21" spans="2:24" ht="90" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
         <v>8</v>
       </c>
@@ -2073,8 +2124,11 @@
       <c r="W21" s="22">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="22" spans="2:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="X21" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
         <v>8</v>
       </c>
@@ -2133,8 +2187,11 @@
       <c r="W22" s="22">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="23" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X22" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
         <v>8</v>
       </c>
@@ -2167,8 +2224,11 @@
       <c r="W23" s="22">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="24" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X23" s="22">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
         <v>8</v>
       </c>
@@ -2191,7 +2251,7 @@
       <c r="J24" s="23"/>
       <c r="P24" s="28"/>
     </row>
-    <row r="25" spans="2:23" ht="90" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:24" ht="90" x14ac:dyDescent="0.25">
       <c r="B25" s="9" t="s">
         <v>8</v>
       </c>
@@ -2218,8 +2278,11 @@
       </c>
       <c r="J25" s="23"/>
       <c r="P25" s="28"/>
-    </row>
-    <row r="26" spans="2:23" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="X25" s="22">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="26" spans="2:24" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="9" t="s">
         <v>2</v>
       </c>
@@ -2286,8 +2349,11 @@
       <c r="W26" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X26" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B27" s="9" t="s">
         <v>2</v>
       </c>
@@ -2341,8 +2407,11 @@
       <c r="W27" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X27" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
         <v>2</v>
       </c>
@@ -2390,8 +2459,11 @@
       <c r="W28" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X28" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
         <v>2</v>
       </c>
@@ -2437,8 +2509,11 @@
       <c r="W29" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X29" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B30" s="9" t="s">
         <v>9</v>
       </c>
@@ -2500,8 +2575,11 @@
       <c r="W30" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="2:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="X30" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="9" t="s">
         <v>9</v>
       </c>
@@ -2563,8 +2641,11 @@
       <c r="W31" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X31" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B32" s="9" t="s">
         <v>9</v>
       </c>
@@ -2607,8 +2688,11 @@
       <c r="W32" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X32" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B33" s="9" t="s">
         <v>9</v>
       </c>
@@ -2648,8 +2732,11 @@
       <c r="W33" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X33" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B34" s="9" t="s">
         <v>9</v>
       </c>
@@ -2689,8 +2776,11 @@
       <c r="W34" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X34" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B35" s="9" t="s">
         <v>36</v>
       </c>
@@ -2755,8 +2845,11 @@
       <c r="W35" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X35" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B36" s="9" t="s">
         <v>36</v>
       </c>
@@ -2810,8 +2903,11 @@
       <c r="W36" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X36" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B37" s="9" t="s">
         <v>36</v>
       </c>
@@ -2864,8 +2960,11 @@
       <c r="W37" s="22">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="38" spans="2:23" ht="75" x14ac:dyDescent="0.25">
+      <c r="X37" s="22">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="38" spans="2:24" ht="75" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="s">
         <v>26</v>
       </c>
@@ -2932,8 +3031,11 @@
       <c r="W38" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X38" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B39" s="9" t="s">
         <v>26</v>
       </c>
@@ -3000,8 +3102,11 @@
       <c r="W39" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="2:23" ht="30" x14ac:dyDescent="0.25">
+      <c r="X39" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="2:24" ht="30" x14ac:dyDescent="0.25">
       <c r="B40" s="9" t="s">
         <v>26</v>
       </c>
@@ -3070,8 +3175,11 @@
       <c r="W40" s="22">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="41" spans="2:23" ht="30" x14ac:dyDescent="0.25">
+      <c r="X40" s="22">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="41" spans="2:24" ht="30" x14ac:dyDescent="0.25">
       <c r="B41" s="9" t="s">
         <v>10</v>
       </c>
@@ -3136,8 +3244,11 @@
       <c r="W41" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X41" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B42" s="7" t="s">
         <v>28</v>
       </c>
@@ -3202,8 +3313,11 @@
       <c r="W42" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X42" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
         <v>11</v>
       </c>
@@ -3268,8 +3382,11 @@
       <c r="W43" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X43" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
         <v>15</v>
       </c>
@@ -3334,8 +3451,11 @@
       <c r="W44" s="22">
         <v>0.99</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" ht="30" x14ac:dyDescent="0.25">
+      <c r="X44" s="22">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" ht="30" x14ac:dyDescent="0.25">
       <c r="B45" s="7" t="s">
         <v>15</v>
       </c>
@@ -3383,8 +3503,11 @@
       <c r="W45" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X45" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B46" s="7" t="s">
         <v>16</v>
       </c>
@@ -3449,8 +3572,11 @@
       <c r="W46" s="22">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X46" s="22">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
         <v>17</v>
       </c>
@@ -3515,8 +3641,11 @@
       <c r="W47" s="22">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" ht="45" x14ac:dyDescent="0.25">
+      <c r="X47" s="22">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" ht="45" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>52</v>
       </c>
@@ -3573,8 +3702,11 @@
       <c r="W48" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X48" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>54</v>
       </c>
@@ -3628,8 +3760,11 @@
       <c r="W49" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="X49" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>86</v>
       </c>
@@ -3669,6 +3804,9 @@
         <v>1</v>
       </c>
       <c r="S50" s="22">
+        <v>1</v>
+      </c>
+      <c r="X50" s="22">
         <v>1</v>
       </c>
     </row>
@@ -3755,6 +3893,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100C3422A7FFD03AF47B40E3148D61510DD" ma:contentTypeVersion="10" ma:contentTypeDescription="Opprett et nytt dokument." ma:contentTypeScope="" ma:versionID="93a5827b91256c075a5bcdb454d162de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0" xmlns:ns3="b6192152-6ac4-477a-b62a-2f500fcdf3b6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="13127a08f307124b01356346b67d6a81" ns2:_="" ns3:_="">
     <xsd:import namespace="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
@@ -3955,36 +4108,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CED3C9C-630D-4C4B-A736-44AEC9EEC0A0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
-    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4007,9 +4134,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CED3C9C-630D-4C4B-A736-44AEC9EEC0A0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
+    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/ContinuationProject/Status.xlsx
+++ b/ContinuationProject/Status.xlsx
@@ -8,10 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\ContinuationProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F62966-08A7-4B01-B615-C29597646EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BBB9FB2-F7D7-4828-A00E-4805A832F5E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D76F2AFF-8B83-4673-A33F-A4D572D8D434}"/>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{942B4681-B083-4B8C-B35C-475A016407EB}"/>
+    <workbookView xWindow="-1860" yWindow="10702" windowWidth="28995" windowHeight="15676" xr2:uid="{D76F2AFF-8B83-4673-A33F-A4D572D8D434}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="4" r:id="rId1"/>
@@ -20,8 +19,8 @@
     <sheet name="AdditionalActivities" sheetId="2" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Status!$B$3:$AS$46</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Status!$B$1:$I$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Status!$B$3:$AS$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Status!$B$1:$I$47</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="173">
   <si>
     <t>DISC DEXPI Continuation Project - Status</t>
   </si>
@@ -554,6 +553,15 @@
   </si>
   <si>
     <t>Symbol not required</t>
+  </si>
+  <si>
+    <t>Requirements Document Update M1</t>
+  </si>
+  <si>
+    <t>Updated requirements document with relevant changes</t>
+  </si>
+  <si>
+    <t>Heat tracing requirement change.</t>
   </si>
 </sst>
 </file>
@@ -777,7 +785,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
@@ -862,21 +870,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -884,7 +885,7 @@
     <cellStyle name="Done" xfId="4" xr:uid="{155A3BE5-8E81-4DF4-8692-E9EB5B66282A}"/>
     <cellStyle name="Heading 1" xfId="3" builtinId="16"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
     <cellStyle name="Title" xfId="2" builtinId="15"/>
   </cellStyles>
   <dxfs count="1">
@@ -1232,7 +1233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825F216F-6A2C-43F0-976D-4459909E096A}">
-  <dimension ref="B1:AS53"/>
+  <dimension ref="B1:AS54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.85546875" customWidth="1"/>
@@ -1357,6 +1358,9 @@
         <v>1</v>
       </c>
       <c r="I4" s="9"/>
+      <c r="J4" s="21">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
@@ -1376,10 +1380,13 @@
         <v>1</v>
       </c>
       <c r="H5" s="11">
-        <f t="shared" ref="H5:H48" si="0">--(G5&gt;=1)</f>
+        <f t="shared" ref="H5:H49" si="0">--(G5&gt;=1)</f>
         <v>1</v>
       </c>
       <c r="I5" s="9"/>
+      <c r="J5" s="21">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
@@ -1404,6 +1411,9 @@
         <v>1</v>
       </c>
       <c r="I6" s="9"/>
+      <c r="J6" s="21">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B7" s="9" t="s">
@@ -1428,6 +1438,9 @@
         <v>1</v>
       </c>
       <c r="I7" s="9"/>
+      <c r="J7" s="21">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
@@ -1452,6 +1465,9 @@
         <v>1</v>
       </c>
       <c r="I8" s="9"/>
+      <c r="J8" s="21">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
@@ -1475,6 +1491,9 @@
         <v>1</v>
       </c>
       <c r="I9" s="9"/>
+      <c r="J9" s="21">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
@@ -1499,6 +1518,9 @@
         <v>1</v>
       </c>
       <c r="I10" s="9"/>
+      <c r="J10" s="21">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
@@ -1523,6 +1545,9 @@
         <v>1</v>
       </c>
       <c r="I11" s="9"/>
+      <c r="J11" s="21">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
@@ -1547,6 +1572,9 @@
         <v>1</v>
       </c>
       <c r="I12" s="9"/>
+      <c r="J12" s="21">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
@@ -1570,6 +1598,9 @@
         <v>1</v>
       </c>
       <c r="I13" s="9"/>
+      <c r="J13" s="21">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B14" s="9" t="s">
@@ -1594,6 +1625,9 @@
         <v>1</v>
       </c>
       <c r="I14" s="9"/>
+      <c r="J14" s="21">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
@@ -1618,6 +1652,9 @@
         <v>1</v>
       </c>
       <c r="I15" s="9"/>
+      <c r="J15" s="21">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
@@ -1640,7 +1677,7 @@
       </c>
       <c r="I16" s="6"/>
     </row>
-    <row r="17" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>11</v>
       </c>
@@ -1661,7 +1698,7 @@
       </c>
       <c r="I17" s="6"/>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
         <v>11</v>
       </c>
@@ -1681,7 +1718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:10" ht="45" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
         <v>11</v>
       </c>
@@ -1707,8 +1744,11 @@
       <c r="I19" s="6" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J19" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>11</v>
       </c>
@@ -1734,8 +1774,11 @@
       <c r="I20" s="6" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J20" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
         <v>11</v>
       </c>
@@ -1758,8 +1801,11 @@
         <v>1</v>
       </c>
       <c r="I21" s="6"/>
-    </row>
-    <row r="22" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J21" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
         <v>11</v>
       </c>
@@ -1781,8 +1827,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J22" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
         <v>11</v>
       </c>
@@ -1804,8 +1853,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J23" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
         <v>86</v>
       </c>
@@ -1827,8 +1879,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J24" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="9" t="s">
         <v>86</v>
       </c>
@@ -1851,8 +1906,11 @@
         <v>1</v>
       </c>
       <c r="I25" s="6"/>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J25" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="9" t="s">
         <v>47</v>
       </c>
@@ -1877,8 +1935,11 @@
       <c r="I26" s="9" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J26" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="9" t="s">
         <v>47</v>
       </c>
@@ -1902,8 +1963,11 @@
       <c r="I27" s="9" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J27" s="21">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
         <v>47</v>
       </c>
@@ -1927,8 +1991,11 @@
       <c r="I28" s="9" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J28" s="21">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
         <v>86</v>
       </c>
@@ -1952,8 +2019,11 @@
         <v>0</v>
       </c>
       <c r="I29" s="9"/>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J29" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="9" t="s">
         <v>86</v>
       </c>
@@ -1976,8 +2046,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J30" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="9" t="s">
         <v>86</v>
       </c>
@@ -2001,8 +2074,11 @@
         <v>0</v>
       </c>
       <c r="I31" s="9"/>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J31" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="9" t="s">
         <v>86</v>
       </c>
@@ -2026,8 +2102,11 @@
         <v>0</v>
       </c>
       <c r="I32" s="9"/>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J32" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="9" t="s">
         <v>86</v>
       </c>
@@ -2051,8 +2130,11 @@
         <v>0</v>
       </c>
       <c r="I33" s="9"/>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J33" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="9" t="s">
         <v>86</v>
       </c>
@@ -2076,8 +2158,11 @@
         <v>0</v>
       </c>
       <c r="I34" s="9"/>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J34" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="9" t="s">
         <v>86</v>
       </c>
@@ -2101,8 +2186,11 @@
         <v>0</v>
       </c>
       <c r="I35" s="9"/>
-    </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J35" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="9" t="s">
         <v>86</v>
       </c>
@@ -2126,8 +2214,11 @@
         <v>0</v>
       </c>
       <c r="I36" s="9"/>
-    </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J36" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="9" t="s">
         <v>86</v>
       </c>
@@ -2151,8 +2242,11 @@
         <v>0</v>
       </c>
       <c r="I37" s="9"/>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J37" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="s">
         <v>86</v>
       </c>
@@ -2176,8 +2270,11 @@
         <v>0</v>
       </c>
       <c r="I38" s="9"/>
-    </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J38" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="9" t="s">
         <v>86</v>
       </c>
@@ -2201,8 +2298,11 @@
         <v>0</v>
       </c>
       <c r="I39" s="9"/>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J39" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="9" t="s">
         <v>95</v>
       </c>
@@ -2224,8 +2324,11 @@
         <v>0</v>
       </c>
       <c r="I40" s="9"/>
-    </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J40" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="9" t="s">
         <v>97</v>
       </c>
@@ -2248,8 +2351,11 @@
         <v>1</v>
       </c>
       <c r="I41" s="9"/>
-    </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J41" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="9" t="s">
         <v>97</v>
       </c>
@@ -2272,8 +2378,11 @@
         <v>1</v>
       </c>
       <c r="I42" s="9"/>
-    </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J42" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="9" t="s">
         <v>97</v>
       </c>
@@ -2296,8 +2405,11 @@
         <v>1</v>
       </c>
       <c r="I43" s="9"/>
-    </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="J43" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="9" t="s">
         <v>97</v>
       </c>
@@ -2310,111 +2422,129 @@
       </c>
       <c r="F44" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>In Progess</v>
+        <v>Complete</v>
       </c>
       <c r="G44" s="13">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="H44" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" s="9"/>
-    </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B45" s="7" t="s">
+      <c r="J44" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="B45" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="D45" t="s">
+        <v>172</v>
+      </c>
+      <c r="E45" s="19">
+        <v>46198</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G45" s="22">
+        <v>1</v>
+      </c>
+      <c r="H45" s="23">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="J45" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B46" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C45" s="9" t="s">
+      <c r="C46" s="9" t="s">
         <v>156</v>
-      </c>
-      <c r="D45" s="12"/>
-      <c r="E45" s="19">
-        <v>46161</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="G45" s="13">
-        <v>0.05</v>
-      </c>
-      <c r="H45" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I45" s="9"/>
-    </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B46" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>157</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="19">
         <v>46161</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G46" s="13">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="H46" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I46" s="9"/>
-    </row>
-    <row r="47" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="J46" s="21">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>155</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="D47" s="12"/>
       <c r="E47" s="19">
         <v>46161</v>
       </c>
       <c r="F47" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="G47" s="13">
+        <v>0</v>
+      </c>
+      <c r="H47" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I47" s="9"/>
+      <c r="J47" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="B48" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="E48" s="19">
+        <v>46161</v>
+      </c>
+      <c r="F48" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G47" s="22">
+      <c r="G48" s="22">
         <v>0.1</v>
       </c>
-      <c r="H47" s="23">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B48" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="E48" s="19">
-        <v>46198</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="G48" s="22">
-        <v>0</v>
-      </c>
       <c r="H48" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="J48" s="21">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="9" t="s">
         <v>158</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E49" s="19">
         <v>46198</v>
@@ -2426,16 +2556,19 @@
         <v>0</v>
       </c>
       <c r="H49" s="23">
-        <f t="shared" ref="H49" si="4">--(G49&gt;=1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J49" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="9" t="s">
         <v>158</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E50" s="19">
         <v>46198</v>
@@ -2447,16 +2580,19 @@
         <v>0</v>
       </c>
       <c r="H50" s="23">
-        <f t="shared" ref="H50:H51" si="5">--(G50&gt;=1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
+        <f t="shared" ref="H50" si="4">--(G50&gt;=1)</f>
+        <v>0</v>
+      </c>
+      <c r="J50" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="9" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E51" s="19">
         <v>46198</v>
@@ -2468,16 +2604,19 @@
         <v>0</v>
       </c>
       <c r="H51" s="23">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
+        <f t="shared" ref="H51:H52" si="5">--(G51&gt;=1)</f>
+        <v>0</v>
+      </c>
+      <c r="J51" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="9" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E52" s="19">
         <v>46198</v>
@@ -2489,34 +2628,64 @@
         <v>0</v>
       </c>
       <c r="H52" s="23">
-        <f t="shared" ref="H52:H53" si="6">--(G52&gt;=1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="2:8" ht="30" x14ac:dyDescent="0.25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B53" s="9" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E53" s="19">
         <v>46198</v>
       </c>
-      <c r="F53" s="38" t="s">
-        <v>91</v>
+      <c r="F53" s="9" t="s">
+        <v>92</v>
       </c>
       <c r="G53" s="22">
-        <v>0.15</v>
-      </c>
-      <c r="H53" s="39">
+        <v>0</v>
+      </c>
+      <c r="H53" s="23">
+        <f t="shared" ref="H53:H54" si="6">--(G53&gt;=1)</f>
+        <v>0</v>
+      </c>
+      <c r="J53" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="B54" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="E54" s="19">
+        <v>46198</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G54" s="22">
+        <v>0</v>
+      </c>
+      <c r="H54" s="23">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
+      <c r="J54" s="21">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:AS46" xr:uid="{825F216F-6A2C-43F0-976D-4459909E096A}"/>
-  <conditionalFormatting sqref="G4:G53">
+  <autoFilter ref="B3:AS47" xr:uid="{825F216F-6A2C-43F0-976D-4459909E096A}"/>
+  <conditionalFormatting sqref="G4:G54">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -2540,7 +2709,7 @@
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Select entry from the list. Select CANCEL, then press ALT+DOWN ARROW to navigate the list. Select ENTER to make selection" sqref="F4:F6" xr:uid="{90892BC2-20A5-4151-9864-7558336C2FE7}">
       <formula1>"Not Started, In Progress, Deferred, Complete"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7:F53" xr:uid="{6E270193-BC92-45F5-BF7F-52289D6B0587}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7:F54" xr:uid="{6E270193-BC92-45F5-BF7F-52289D6B0587}">
       <formula1>"Not Started, In Progress, Deferred, Complete,Not Required"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2562,7 +2731,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>G4:G53</xm:sqref>
+          <xm:sqref>G4:G54</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="25" id="{E713B901-0E7B-40B8-A534-1C73C66CF397}">
@@ -2581,7 +2750,7 @@
               <x14:cfIcon iconSet="3Symbols" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>H4:H53</xm:sqref>
+          <xm:sqref>H4:H54</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -2613,7 +2782,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="37" t="s">
+      <c r="A2" t="s">
         <v>107</v>
       </c>
       <c r="B2" t="s">
@@ -2627,7 +2796,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="37" t="s">
+      <c r="A3" t="s">
         <v>111</v>
       </c>
       <c r="B3" t="s">
@@ -2641,7 +2810,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="37" t="s">
+      <c r="A4" t="s">
         <v>114</v>
       </c>
       <c r="B4" t="s">
@@ -2655,7 +2824,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="37" t="s">
+      <c r="A5" t="s">
         <v>116</v>
       </c>
       <c r="B5" t="s">
@@ -2669,7 +2838,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="37" t="s">
+      <c r="A6" t="s">
         <v>118</v>
       </c>
       <c r="B6" t="s">
@@ -2683,7 +2852,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="37" t="s">
+      <c r="A7" t="s">
         <v>120</v>
       </c>
       <c r="B7" t="s">
@@ -2697,7 +2866,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="37" t="s">
+      <c r="A8" t="s">
         <v>122</v>
       </c>
       <c r="B8" t="s">
@@ -2711,7 +2880,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="37" t="s">
+      <c r="A9" t="s">
         <v>125</v>
       </c>
       <c r="B9" t="s">
@@ -2725,7 +2894,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="37" t="s">
+      <c r="A10" t="s">
         <v>127</v>
       </c>
       <c r="B10" t="s">
@@ -2739,7 +2908,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="37" t="s">
+      <c r="A11" t="s">
         <v>130</v>
       </c>
       <c r="B11" t="s">
@@ -2753,7 +2922,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="37" t="s">
+      <c r="A12" t="s">
         <v>132</v>
       </c>
       <c r="B12" t="s">
@@ -2767,7 +2936,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="37" t="s">
+      <c r="A13" t="s">
         <v>134</v>
       </c>
       <c r="B13" t="s">
@@ -2781,7 +2950,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
+      <c r="A14" t="s">
         <v>136</v>
       </c>
       <c r="B14" t="s">
@@ -2795,7 +2964,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="37" t="s">
+      <c r="A15" t="s">
         <v>137</v>
       </c>
       <c r="B15" t="s">
@@ -2809,7 +2978,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="37" t="s">
+      <c r="A16" t="s">
         <v>138</v>
       </c>
       <c r="B16" t="s">
@@ -2823,7 +2992,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="37" t="s">
+      <c r="A17" t="s">
         <v>140</v>
       </c>
       <c r="B17" t="s">
@@ -2837,7 +3006,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="37" t="s">
+      <c r="A18" t="s">
         <v>142</v>
       </c>
       <c r="B18" t="s">
@@ -2851,7 +3020,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="37" t="s">
+      <c r="A19" t="s">
         <v>144</v>
       </c>
       <c r="B19" t="s">
@@ -2865,7 +3034,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="37" t="s">
+      <c r="A20" t="s">
         <v>147</v>
       </c>
       <c r="B20" t="s">
@@ -2879,7 +3048,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="37" t="s">
+      <c r="A21" t="s">
         <v>149</v>
       </c>
       <c r="B21" t="s">
@@ -2982,44 +3151,44 @@
       <c r="D7" s="32"/>
     </row>
     <row r="8" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="35"/>
+      <c r="A8" s="34"/>
       <c r="B8" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
     </row>
     <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="34"/>
+      <c r="A9" s="36"/>
       <c r="B9" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
     </row>
     <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="34"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
     </row>
     <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="34"/>
+      <c r="A11" s="36"/>
       <c r="B11" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
     </row>
     <row r="12" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="36"/>
+      <c r="A12" s="35"/>
       <c r="B12" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
     </row>
     <row r="13" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="28" t="s">
@@ -3052,20 +3221,20 @@
       <c r="D15" s="32"/>
     </row>
     <row r="16" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="35"/>
+      <c r="A16" s="34"/>
       <c r="B16" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
     </row>
     <row r="17" spans="1:4" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="36"/>
+      <c r="A17" s="35"/>
       <c r="B17" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
     </row>
     <row r="18" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="28" t="s">
@@ -3106,20 +3275,20 @@
       <c r="D21" s="32"/>
     </row>
     <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="35"/>
+      <c r="A22" s="34"/>
       <c r="B22" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
     </row>
     <row r="23" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="36"/>
+      <c r="A23" s="35"/>
       <c r="B23" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
     </row>
     <row r="24" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="31"/>
@@ -3155,6 +3324,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100C3422A7FFD03AF47B40E3148D61510DD" ma:contentTypeVersion="10" ma:contentTypeDescription="Opprett et nytt dokument." ma:contentTypeScope="" ma:versionID="93a5827b91256c075a5bcdb454d162de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0" xmlns:ns3="b6192152-6ac4-477a-b62a-2f500fcdf3b6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="13127a08f307124b01356346b67d6a81" ns2:_="" ns3:_="">
     <xsd:import namespace="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
@@ -3355,36 +3539,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CED3C9C-630D-4C4B-A736-44AEC9EEC0A0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
-    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3407,9 +3565,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CED3C9C-630D-4C4B-A736-44AEC9EEC0A0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
+    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/ContinuationProject/Status.xlsx
+++ b/ContinuationProject/Status.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\ContinuationProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BBB9FB2-F7D7-4828-A00E-4805A832F5E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35908EE8-1559-46D1-9ACD-81BFD467251B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1860" yWindow="10702" windowWidth="28995" windowHeight="15676" xr2:uid="{D76F2AFF-8B83-4673-A33F-A4D572D8D434}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{D76F2AFF-8B83-4673-A33F-A4D572D8D434}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{942B4681-B083-4B8C-B35C-475A016407EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="4" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="6" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId3"/>
-    <sheet name="AdditionalActivities" sheetId="2" state="hidden" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId2"/>
+    <sheet name="AdditionalActivities" sheetId="2" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Status!$B$3:$AS$47</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Status!$B$1:$I$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Status!$B$3:$AS$46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Status!$B$1:$I$46</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="121">
   <si>
     <t>DISC DEXPI Continuation Project - Status</t>
   </si>
@@ -309,27 +309,15 @@
     <t>Not Required</t>
   </si>
   <si>
-    <t>Added 1G Heattracing rule to Requirements document, added HeatTraceRequired to other class types</t>
-  </si>
-  <si>
     <t>PIF: Shutdown</t>
   </si>
   <si>
-    <t xml:space="preserve">Added additional shutdown codes to Profile </t>
-  </si>
-  <si>
     <t>In Progress</t>
   </si>
   <si>
     <t>Not Started</t>
   </si>
   <si>
-    <t>Flip horizontally for heat trace rule and add options</t>
-  </si>
-  <si>
-    <t>Resized</t>
-  </si>
-  <si>
     <t>DISC DEXPI Profile - M1</t>
   </si>
   <si>
@@ -354,156 +342,6 @@
     <t>Update Symbol Ref ID</t>
   </si>
   <si>
-    <t>Error ID</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Error condition</t>
-  </si>
-  <si>
-    <t>Default severity</t>
-  </si>
-  <si>
-    <t>ERR-E01</t>
-  </si>
-  <si>
-    <t>Schema</t>
-  </si>
-  <si>
-    <t>XML is not well-formed: the file cannot be parsed as valid XML.</t>
-  </si>
-  <si>
-    <t>Error — file cannot be processed further</t>
-  </si>
-  <si>
-    <t>ERR-E02</t>
-  </si>
-  <si>
-    <t>Element namespace does not match the declared DEXPI 2.0 schema namespace.</t>
-  </si>
-  <si>
-    <t>Error</t>
-  </si>
-  <si>
-    <t>ERR-E03</t>
-  </si>
-  <si>
-    <t>An element present in the file is not defined in the DEXPI 2.0 XML schema.</t>
-  </si>
-  <si>
-    <t>ERR-E04</t>
-  </si>
-  <si>
-    <t>An attribute present on an element is not permitted for that element by the DEXPI 2.0 XML schema.</t>
-  </si>
-  <si>
-    <t>ERR-E05</t>
-  </si>
-  <si>
-    <t>A mandatory attribute defined in the DEXPI 2.0 schema is absent from an element that requires it.</t>
-  </si>
-  <si>
-    <t>ERR-E06</t>
-  </si>
-  <si>
-    <t>An attribute value does not conform to the data type defined for that attribute in the DEXPI 2.0 schema (e.g. non-numeric value in a numeric field).</t>
-  </si>
-  <si>
-    <t>ERR-E07</t>
-  </si>
-  <si>
-    <t>Meta model</t>
-  </si>
-  <si>
-    <t>An object's type attribute references a class that does not exist in the DEXPI 2.0 Plant Meta Model.</t>
-  </si>
-  <si>
-    <t>ERR-E08</t>
-  </si>
-  <si>
-    <t>An object is assigned to a parent element for which the DEXPI 2.0 Plant Meta Model does not permit objects of that type.</t>
-  </si>
-  <si>
-    <t>ERR-E09</t>
-  </si>
-  <si>
-    <t>Referential</t>
-  </si>
-  <si>
-    <t>An ID referenced by a relationship attribute does not correspond to any object present in the file.</t>
-  </si>
-  <si>
-    <t>ERR-E10</t>
-  </si>
-  <si>
-    <t>An ID attribute value is not unique within the file: two or more objects share the same ID.</t>
-  </si>
-  <si>
-    <t>ERR-E11</t>
-  </si>
-  <si>
-    <t>A Persistent Identifier (PersistentID) attribute value is not unique within the file.</t>
-  </si>
-  <si>
-    <t>ERR-E12</t>
-  </si>
-  <si>
-    <t>A relationship references an object of a type that is not permitted as the target of that relationship by the Plant Meta Model.</t>
-  </si>
-  <si>
-    <t>ERR-E13</t>
-  </si>
-  <si>
-    <t>ERR-E14</t>
-  </si>
-  <si>
-    <t>ERR-E15</t>
-  </si>
-  <si>
-    <t>A PlantMetaData element is absent from the file.</t>
-  </si>
-  <si>
-    <t>ERR-E16</t>
-  </si>
-  <si>
-    <t>A graphical element present in the DEXPI file has no corresponding model object (orphaned graphical element).</t>
-  </si>
-  <si>
-    <t>ERR-E17</t>
-  </si>
-  <si>
-    <t>A model object present in the DEXPI file has no corresponding graphical representation (orphaned model object).</t>
-  </si>
-  <si>
-    <t>PRF-E01</t>
-  </si>
-  <si>
-    <t>Profile</t>
-  </si>
-  <si>
-    <t>A profile XML file supplied by the member does not conform to the DEXPI Profile Meta Model structure and cannot be parsed.</t>
-  </si>
-  <si>
-    <t>PRF-E02</t>
-  </si>
-  <si>
-    <t>A PropertyConstraint in the profile references a ConstrainedType that does not exist in the DEXPI 2.0 Plant Meta Model or in any loaded extension profile model.</t>
-  </si>
-  <si>
-    <t>PRF-E03</t>
-  </si>
-  <si>
-    <t>An object of a ConstrainedType defined in the profile has a property whose value count is below the Lower bound specified in the PropertyConstraint.</t>
-  </si>
-  <si>
-    <t>Symbol reference for class as defined in profile is not correct</t>
-  </si>
-  <si>
-    <t>Node connection graphical x/y ordinates do not match connection</t>
-  </si>
-  <si>
     <t>DISC DEXPI Profile - M2</t>
   </si>
   <si>
@@ -555,13 +393,19 @@
     <t>Symbol not required</t>
   </si>
   <si>
-    <t>Requirements Document Update M1</t>
-  </si>
-  <si>
-    <t>Updated requirements document with relevant changes</t>
-  </si>
-  <si>
-    <t>Heat tracing requirement change.</t>
+    <t>New Type code</t>
+  </si>
+  <si>
+    <t>New symbol option - invalid grid points</t>
+  </si>
+  <si>
+    <t>Delayed by project approval</t>
+  </si>
+  <si>
+    <t>Need to check with project files.</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
   </si>
 </sst>
 </file>
@@ -785,7 +629,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
@@ -842,7 +686,6 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -879,6 +722,12 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Date" xfId="5" xr:uid="{2ABB41C5-3CC8-4E1C-85D9-965CF83E22BD}"/>
@@ -1244,9 +1093,9 @@
     <col min="6" max="6" width="14.42578125" customWidth="1"/>
     <col min="7" max="7" width="19.7109375" customWidth="1"/>
     <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="49" customWidth="1"/>
+    <col min="9" max="9" width="25.28515625" customWidth="1"/>
     <col min="10" max="10" width="16.85546875" style="21" customWidth="1"/>
-    <col min="11" max="11" width="34.42578125" style="21" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="21" customWidth="1"/>
     <col min="12" max="22" width="9.140625" style="21"/>
   </cols>
   <sheetData>
@@ -1261,6 +1110,7 @@
       <c r="G1" s="4"/>
       <c r="H1" s="1"/>
       <c r="I1" s="6"/>
+      <c r="J1" s="36"/>
     </row>
     <row r="2" spans="2:45" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="6"/>
@@ -1270,6 +1120,7 @@
       <c r="G2" s="4"/>
       <c r="H2" s="1"/>
       <c r="I2" s="6"/>
+      <c r="J2" s="36"/>
     </row>
     <row r="3" spans="2:45" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
@@ -1296,10 +1147,12 @@
       <c r="I3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="24" t="s">
+      <c r="J3" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="20"/>
+      <c r="K3" s="39" t="s">
+        <v>120</v>
+      </c>
       <c r="L3" s="20"/>
       <c r="M3" s="20"/>
       <c r="N3" s="20"/>
@@ -1358,7 +1211,10 @@
         <v>1</v>
       </c>
       <c r="I4" s="9"/>
-      <c r="J4" s="21">
+      <c r="J4" s="38">
+        <v>1</v>
+      </c>
+      <c r="K4" s="21">
         <v>1</v>
       </c>
     </row>
@@ -1380,11 +1236,14 @@
         <v>1</v>
       </c>
       <c r="H5" s="11">
-        <f t="shared" ref="H5:H49" si="0">--(G5&gt;=1)</f>
+        <f t="shared" ref="H5:H48" si="0">--(G5&gt;=1)</f>
         <v>1</v>
       </c>
       <c r="I5" s="9"/>
-      <c r="J5" s="21">
+      <c r="J5" s="38">
+        <v>1</v>
+      </c>
+      <c r="K5" s="21">
         <v>1</v>
       </c>
     </row>
@@ -1411,7 +1270,10 @@
         <v>1</v>
       </c>
       <c r="I6" s="9"/>
-      <c r="J6" s="21">
+      <c r="J6" s="38">
+        <v>1</v>
+      </c>
+      <c r="K6" s="21">
         <v>1</v>
       </c>
     </row>
@@ -1438,7 +1300,10 @@
         <v>1</v>
       </c>
       <c r="I7" s="9"/>
-      <c r="J7" s="21">
+      <c r="J7" s="38">
+        <v>1</v>
+      </c>
+      <c r="K7" s="21">
         <v>1</v>
       </c>
     </row>
@@ -1465,7 +1330,10 @@
         <v>1</v>
       </c>
       <c r="I8" s="9"/>
-      <c r="J8" s="21">
+      <c r="J8" s="38">
+        <v>1</v>
+      </c>
+      <c r="K8" s="21">
         <v>1</v>
       </c>
     </row>
@@ -1491,7 +1359,10 @@
         <v>1</v>
       </c>
       <c r="I9" s="9"/>
-      <c r="J9" s="21">
+      <c r="J9" s="38">
+        <v>1</v>
+      </c>
+      <c r="K9" s="21">
         <v>1</v>
       </c>
     </row>
@@ -1518,7 +1389,10 @@
         <v>1</v>
       </c>
       <c r="I10" s="9"/>
-      <c r="J10" s="21">
+      <c r="J10" s="38">
+        <v>1</v>
+      </c>
+      <c r="K10" s="21">
         <v>1</v>
       </c>
     </row>
@@ -1545,7 +1419,10 @@
         <v>1</v>
       </c>
       <c r="I11" s="9"/>
-      <c r="J11" s="21">
+      <c r="J11" s="38">
+        <v>1</v>
+      </c>
+      <c r="K11" s="21">
         <v>1</v>
       </c>
     </row>
@@ -1572,7 +1449,10 @@
         <v>1</v>
       </c>
       <c r="I12" s="9"/>
-      <c r="J12" s="21">
+      <c r="J12" s="38">
+        <v>1</v>
+      </c>
+      <c r="K12" s="21">
         <v>1</v>
       </c>
     </row>
@@ -1598,7 +1478,10 @@
         <v>1</v>
       </c>
       <c r="I13" s="9"/>
-      <c r="J13" s="21">
+      <c r="J13" s="38">
+        <v>1</v>
+      </c>
+      <c r="K13" s="21">
         <v>1</v>
       </c>
     </row>
@@ -1625,7 +1508,10 @@
         <v>1</v>
       </c>
       <c r="I14" s="9"/>
-      <c r="J14" s="21">
+      <c r="J14" s="38">
+        <v>1</v>
+      </c>
+      <c r="K14" s="21">
         <v>1</v>
       </c>
     </row>
@@ -1652,7 +1538,10 @@
         <v>1</v>
       </c>
       <c r="I15" s="9"/>
-      <c r="J15" s="21">
+      <c r="J15" s="38">
+        <v>1</v>
+      </c>
+      <c r="K15" s="21">
         <v>1</v>
       </c>
     </row>
@@ -1676,8 +1565,9 @@
         <v>0</v>
       </c>
       <c r="I16" s="6"/>
-    </row>
-    <row r="17" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J16" s="36"/>
+    </row>
+    <row r="17" spans="2:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>11</v>
       </c>
@@ -1697,8 +1587,9 @@
         <v>0</v>
       </c>
       <c r="I17" s="6"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J17" s="36"/>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
         <v>11</v>
       </c>
@@ -1717,8 +1608,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="2:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="J18" s="36"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
         <v>11</v>
       </c>
@@ -1726,7 +1618,7 @@
         <v>27</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>169</v>
+        <v>115</v>
       </c>
       <c r="E19" s="19">
         <v>46133</v>
@@ -1741,22 +1633,23 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I19" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="J19" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I19" s="6"/>
+      <c r="J19" s="38">
+        <v>1</v>
+      </c>
+      <c r="K19" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>169</v>
+        <v>115</v>
       </c>
       <c r="E20" s="19">
         <v>46133</v>
@@ -1771,14 +1664,15 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I20" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="J20" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I20" s="6"/>
+      <c r="J20" s="38">
+        <v>1</v>
+      </c>
+      <c r="K20" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
         <v>11</v>
       </c>
@@ -1801,11 +1695,14 @@
         <v>1</v>
       </c>
       <c r="I21" s="6"/>
-      <c r="J21" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J21" s="38">
+        <v>1</v>
+      </c>
+      <c r="K21" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
         <v>11</v>
       </c>
@@ -1827,11 +1724,14 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J22" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J22" s="38">
+        <v>1</v>
+      </c>
+      <c r="K22" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
         <v>11</v>
       </c>
@@ -1853,11 +1753,14 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J23" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J23" s="38">
+        <v>1</v>
+      </c>
+      <c r="K23" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
         <v>86</v>
       </c>
@@ -1879,11 +1782,14 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J24" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J24" s="38">
+        <v>1</v>
+      </c>
+      <c r="K24" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" s="9" t="s">
         <v>86</v>
       </c>
@@ -1906,11 +1812,14 @@
         <v>1</v>
       </c>
       <c r="I25" s="6"/>
-      <c r="J25" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J25" s="38">
+        <v>1</v>
+      </c>
+      <c r="K25" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" s="9" t="s">
         <v>47</v>
       </c>
@@ -1932,14 +1841,15 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I26" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="J26" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I26" s="9"/>
+      <c r="J26" s="38">
+        <v>1</v>
+      </c>
+      <c r="K26" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="9" t="s">
         <v>47</v>
       </c>
@@ -1951,23 +1861,24 @@
         <v>46161</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G27" s="10">
+        <v>1</v>
+      </c>
+      <c r="H27" s="11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I27" s="9"/>
+      <c r="J27" s="38">
         <v>0.15</v>
       </c>
-      <c r="H27" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="J27" s="21">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K27" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
         <v>47</v>
       </c>
@@ -1979,23 +1890,24 @@
         <v>46161</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G28" s="10">
+        <v>1</v>
+      </c>
+      <c r="H28" s="11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I28" s="9"/>
+      <c r="J28" s="38">
         <v>0.15</v>
       </c>
-      <c r="H28" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="J28" s="21">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K28" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
         <v>86</v>
       </c>
@@ -2003,27 +1915,30 @@
         <v>36</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="E29" s="19">
         <v>46161</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G29" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" s="9"/>
-      <c r="J29" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J29" s="38">
+        <v>0</v>
+      </c>
+      <c r="K29" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B30" s="9" t="s">
         <v>86</v>
       </c>
@@ -2031,26 +1946,32 @@
         <v>37</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="E30" s="19">
         <v>46161</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G30" s="10">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H30" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J30" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I30" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="J30" s="38">
+        <v>0</v>
+      </c>
+      <c r="K30" s="21">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B31" s="9" t="s">
         <v>86</v>
       </c>
@@ -2058,27 +1979,32 @@
         <v>38</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="E31" s="19">
         <v>46161</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G31" s="10">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H31" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I31" s="9"/>
-      <c r="J31" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I31" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="J31" s="38">
+        <v>0</v>
+      </c>
+      <c r="K31" s="21">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" s="9" t="s">
         <v>86</v>
       </c>
@@ -2086,27 +2012,30 @@
         <v>39</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="E32" s="19">
         <v>46161</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G32" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" s="9"/>
-      <c r="J32" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J32" s="38">
+        <v>0</v>
+      </c>
+      <c r="K32" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" s="9" t="s">
         <v>86</v>
       </c>
@@ -2114,27 +2043,32 @@
         <v>40</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="E33" s="19">
         <v>46161</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G33" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I33" s="9"/>
-      <c r="J33" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="J33" s="38">
+        <v>0</v>
+      </c>
+      <c r="K33" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B34" s="9" t="s">
         <v>86</v>
       </c>
@@ -2142,27 +2076,32 @@
         <v>41</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="E34" s="19">
         <v>46161</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G34" s="10">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H34" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I34" s="9"/>
-      <c r="J34" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I34" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="J34" s="38">
+        <v>0</v>
+      </c>
+      <c r="K34" s="21">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B35" s="9" t="s">
         <v>86</v>
       </c>
@@ -2170,27 +2109,32 @@
         <v>42</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="E35" s="19">
         <v>46161</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G35" s="10">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H35" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I35" s="9"/>
-      <c r="J35" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I35" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="J35" s="38">
+        <v>0</v>
+      </c>
+      <c r="K35" s="21">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B36" s="9" t="s">
         <v>86</v>
       </c>
@@ -2198,13 +2142,13 @@
         <v>43</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="E36" s="19">
         <v>46161</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G36" s="10">
         <v>0</v>
@@ -2213,12 +2157,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I36" s="9"/>
-      <c r="J36" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I36" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="J36" s="38">
+        <v>0</v>
+      </c>
+      <c r="K36" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" s="9" t="s">
         <v>86</v>
       </c>
@@ -2226,27 +2175,30 @@
         <v>44</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="E37" s="19">
         <v>46161</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G37" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" s="11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" s="9"/>
-      <c r="J37" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J37" s="38">
+        <v>0</v>
+      </c>
+      <c r="K37" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="s">
         <v>86</v>
       </c>
@@ -2254,27 +2206,32 @@
         <v>45</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="E38" s="19">
         <v>46161</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G38" s="10">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H38" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I38" s="9"/>
-      <c r="J38" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I38" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="J38" s="38">
+        <v>0</v>
+      </c>
+      <c r="K38" s="21">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" s="9" t="s">
         <v>86</v>
       </c>
@@ -2282,58 +2239,64 @@
         <v>46</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="E39" s="19">
         <v>46161</v>
       </c>
       <c r="F39" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G39" s="10">
+        <v>1</v>
+      </c>
+      <c r="H39" s="11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I39" s="9"/>
+      <c r="J39" s="38">
+        <v>0</v>
+      </c>
+      <c r="K39" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B40" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C40" s="9" t="s">
         <v>92</v>
-      </c>
-      <c r="G39" s="10">
-        <v>0</v>
-      </c>
-      <c r="H39" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I39" s="9"/>
-      <c r="J39" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B40" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>96</v>
       </c>
       <c r="D40" s="9"/>
       <c r="E40" s="19">
         <v>46133</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G40" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" s="11">
         <f t="shared" ref="H40" si="2">--(G40&gt;=1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" s="9"/>
-      <c r="J40" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J40" s="38">
+        <v>1</v>
+      </c>
+      <c r="K40" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" s="9" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D41" s="12"/>
       <c r="E41" s="19">
@@ -2351,16 +2314,19 @@
         <v>1</v>
       </c>
       <c r="I41" s="9"/>
-      <c r="J41" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J41" s="38">
+        <v>1</v>
+      </c>
+      <c r="K41" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="9" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D42" s="7"/>
       <c r="E42" s="19">
@@ -2378,16 +2344,19 @@
         <v>1</v>
       </c>
       <c r="I42" s="9"/>
-      <c r="J42" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J42" s="38">
+        <v>1</v>
+      </c>
+      <c r="K42" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" s="9" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D43" s="7"/>
       <c r="E43" s="19">
@@ -2405,16 +2374,19 @@
         <v>1</v>
       </c>
       <c r="I43" s="9"/>
-      <c r="J43" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J43" s="38">
+        <v>1</v>
+      </c>
+      <c r="K43" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44" s="9" t="s">
         <v>97</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>101</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="19">
@@ -2422,270 +2394,281 @@
       </c>
       <c r="F44" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>Complete</v>
+        <v>In Progess</v>
       </c>
       <c r="G44" s="13">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="H44" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" s="9"/>
-      <c r="J44" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="2:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B45" s="9" t="s">
-        <v>170</v>
+      <c r="J44" s="38">
+        <v>1</v>
+      </c>
+      <c r="K44" s="21">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B45" s="7" t="s">
+        <v>98</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="D45" t="s">
-        <v>172</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="D45" s="12"/>
       <c r="E45" s="19">
-        <v>46198</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G45" s="22">
-        <v>1</v>
-      </c>
-      <c r="H45" s="23">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J45" s="21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B46" s="7" t="s">
-        <v>102</v>
+        <v>46161</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="G45" s="13">
+        <v>1</v>
+      </c>
+      <c r="H45" s="11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I45" s="9"/>
+      <c r="J45" s="38">
+        <v>1</v>
+      </c>
+      <c r="K45" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B46" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>156</v>
+        <v>103</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="19">
         <v>46161</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G46" s="13">
+        <v>1</v>
+      </c>
+      <c r="H46" s="11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I46" s="9"/>
+      <c r="J46" s="38">
         <v>0.15</v>
       </c>
-      <c r="H46" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I46" s="9"/>
-      <c r="J46" s="21">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K46" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B47" s="9" t="s">
-        <v>153</v>
+        <v>100</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="D47" s="12"/>
+        <v>101</v>
+      </c>
       <c r="E47" s="19">
         <v>46161</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="G47" s="13">
-        <v>0</v>
-      </c>
-      <c r="H47" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I47" s="9"/>
-      <c r="J47" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="G47" s="22">
+        <v>0.95</v>
+      </c>
+      <c r="H47" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I47" t="s">
+        <v>119</v>
+      </c>
+      <c r="J47" s="38">
+        <v>0</v>
+      </c>
+      <c r="K47" s="21">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" s="9" t="s">
-        <v>154</v>
+        <v>104</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>155</v>
+        <v>106</v>
       </c>
       <c r="E48" s="19">
-        <v>46161</v>
+        <v>46198</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G48" s="22">
+        <v>0</v>
+      </c>
+      <c r="H48" s="23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J48" s="38">
         <v>0.1</v>
       </c>
-      <c r="H48" s="23">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J48" s="21">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K48" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" s="9" t="s">
-        <v>158</v>
+        <v>104</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>160</v>
+        <v>107</v>
       </c>
       <c r="E49" s="19">
         <v>46198</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G49" s="22">
         <v>0</v>
       </c>
       <c r="H49" s="23">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J49" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
+        <f t="shared" ref="H49" si="4">--(G49&gt;=1)</f>
+        <v>0</v>
+      </c>
+      <c r="J49" s="38">
+        <v>0</v>
+      </c>
+      <c r="K49" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" s="9" t="s">
-        <v>158</v>
+        <v>104</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="E50" s="19">
         <v>46198</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G50" s="22">
         <v>0</v>
       </c>
       <c r="H50" s="23">
-        <f t="shared" ref="H50" si="4">--(G50&gt;=1)</f>
-        <v>0</v>
-      </c>
-      <c r="J50" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+        <f t="shared" ref="H50:H51" si="5">--(G50&gt;=1)</f>
+        <v>0</v>
+      </c>
+      <c r="J50" s="38">
+        <v>0</v>
+      </c>
+      <c r="K50" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" s="9" t="s">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>164</v>
+        <v>109</v>
       </c>
       <c r="E51" s="19">
         <v>46198</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G51" s="22">
         <v>0</v>
       </c>
       <c r="H51" s="23">
-        <f t="shared" ref="H51:H52" si="5">--(G51&gt;=1)</f>
-        <v>0</v>
-      </c>
-      <c r="J51" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="38">
+        <v>0</v>
+      </c>
+      <c r="K51" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B52" s="9" t="s">
-        <v>162</v>
+        <v>105</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>163</v>
+        <v>111</v>
       </c>
       <c r="E52" s="19">
         <v>46198</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G52" s="22">
         <v>0</v>
       </c>
       <c r="H52" s="23">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J52" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+        <f t="shared" ref="H52:H53" si="6">--(G52&gt;=1)</f>
+        <v>0</v>
+      </c>
+      <c r="J52" s="38">
+        <v>0</v>
+      </c>
+      <c r="K52" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B53" s="9" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>165</v>
+        <v>114</v>
       </c>
       <c r="E53" s="19">
         <v>46198</v>
       </c>
-      <c r="F53" s="9" t="s">
-        <v>92</v>
+      <c r="F53" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="G53" s="22">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="H53" s="23">
-        <f t="shared" ref="H53:H54" si="6">--(G53&gt;=1)</f>
-        <v>0</v>
-      </c>
-      <c r="J53" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B54" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="C54" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="E54" s="19">
-        <v>46198</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="G54" s="22">
-        <v>0</v>
-      </c>
-      <c r="H54" s="23">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J54" s="21">
+      <c r="J53" s="38">
+        <v>0</v>
+      </c>
+      <c r="K53" s="21">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="J54" s="38">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:AS47" xr:uid="{825F216F-6A2C-43F0-976D-4459909E096A}"/>
-  <conditionalFormatting sqref="G4:G54">
+  <autoFilter ref="B3:AS46" xr:uid="{825F216F-6A2C-43F0-976D-4459909E096A}"/>
+  <conditionalFormatting sqref="G4:G53">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -2709,7 +2692,7 @@
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Select entry from the list. Select CANCEL, then press ALT+DOWN ARROW to navigate the list. Select ENTER to make selection" sqref="F4:F6" xr:uid="{90892BC2-20A5-4151-9864-7558336C2FE7}">
       <formula1>"Not Started, In Progress, Deferred, Complete"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7:F54" xr:uid="{6E270193-BC92-45F5-BF7F-52289D6B0587}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7:F53" xr:uid="{6E270193-BC92-45F5-BF7F-52289D6B0587}">
       <formula1>"Not Started, In Progress, Deferred, Complete,Not Required"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2731,7 +2714,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>G4:G54</xm:sqref>
+          <xm:sqref>G4:G53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="25" id="{E713B901-0E7B-40B8-A534-1C73C66CF397}">
@@ -2750,7 +2733,7 @@
               <x14:cfIcon iconSet="3Symbols" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>H4:H54</xm:sqref>
+          <xm:sqref>H4:H53</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -2759,314 +2742,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FF75A6A-A34E-4020-B195-EB8113DACDFE}">
-  <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="15.85546875" customWidth="1"/>
-    <col min="3" max="3" width="126" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>120</v>
-      </c>
-      <c r="B7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" t="s">
-        <v>121</v>
-      </c>
-      <c r="D7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>122</v>
-      </c>
-      <c r="B8" t="s">
-        <v>123</v>
-      </c>
-      <c r="C8" t="s">
-        <v>124</v>
-      </c>
-      <c r="D8" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>125</v>
-      </c>
-      <c r="B9" t="s">
-        <v>123</v>
-      </c>
-      <c r="C9" t="s">
-        <v>126</v>
-      </c>
-      <c r="D9" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>127</v>
-      </c>
-      <c r="B10" t="s">
-        <v>128</v>
-      </c>
-      <c r="C10" t="s">
-        <v>129</v>
-      </c>
-      <c r="D10" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>130</v>
-      </c>
-      <c r="B11" t="s">
-        <v>128</v>
-      </c>
-      <c r="C11" t="s">
-        <v>131</v>
-      </c>
-      <c r="D11" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>132</v>
-      </c>
-      <c r="B12" t="s">
-        <v>128</v>
-      </c>
-      <c r="C12" t="s">
-        <v>133</v>
-      </c>
-      <c r="D12" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>134</v>
-      </c>
-      <c r="B13" t="s">
-        <v>128</v>
-      </c>
-      <c r="C13" t="s">
-        <v>135</v>
-      </c>
-      <c r="D13" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>136</v>
-      </c>
-      <c r="B14" t="s">
-        <v>145</v>
-      </c>
-      <c r="C14" t="s">
-        <v>151</v>
-      </c>
-      <c r="D14" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>137</v>
-      </c>
-      <c r="B15" t="s">
-        <v>145</v>
-      </c>
-      <c r="C15" t="s">
-        <v>152</v>
-      </c>
-      <c r="D15" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>138</v>
-      </c>
-      <c r="B16" t="s">
-        <v>145</v>
-      </c>
-      <c r="C16" t="s">
-        <v>139</v>
-      </c>
-      <c r="D16" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>140</v>
-      </c>
-      <c r="B17" t="s">
-        <v>145</v>
-      </c>
-      <c r="C17" t="s">
-        <v>141</v>
-      </c>
-      <c r="D17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>142</v>
-      </c>
-      <c r="B18" t="s">
-        <v>145</v>
-      </c>
-      <c r="C18" t="s">
-        <v>143</v>
-      </c>
-      <c r="D18" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>144</v>
-      </c>
-      <c r="B19" t="s">
-        <v>145</v>
-      </c>
-      <c r="C19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D19" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>147</v>
-      </c>
-      <c r="B20" t="s">
-        <v>145</v>
-      </c>
-      <c r="C20" t="s">
-        <v>148</v>
-      </c>
-      <c r="D20" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>149</v>
-      </c>
-      <c r="B21" t="s">
-        <v>145</v>
-      </c>
-      <c r="C21" t="s">
-        <v>150</v>
-      </c>
-      <c r="D21" t="s">
-        <v>113</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB91EF88-7E56-441B-8A64-7F04D70AC37D}">
   <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3077,226 +2752,226 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="26" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="28" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="28"/>
-      <c r="B3" s="30" t="s">
+      <c r="A3" s="27"/>
+      <c r="B3" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
     </row>
     <row r="4" spans="1:4" ht="48" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="28"/>
-      <c r="B4" s="30" t="s">
+      <c r="A4" s="27"/>
+      <c r="B4" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
     </row>
     <row r="5" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="28" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="31"/>
-      <c r="B6" s="30" t="s">
+      <c r="A6" s="30"/>
+      <c r="B6" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
     </row>
     <row r="7" spans="1:4" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="31"/>
-      <c r="B7" s="30" t="s">
+      <c r="A7" s="30"/>
+      <c r="B7" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
     </row>
     <row r="8" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="34"/>
-      <c r="B8" s="33" t="s">
+      <c r="A8" s="33"/>
+      <c r="B8" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
     </row>
     <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="36"/>
-      <c r="B9" s="33" t="s">
+      <c r="A9" s="35"/>
+      <c r="B9" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
     </row>
     <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="36"/>
-      <c r="B10" s="33" t="s">
+      <c r="A10" s="35"/>
+      <c r="B10" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
     </row>
     <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="36"/>
-      <c r="B11" s="33" t="s">
+      <c r="A11" s="35"/>
+      <c r="B11" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
     </row>
     <row r="12" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="35"/>
-      <c r="B12" s="30" t="s">
+      <c r="A12" s="34"/>
+      <c r="B12" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
     </row>
     <row r="13" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="29" t="s">
+      <c r="D13" s="28" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="31"/>
-      <c r="B14" s="30" t="s">
+      <c r="A14" s="30"/>
+      <c r="B14" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
     </row>
     <row r="15" spans="1:4" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="31"/>
-      <c r="B15" s="30" t="s">
+      <c r="A15" s="30"/>
+      <c r="B15" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
     </row>
     <row r="16" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="34"/>
-      <c r="B16" s="33" t="s">
+      <c r="A16" s="33"/>
+      <c r="B16" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
     </row>
     <row r="17" spans="1:4" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="35"/>
-      <c r="B17" s="30" t="s">
+      <c r="A17" s="34"/>
+      <c r="B17" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
     </row>
     <row r="18" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="29" t="s">
+      <c r="D18" s="28" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="31"/>
-      <c r="B19" s="30" t="s">
+      <c r="A19" s="30"/>
+      <c r="B19" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
     </row>
     <row r="20" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="31"/>
-      <c r="B20" s="30" t="s">
+      <c r="A20" s="30"/>
+      <c r="B20" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
     </row>
     <row r="21" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="31"/>
-      <c r="B21" s="30" t="s">
+      <c r="A21" s="30"/>
+      <c r="B21" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
     </row>
     <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="34"/>
-      <c r="B22" s="33" t="s">
+      <c r="A22" s="33"/>
+      <c r="B22" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
     </row>
     <row r="23" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="35"/>
-      <c r="B23" s="30" t="s">
+      <c r="A23" s="34"/>
+      <c r="B23" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
     </row>
     <row r="24" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="31"/>
-      <c r="B24" s="30" t="s">
+      <c r="A24" s="30"/>
+      <c r="B24" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -3314,7 +2989,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23963325-1FFB-4B92-8120-662513F10342}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3324,21 +2999,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100C3422A7FFD03AF47B40E3148D61510DD" ma:contentTypeVersion="10" ma:contentTypeDescription="Opprett et nytt dokument." ma:contentTypeScope="" ma:versionID="93a5827b91256c075a5bcdb454d162de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0" xmlns:ns3="b6192152-6ac4-477a-b62a-2f500fcdf3b6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="13127a08f307124b01356346b67d6a81" ns2:_="" ns3:_="">
     <xsd:import namespace="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
@@ -3539,32 +3199,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CED3C9C-630D-4C4B-A736-44AEC9EEC0A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3581,4 +3231,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/ContinuationProject/Status.xlsx
+++ b/ContinuationProject/Status.xlsx
@@ -1,17 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\ContinuationProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35908EE8-1559-46D1-9ACD-81BFD467251B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{273908E1-C46B-4C17-AF31-DF066D883889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{D76F2AFF-8B83-4673-A33F-A4D572D8D434}"/>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{942B4681-B083-4B8C-B35C-475A016407EB}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{942B4681-B083-4B8C-B35C-475A016407EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Status" sheetId="4" r:id="rId1"/>
@@ -369,12 +368,6 @@
     <t>Add PCA symbol reference URI placeholder</t>
   </si>
   <si>
-    <t>Blueprint - rev 10</t>
-  </si>
-  <si>
-    <t>Blueprint files with updated symbols</t>
-  </si>
-  <si>
     <t>HTML - human readable Profile</t>
   </si>
   <si>
@@ -406,6 +399,12 @@
   </si>
   <si>
     <t>19/05/2026</t>
+  </si>
+  <si>
+    <t>Blueprint - rev 12</t>
+  </si>
+  <si>
+    <t>Blueprint files with updated symbol references</t>
   </si>
 </sst>
 </file>
@@ -629,7 +628,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
@@ -713,6 +712,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -722,19 +722,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Date" xfId="5" xr:uid="{2ABB41C5-3CC8-4E1C-85D9-965CF83E22BD}"/>
     <cellStyle name="Done" xfId="4" xr:uid="{155A3BE5-8E81-4DF4-8692-E9EB5B66282A}"/>
     <cellStyle name="Heading 1" xfId="3" builtinId="16"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
     <cellStyle name="Title" xfId="2" builtinId="15"/>
   </cellStyles>
   <dxfs count="1">
@@ -1110,7 +1104,7 @@
       <c r="G1" s="4"/>
       <c r="H1" s="1"/>
       <c r="I1" s="6"/>
-      <c r="J1" s="36"/>
+      <c r="J1"/>
     </row>
     <row r="2" spans="2:45" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="6"/>
@@ -1120,7 +1114,7 @@
       <c r="G2" s="4"/>
       <c r="H2" s="1"/>
       <c r="I2" s="6"/>
-      <c r="J2" s="36"/>
+      <c r="J2"/>
     </row>
     <row r="3" spans="2:45" ht="19.5" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
@@ -1147,11 +1141,11 @@
       <c r="I3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="39" t="s">
+      <c r="J3" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="39" t="s">
-        <v>120</v>
+      <c r="K3" s="33" t="s">
+        <v>118</v>
       </c>
       <c r="L3" s="20"/>
       <c r="M3" s="20"/>
@@ -1211,7 +1205,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="9"/>
-      <c r="J4" s="38">
+      <c r="J4" s="21">
         <v>1</v>
       </c>
       <c r="K4" s="21">
@@ -1240,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="9"/>
-      <c r="J5" s="38">
+      <c r="J5" s="21">
         <v>1</v>
       </c>
       <c r="K5" s="21">
@@ -1270,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="9"/>
-      <c r="J6" s="38">
+      <c r="J6" s="21">
         <v>1</v>
       </c>
       <c r="K6" s="21">
@@ -1300,7 +1294,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="9"/>
-      <c r="J7" s="38">
+      <c r="J7" s="21">
         <v>1</v>
       </c>
       <c r="K7" s="21">
@@ -1330,7 +1324,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="9"/>
-      <c r="J8" s="38">
+      <c r="J8" s="21">
         <v>1</v>
       </c>
       <c r="K8" s="21">
@@ -1359,7 +1353,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="9"/>
-      <c r="J9" s="38">
+      <c r="J9" s="21">
         <v>1</v>
       </c>
       <c r="K9" s="21">
@@ -1389,7 +1383,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="9"/>
-      <c r="J10" s="38">
+      <c r="J10" s="21">
         <v>1</v>
       </c>
       <c r="K10" s="21">
@@ -1419,7 +1413,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="9"/>
-      <c r="J11" s="38">
+      <c r="J11" s="21">
         <v>1</v>
       </c>
       <c r="K11" s="21">
@@ -1449,7 +1443,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="9"/>
-      <c r="J12" s="38">
+      <c r="J12" s="21">
         <v>1</v>
       </c>
       <c r="K12" s="21">
@@ -1478,7 +1472,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="9"/>
-      <c r="J13" s="38">
+      <c r="J13" s="21">
         <v>1</v>
       </c>
       <c r="K13" s="21">
@@ -1508,7 +1502,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="9"/>
-      <c r="J14" s="38">
+      <c r="J14" s="21">
         <v>1</v>
       </c>
       <c r="K14" s="21">
@@ -1538,7 +1532,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="9"/>
-      <c r="J15" s="38">
+      <c r="J15" s="21">
         <v>1</v>
       </c>
       <c r="K15" s="21">
@@ -1565,7 +1559,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="6"/>
-      <c r="J16" s="36"/>
+      <c r="J16"/>
     </row>
     <row r="17" spans="2:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
@@ -1587,7 +1581,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="6"/>
-      <c r="J17" s="36"/>
+      <c r="J17"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
@@ -1608,7 +1602,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="36"/>
+      <c r="J18"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
@@ -1618,7 +1612,7 @@
         <v>27</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E19" s="19">
         <v>46133</v>
@@ -1634,7 +1628,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="6"/>
-      <c r="J19" s="38">
+      <c r="J19" s="21">
         <v>1</v>
       </c>
       <c r="K19" s="21">
@@ -1649,7 +1643,7 @@
         <v>88</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E20" s="19">
         <v>46133</v>
@@ -1665,7 +1659,7 @@
         <v>1</v>
       </c>
       <c r="I20" s="6"/>
-      <c r="J20" s="38">
+      <c r="J20" s="21">
         <v>1</v>
       </c>
       <c r="K20" s="21">
@@ -1695,7 +1689,7 @@
         <v>1</v>
       </c>
       <c r="I21" s="6"/>
-      <c r="J21" s="38">
+      <c r="J21" s="21">
         <v>1</v>
       </c>
       <c r="K21" s="21">
@@ -1724,7 +1718,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J22" s="38">
+      <c r="J22" s="21">
         <v>1</v>
       </c>
       <c r="K22" s="21">
@@ -1753,7 +1747,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J23" s="38">
+      <c r="J23" s="21">
         <v>1</v>
       </c>
       <c r="K23" s="21">
@@ -1782,7 +1776,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J24" s="38">
+      <c r="J24" s="21">
         <v>1</v>
       </c>
       <c r="K24" s="21">
@@ -1812,7 +1806,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="6"/>
-      <c r="J25" s="38">
+      <c r="J25" s="21">
         <v>1</v>
       </c>
       <c r="K25" s="21">
@@ -1842,7 +1836,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="9"/>
-      <c r="J26" s="38">
+      <c r="J26" s="21">
         <v>1</v>
       </c>
       <c r="K26" s="21">
@@ -1871,7 +1865,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="9"/>
-      <c r="J27" s="38">
+      <c r="J27" s="21">
         <v>0.15</v>
       </c>
       <c r="K27" s="21">
@@ -1900,7 +1894,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="9"/>
-      <c r="J28" s="38">
+      <c r="J28" s="21">
         <v>0.15</v>
       </c>
       <c r="K28" s="21">
@@ -1915,7 +1909,7 @@
         <v>36</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E29" s="19">
         <v>46161</v>
@@ -1931,7 +1925,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="9"/>
-      <c r="J29" s="38">
+      <c r="J29" s="21">
         <v>0</v>
       </c>
       <c r="K29" s="21">
@@ -1946,7 +1940,7 @@
         <v>37</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E30" s="19">
         <v>46161</v>
@@ -1961,10 +1955,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I30" s="37" t="s">
-        <v>118</v>
-      </c>
-      <c r="J30" s="38">
+      <c r="I30" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="J30" s="21">
         <v>0</v>
       </c>
       <c r="K30" s="21">
@@ -1979,7 +1973,7 @@
         <v>38</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E31" s="19">
         <v>46161</v>
@@ -1994,10 +1988,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I31" s="37" t="s">
-        <v>118</v>
-      </c>
-      <c r="J31" s="38">
+      <c r="I31" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="J31" s="21">
         <v>0</v>
       </c>
       <c r="K31" s="21">
@@ -2012,7 +2006,7 @@
         <v>39</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E32" s="19">
         <v>46161</v>
@@ -2028,7 +2022,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="9"/>
-      <c r="J32" s="38">
+      <c r="J32" s="21">
         <v>0</v>
       </c>
       <c r="K32" s="21">
@@ -2043,7 +2037,7 @@
         <v>40</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E33" s="19">
         <v>46161</v>
@@ -2059,9 +2053,9 @@
         <v>1</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="J33" s="38">
+        <v>114</v>
+      </c>
+      <c r="J33" s="21">
         <v>0</v>
       </c>
       <c r="K33" s="21">
@@ -2076,7 +2070,7 @@
         <v>41</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E34" s="19">
         <v>46161</v>
@@ -2091,10 +2085,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I34" s="37" t="s">
-        <v>118</v>
-      </c>
-      <c r="J34" s="38">
+      <c r="I34" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="J34" s="21">
         <v>0</v>
       </c>
       <c r="K34" s="21">
@@ -2109,7 +2103,7 @@
         <v>42</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E35" s="19">
         <v>46161</v>
@@ -2124,10 +2118,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I35" s="37" t="s">
-        <v>118</v>
-      </c>
-      <c r="J35" s="38">
+      <c r="I35" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="J35" s="21">
         <v>0</v>
       </c>
       <c r="K35" s="21">
@@ -2142,7 +2136,7 @@
         <v>43</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E36" s="19">
         <v>46161</v>
@@ -2158,9 +2152,9 @@
         <v>0</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="J36" s="38">
+        <v>115</v>
+      </c>
+      <c r="J36" s="21">
         <v>0</v>
       </c>
       <c r="K36" s="21">
@@ -2175,7 +2169,7 @@
         <v>44</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E37" s="19">
         <v>46161</v>
@@ -2191,7 +2185,7 @@
         <v>1</v>
       </c>
       <c r="I37" s="9"/>
-      <c r="J37" s="38">
+      <c r="J37" s="21">
         <v>0</v>
       </c>
       <c r="K37" s="21">
@@ -2206,7 +2200,7 @@
         <v>45</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E38" s="19">
         <v>46161</v>
@@ -2222,9 +2216,9 @@
         <v>0</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="J38" s="38">
+        <v>116</v>
+      </c>
+      <c r="J38" s="21">
         <v>0</v>
       </c>
       <c r="K38" s="21">
@@ -2239,7 +2233,7 @@
         <v>46</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E39" s="19">
         <v>46161</v>
@@ -2255,7 +2249,7 @@
         <v>1</v>
       </c>
       <c r="I39" s="9"/>
-      <c r="J39" s="38">
+      <c r="J39" s="21">
         <v>0</v>
       </c>
       <c r="K39" s="21">
@@ -2284,7 +2278,7 @@
         <v>1</v>
       </c>
       <c r="I40" s="9"/>
-      <c r="J40" s="38">
+      <c r="J40" s="21">
         <v>1</v>
       </c>
       <c r="K40" s="21">
@@ -2314,7 +2308,7 @@
         <v>1</v>
       </c>
       <c r="I41" s="9"/>
-      <c r="J41" s="38">
+      <c r="J41" s="21">
         <v>1</v>
       </c>
       <c r="K41" s="21">
@@ -2344,7 +2338,7 @@
         <v>1</v>
       </c>
       <c r="I42" s="9"/>
-      <c r="J42" s="38">
+      <c r="J42" s="21">
         <v>1</v>
       </c>
       <c r="K42" s="21">
@@ -2374,7 +2368,7 @@
         <v>1</v>
       </c>
       <c r="I43" s="9"/>
-      <c r="J43" s="38">
+      <c r="J43" s="21">
         <v>1</v>
       </c>
       <c r="K43" s="21">
@@ -2404,7 +2398,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="9"/>
-      <c r="J44" s="38">
+      <c r="J44" s="21">
         <v>1</v>
       </c>
       <c r="K44" s="21">
@@ -2433,7 +2427,7 @@
         <v>1</v>
       </c>
       <c r="I45" s="9"/>
-      <c r="J45" s="38">
+      <c r="J45" s="21">
         <v>1</v>
       </c>
       <c r="K45" s="21">
@@ -2462,7 +2456,7 @@
         <v>1</v>
       </c>
       <c r="I46" s="9"/>
-      <c r="J46" s="38">
+      <c r="J46" s="21">
         <v>0.15</v>
       </c>
       <c r="K46" s="21">
@@ -2490,9 +2484,9 @@
         <v>0</v>
       </c>
       <c r="I47" t="s">
-        <v>119</v>
-      </c>
-      <c r="J47" s="38">
+        <v>117</v>
+      </c>
+      <c r="J47" s="21">
         <v>0</v>
       </c>
       <c r="K47" s="21">
@@ -2519,7 +2513,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J48" s="38">
+      <c r="J48" s="21">
         <v>0.1</v>
       </c>
       <c r="K48" s="21">
@@ -2546,7 +2540,7 @@
         <f t="shared" ref="H49" si="4">--(G49&gt;=1)</f>
         <v>0</v>
       </c>
-      <c r="J49" s="38">
+      <c r="J49" s="21">
         <v>0</v>
       </c>
       <c r="K49" s="21">
@@ -2558,7 +2552,7 @@
         <v>104</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E50" s="19">
         <v>46198</v>
@@ -2570,10 +2564,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="23">
-        <f t="shared" ref="H50:H51" si="5">--(G50&gt;=1)</f>
-        <v>0</v>
-      </c>
-      <c r="J50" s="38">
+        <f t="shared" ref="H50" si="5">--(G50&gt;=1)</f>
+        <v>0</v>
+      </c>
+      <c r="J50" s="21">
         <v>0</v>
       </c>
       <c r="K50" s="21">
@@ -2582,10 +2576,10 @@
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" s="9" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="E51" s="19">
         <v>46198</v>
@@ -2594,17 +2588,17 @@
         <v>90</v>
       </c>
       <c r="G51" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" s="23">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J51" s="38">
+        <f t="shared" ref="H51" si="6">--(G51&gt;=1)</f>
+        <v>1</v>
+      </c>
+      <c r="J51" s="21">
         <v>0</v>
       </c>
       <c r="K51" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="2:11" ht="30" x14ac:dyDescent="0.25">
@@ -2612,7 +2606,7 @@
         <v>105</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E52" s="19">
         <v>46198</v>
@@ -2624,10 +2618,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="23">
-        <f t="shared" ref="H52:H53" si="6">--(G52&gt;=1)</f>
-        <v>0</v>
-      </c>
-      <c r="J52" s="38">
+        <f t="shared" ref="H52:H53" si="7">--(G52&gt;=1)</f>
+        <v>0</v>
+      </c>
+      <c r="J52" s="21">
         <v>0</v>
       </c>
       <c r="K52" s="21">
@@ -2636,10 +2630,10 @@
     </row>
     <row r="53" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B53" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E53" s="19">
         <v>46198</v>
@@ -2651,10 +2645,10 @@
         <v>0.15</v>
       </c>
       <c r="H53" s="23">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J53" s="38">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="21">
         <v>0</v>
       </c>
       <c r="K53" s="21">
@@ -2662,7 +2656,7 @@
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="J54" s="38">
+      <c r="J54" s="21">
         <v>0</v>
       </c>
     </row>
@@ -2717,7 +2711,7 @@
           <xm:sqref>G4:G53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="25" id="{E713B901-0E7B-40B8-A534-1C73C66CF397}">
+          <x14:cfRule type="iconSet" priority="28" id="{E713B901-0E7B-40B8-A534-1C73C66CF397}">
             <x14:iconSet iconSet="3Symbols" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -2826,44 +2820,44 @@
       <c r="D7" s="31"/>
     </row>
     <row r="8" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="33"/>
+      <c r="A8" s="34"/>
       <c r="B8" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
     </row>
     <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="35"/>
+      <c r="A9" s="36"/>
       <c r="B9" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
     </row>
     <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="35"/>
+      <c r="A10" s="36"/>
       <c r="B10" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
     </row>
     <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="35"/>
+      <c r="A11" s="36"/>
       <c r="B11" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
     </row>
     <row r="12" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="34"/>
+      <c r="A12" s="35"/>
       <c r="B12" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
     </row>
     <row r="13" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="27" t="s">
@@ -2896,20 +2890,20 @@
       <c r="D15" s="31"/>
     </row>
     <row r="16" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="33"/>
+      <c r="A16" s="34"/>
       <c r="B16" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
     </row>
     <row r="17" spans="1:4" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="34"/>
+      <c r="A17" s="35"/>
       <c r="B17" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
     </row>
     <row r="18" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="27" t="s">
@@ -2950,20 +2944,20 @@
       <c r="D21" s="31"/>
     </row>
     <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="33"/>
+      <c r="A22" s="34"/>
       <c r="B22" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
     </row>
     <row r="23" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="34"/>
+      <c r="A23" s="35"/>
       <c r="B23" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="C23" s="34"/>
-      <c r="D23" s="34"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
     </row>
     <row r="24" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="30"/>
@@ -2999,6 +2993,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100C3422A7FFD03AF47B40E3148D61510DD" ma:contentTypeVersion="10" ma:contentTypeDescription="Opprett et nytt dokument." ma:contentTypeScope="" ma:versionID="93a5827b91256c075a5bcdb454d162de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0" xmlns:ns3="b6192152-6ac4-477a-b62a-2f500fcdf3b6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="13127a08f307124b01356346b67d6a81" ns2:_="" ns3:_="">
     <xsd:import namespace="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
@@ -3199,22 +3208,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CED3C9C-630D-4C4B-A736-44AEC9EEC0A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3231,29 +3250,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E81441C-10B0-478C-AED5-6210518ADFA7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE334B8-DB7D-495D-B7B7-7E69CDC1BE08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7ae1cb1b-b89b-4b35-8dc1-6b34b6393ff0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="b6192152-6ac4-477a-b62a-2f500fcdf3b6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>